--- a/FFT on froth/data_dep_augm_Pb.xlsx
+++ b/FFT on froth/data_dep_augm_Pb.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Relavage 4" sheetId="1" r:id="rId1"/>
+    <sheet name="Relavage Pb" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="205">
   <si>
     <t>points</t>
   </si>
@@ -29,6 +29,420 @@
   </si>
   <si>
     <t>Zn (%)</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-0.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-1.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-10.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-11.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-12.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-13.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-14.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-15.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-16.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-17.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-18.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-19.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-2.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-20.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-21.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-22.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-23.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-24.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-25.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-26.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-27.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-28.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-29.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-3.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-30.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-31.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-32.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-33.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-34.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-35.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-36.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-37.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-38.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-39.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-4.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-40.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-41.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-42.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-43.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-44.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-45.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-46.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-47.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-48.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-49.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-5.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-50.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-51.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-52.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-53.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-54.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-55.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-56.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-57.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-58.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-59.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-6.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-60.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-61.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-62.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-63.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-64.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-65.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-66.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-67.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-68.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-69.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-7.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-70.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-71.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-8.jpg</t>
+  </si>
+  <si>
+    <t>rl3_pb17-4-9.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-0.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-1.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-10.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-11.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-12.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-13.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-14.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-15.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-16.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-17.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-18.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-19.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-2.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-20.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-21.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-22.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-23.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-24.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-25.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-26.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-27.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-28.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-29.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-3.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-30.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-31.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-32.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-33.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-34.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-35.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-36.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-37.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-38.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-39.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-4.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-40.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-41.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-42.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-43.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-44.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-45.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-46.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-47.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-48.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-49.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-5.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-50.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-51.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-52.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-53.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-54.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-55.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-56.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-57.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-58.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-59.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-6.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-60.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-61.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-62.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-63.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-64.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-65.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-7.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-8.jpg</t>
+  </si>
+  <si>
+    <t>rl1_pb23-4-9.jpg</t>
   </si>
   <si>
     <t>rl4_pb15-7-0.jpg</t>
@@ -572,7 +986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -597,16 +1011,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>4.575938909733445</v>
+        <v>2.592698573507437</v>
       </c>
       <c r="C2">
-        <v>11.01205072612416</v>
+        <v>11.05923870183131</v>
       </c>
       <c r="D2">
-        <v>58.45280221181721</v>
+        <v>46.35799449797148</v>
       </c>
       <c r="E2">
-        <v>4.70909526343425</v>
+        <v>3.858969251400384</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -614,16 +1028,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>4.336594727740516</v>
+        <v>3.367116014035259</v>
       </c>
       <c r="C3">
-        <v>10.83707364406867</v>
+        <v>11.57426947970576</v>
       </c>
       <c r="D3">
-        <v>58.2648783369801</v>
+        <v>46.03188535751384</v>
       </c>
       <c r="E3">
-        <v>4.75699833570849</v>
+        <v>4.640204503734958</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -631,16 +1045,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>4.205045936227044</v>
+        <v>3.094719855356766</v>
       </c>
       <c r="C4">
-        <v>10.8017968686604</v>
+        <v>11.26243148372452</v>
       </c>
       <c r="D4">
-        <v>57.9169740893155</v>
+        <v>46.21898037955469</v>
       </c>
       <c r="E4">
-        <v>4.768122049959751</v>
+        <v>4.581931053914289</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -648,16 +1062,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>4.292338199960033</v>
+        <v>2.741092691383249</v>
       </c>
       <c r="C5">
-        <v>11.30584447527979</v>
+        <v>11.41019168259806</v>
       </c>
       <c r="D5">
-        <v>58.4160944423369</v>
+        <v>46.22920288398545</v>
       </c>
       <c r="E5">
-        <v>4.452874737269402</v>
+        <v>3.708986323166551</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -665,16 +1079,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>3.88987072183912</v>
+        <v>3.416922591780453</v>
       </c>
       <c r="C6">
-        <v>10.56830645496359</v>
+        <v>10.62565399755671</v>
       </c>
       <c r="D6">
-        <v>58.79977087884962</v>
+        <v>46.2066097972874</v>
       </c>
       <c r="E6">
-        <v>4.225759383157859</v>
+        <v>4.184496129779569</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -682,16 +1096,16 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>4.252324733803575</v>
+        <v>3.197121101822475</v>
       </c>
       <c r="C7">
-        <v>11.23232952096937</v>
+        <v>11.66241553222376</v>
       </c>
       <c r="D7">
-        <v>58.756054528375</v>
+        <v>46.06386946356611</v>
       </c>
       <c r="E7">
-        <v>4.189940933243967</v>
+        <v>4.473419075065475</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -699,16 +1113,16 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>4.265264383238292</v>
+        <v>4.268195496708804</v>
       </c>
       <c r="C8">
-        <v>10.55121708213462</v>
+        <v>11.39155662048191</v>
       </c>
       <c r="D8">
-        <v>57.93436484800486</v>
+        <v>46.23575220041424</v>
       </c>
       <c r="E8">
-        <v>3.940936299429934</v>
+        <v>4.046763525873202</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -716,16 +1130,16 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>4.014118046445708</v>
+        <v>3.315010633931984</v>
       </c>
       <c r="C9">
-        <v>11.26582431175723</v>
+        <v>11.12949779109028</v>
       </c>
       <c r="D9">
-        <v>58.10521886711243</v>
+        <v>46.40714409363097</v>
       </c>
       <c r="E9">
-        <v>4.138983699261955</v>
+        <v>3.967153519021084</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -733,16 +1147,16 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>4.019508640366423</v>
+        <v>4.158112742181768</v>
       </c>
       <c r="C10">
-        <v>11.09604886303255</v>
+        <v>11.81240710171963</v>
       </c>
       <c r="D10">
-        <v>58.74643311254081</v>
+        <v>46.461972481563</v>
       </c>
       <c r="E10">
-        <v>4.626316202311401</v>
+        <v>4.476263578564923</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -750,16 +1164,16 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>4.370567249782393</v>
+        <v>4.155642399316388</v>
       </c>
       <c r="C11">
-        <v>11.13661264922241</v>
+        <v>12.14773769759149</v>
       </c>
       <c r="D11">
-        <v>58.33450552621932</v>
+        <v>46.13792858241298</v>
       </c>
       <c r="E11">
-        <v>4.122583306364906</v>
+        <v>4.619374970217462</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -767,16 +1181,16 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>4.280600242689049</v>
+        <v>3.666622155506706</v>
       </c>
       <c r="C12">
-        <v>10.91152122994732</v>
+        <v>10.66173690743789</v>
       </c>
       <c r="D12">
-        <v>58.78832837682473</v>
+        <v>46.47004488049367</v>
       </c>
       <c r="E12">
-        <v>4.753696731821402</v>
+        <v>4.297849575826643</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -784,16 +1198,16 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>4.194983611967808</v>
+        <v>3.756626455739708</v>
       </c>
       <c r="C13">
-        <v>10.9385637524322</v>
+        <v>11.99773590140614</v>
       </c>
       <c r="D13">
-        <v>58.25937504443591</v>
+        <v>46.17323382731013</v>
       </c>
       <c r="E13">
-        <v>4.54500309773413</v>
+        <v>4.967009291693021</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -801,16 +1215,16 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>4.130808930901573</v>
+        <v>3.914718448596162</v>
       </c>
       <c r="C14">
-        <v>11.10020004014228</v>
+        <v>11.21381440538855</v>
       </c>
       <c r="D14">
-        <v>58.73308083832011</v>
+        <v>46.25416369083036</v>
       </c>
       <c r="E14">
-        <v>4.211329413962463</v>
+        <v>3.8684970331327</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -818,16 +1232,16 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>4.547281593720211</v>
+        <v>3.428272079597806</v>
       </c>
       <c r="C15">
-        <v>10.98391025982618</v>
+        <v>12.11768069308611</v>
       </c>
       <c r="D15">
-        <v>57.95348407682757</v>
+        <v>46.07982985095677</v>
       </c>
       <c r="E15">
-        <v>4.123340093217508</v>
+        <v>4.079893670579892</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -835,16 +1249,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>4.119370279535536</v>
+        <v>4.191664595472147</v>
       </c>
       <c r="C16">
-        <v>10.65718299222077</v>
+        <v>12.09329126355431</v>
       </c>
       <c r="D16">
-        <v>58.85036126899786</v>
+        <v>46.10490999856153</v>
       </c>
       <c r="E16">
-        <v>4.403073376376473</v>
+        <v>4.666855972014259</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -852,16 +1266,16 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>4.335732613852771</v>
+        <v>4.234658943097203</v>
       </c>
       <c r="C17">
-        <v>10.64661380069665</v>
+        <v>11.94428083716397</v>
       </c>
       <c r="D17">
-        <v>58.49449866961678</v>
+        <v>46.20259485379988</v>
       </c>
       <c r="E17">
-        <v>3.964626429328515</v>
+        <v>4.551522961870388</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -869,16 +1283,16 @@
         <v>21</v>
       </c>
       <c r="B18">
-        <v>4.248816438117952</v>
+        <v>2.787732421518615</v>
       </c>
       <c r="C18">
-        <v>11.28344817302068</v>
+        <v>11.66927889059096</v>
       </c>
       <c r="D18">
-        <v>58.72498504569884</v>
+        <v>46.12089687847315</v>
       </c>
       <c r="E18">
-        <v>3.942508592314096</v>
+        <v>5.020240596683117</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -886,16 +1300,16 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>3.981332936983367</v>
+        <v>4.114541748131536</v>
       </c>
       <c r="C19">
-        <v>11.42857109350497</v>
+        <v>11.65780355714616</v>
       </c>
       <c r="D19">
-        <v>58.45110522479911</v>
+        <v>46.04436249133353</v>
       </c>
       <c r="E19">
-        <v>4.100477353781171</v>
+        <v>4.282470103913346</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -903,16 +1317,16 @@
         <v>23</v>
       </c>
       <c r="B20">
-        <v>3.932113205967097</v>
+        <v>2.716123015905106</v>
       </c>
       <c r="C20">
-        <v>11.09555522274513</v>
+        <v>11.83580600734514</v>
       </c>
       <c r="D20">
-        <v>58.85785098019932</v>
+        <v>46.31785435773973</v>
       </c>
       <c r="E20">
-        <v>4.03702339909043</v>
+        <v>3.722762310455626</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -920,16 +1334,16 @@
         <v>24</v>
       </c>
       <c r="B21">
-        <v>4.420517771345158</v>
+        <v>2.881744841673688</v>
       </c>
       <c r="C21">
-        <v>11.17115914887424</v>
+        <v>12.06040823787726</v>
       </c>
       <c r="D21">
-        <v>58.3753253930588</v>
+        <v>46.39893128133419</v>
       </c>
       <c r="E21">
-        <v>4.775232584565713</v>
+        <v>4.790314626767479</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -937,16 +1351,16 @@
         <v>25</v>
       </c>
       <c r="B22">
-        <v>4.520123913338197</v>
+        <v>3.193705657676086</v>
       </c>
       <c r="C22">
-        <v>11.29706808219553</v>
+        <v>10.94768252592088</v>
       </c>
       <c r="D22">
-        <v>58.73929838277128</v>
+        <v>46.0185791648141</v>
       </c>
       <c r="E22">
-        <v>4.490259324838435</v>
+        <v>5.146938686696585</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -954,16 +1368,16 @@
         <v>26</v>
       </c>
       <c r="B23">
-        <v>4.177041012435553</v>
+        <v>3.095040738973983</v>
       </c>
       <c r="C23">
-        <v>10.47032266358723</v>
+        <v>11.09648541553623</v>
       </c>
       <c r="D23">
-        <v>58.546518017792</v>
+        <v>46.431163205678</v>
       </c>
       <c r="E23">
-        <v>4.893984110591992</v>
+        <v>3.946684164790486</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -971,16 +1385,16 @@
         <v>27</v>
       </c>
       <c r="B24">
-        <v>3.629332500977141</v>
+        <v>3.933795718861304</v>
       </c>
       <c r="C24">
-        <v>10.96266679880761</v>
+        <v>10.9654734835479</v>
       </c>
       <c r="D24">
-        <v>58.51824515632544</v>
+        <v>46.1586750144742</v>
       </c>
       <c r="E24">
-        <v>4.0130054289651</v>
+        <v>4.033460663229741</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -988,16 +1402,16 @@
         <v>28</v>
       </c>
       <c r="B25">
-        <v>3.94639500793495</v>
+        <v>3.538113196008861</v>
       </c>
       <c r="C25">
-        <v>11.3902650990514</v>
+        <v>11.42261396079351</v>
       </c>
       <c r="D25">
-        <v>58.4139522267924</v>
+        <v>46.36969128797122</v>
       </c>
       <c r="E25">
-        <v>4.321848192152152</v>
+        <v>4.220635412646967</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1005,16 +1419,16 @@
         <v>29</v>
       </c>
       <c r="B26">
-        <v>4.104876160883761</v>
+        <v>3.832810990834187</v>
       </c>
       <c r="C26">
-        <v>10.79664725398527</v>
+        <v>11.88398476713655</v>
       </c>
       <c r="D26">
-        <v>57.96585478741034</v>
+        <v>46.02860076958173</v>
       </c>
       <c r="E26">
-        <v>4.022583368274755</v>
+        <v>3.926174798128974</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1022,16 +1436,16 @@
         <v>30</v>
       </c>
       <c r="B27">
-        <v>3.863360187249241</v>
+        <v>3.410716527592298</v>
       </c>
       <c r="C27">
-        <v>10.80149644740371</v>
+        <v>10.95655873701188</v>
       </c>
       <c r="D27">
-        <v>58.2504876136078</v>
+        <v>46.06012146672988</v>
       </c>
       <c r="E27">
-        <v>4.117206835641085</v>
+        <v>5.124620938409272</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1039,16 +1453,16 @@
         <v>31</v>
       </c>
       <c r="B28">
-        <v>4.513028452698622</v>
+        <v>3.797463664373693</v>
       </c>
       <c r="C28">
-        <v>11.25274677414494</v>
+        <v>10.75656059499682</v>
       </c>
       <c r="D28">
-        <v>58.52076733336793</v>
+        <v>46.41447321443887</v>
       </c>
       <c r="E28">
-        <v>4.88430835772932</v>
+        <v>4.291195620682204</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1056,16 +1470,16 @@
         <v>32</v>
       </c>
       <c r="B29">
-        <v>4.306185548829802</v>
+        <v>2.543381798356851</v>
       </c>
       <c r="C29">
-        <v>10.65097764577771</v>
+        <v>11.24438423843446</v>
       </c>
       <c r="D29">
-        <v>58.81317874597801</v>
+        <v>46.07621014547986</v>
       </c>
       <c r="E29">
-        <v>4.280712041133131</v>
+        <v>5.056000712594136</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1073,16 +1487,16 @@
         <v>33</v>
       </c>
       <c r="B30">
-        <v>4.152829744181033</v>
+        <v>3.634050135703158</v>
       </c>
       <c r="C30">
-        <v>11.30306027133705</v>
+        <v>12.05037579339043</v>
       </c>
       <c r="D30">
-        <v>58.1755205828289</v>
+        <v>46.02992124664228</v>
       </c>
       <c r="E30">
-        <v>4.119465717043276</v>
+        <v>5.078874462479693</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1090,16 +1504,16 @@
         <v>34</v>
       </c>
       <c r="B31">
-        <v>4.433145352412757</v>
+        <v>3.301667540055715</v>
       </c>
       <c r="C31">
-        <v>10.92129551759725</v>
+        <v>11.40808510011583</v>
       </c>
       <c r="D31">
-        <v>58.34650083116099</v>
+        <v>46.18741399901288</v>
       </c>
       <c r="E31">
-        <v>4.243749797699866</v>
+        <v>4.507326397186617</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1107,16 +1521,16 @@
         <v>35</v>
       </c>
       <c r="B32">
-        <v>4.085105363191382</v>
+        <v>2.621098977109415</v>
       </c>
       <c r="C32">
-        <v>11.32209298830339</v>
+        <v>10.91458215970433</v>
       </c>
       <c r="D32">
-        <v>58.44945583198389</v>
+        <v>46.21659060704211</v>
       </c>
       <c r="E32">
-        <v>4.520275796461648</v>
+        <v>4.877018232143378</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1124,16 +1538,16 @@
         <v>36</v>
       </c>
       <c r="B33">
-        <v>4.256810115780051</v>
+        <v>2.705871952325335</v>
       </c>
       <c r="C33">
-        <v>10.67365936047286</v>
+        <v>11.87380428071107</v>
       </c>
       <c r="D33">
-        <v>58.60076774175108</v>
+        <v>45.99337335691192</v>
       </c>
       <c r="E33">
-        <v>3.933222816215901</v>
+        <v>4.03408400742885</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1141,16 +1555,16 @@
         <v>37</v>
       </c>
       <c r="B34">
-        <v>4.054609410538103</v>
+        <v>2.839997752409716</v>
       </c>
       <c r="C34">
-        <v>10.92022806177441</v>
+        <v>12.08660538563952</v>
       </c>
       <c r="D34">
-        <v>58.3255976088121</v>
+        <v>46.39851339178372</v>
       </c>
       <c r="E34">
-        <v>4.647283106654815</v>
+        <v>4.23541138629222</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1158,16 +1572,16 @@
         <v>38</v>
       </c>
       <c r="B35">
-        <v>4.419837384214274</v>
+        <v>4.097138674412497</v>
       </c>
       <c r="C35">
-        <v>11.23890279344202</v>
+        <v>10.68587015694093</v>
       </c>
       <c r="D35">
-        <v>58.83489713660548</v>
+        <v>46.12785399178848</v>
       </c>
       <c r="E35">
-        <v>4.50181382321552</v>
+        <v>4.170620399312092</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1175,16 +1589,16 @@
         <v>39</v>
       </c>
       <c r="B36">
-        <v>4.610446200829679</v>
+        <v>2.849125014365681</v>
       </c>
       <c r="C36">
-        <v>10.86814212804189</v>
+        <v>11.13375920747506</v>
       </c>
       <c r="D36">
-        <v>58.85918095991626</v>
+        <v>46.43949385055539</v>
       </c>
       <c r="E36">
-        <v>4.479468100093003</v>
+        <v>4.319547990683203</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1192,16 +1606,16 @@
         <v>40</v>
       </c>
       <c r="B37">
-        <v>3.956521789159718</v>
+        <v>3.119832016051373</v>
       </c>
       <c r="C37">
-        <v>10.4815720089554</v>
+        <v>11.79896471043419</v>
       </c>
       <c r="D37">
-        <v>58.13068358683083</v>
+        <v>46.30204625223075</v>
       </c>
       <c r="E37">
-        <v>4.237277016520919</v>
+        <v>4.690015342600688</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1209,16 +1623,16 @@
         <v>41</v>
       </c>
       <c r="B38">
-        <v>3.912410830283081</v>
+        <v>3.802153920489048</v>
       </c>
       <c r="C38">
-        <v>10.87934673234855</v>
+        <v>12.07680517545809</v>
       </c>
       <c r="D38">
-        <v>58.657646820946</v>
+        <v>46.46204610628803</v>
       </c>
       <c r="E38">
-        <v>4.803442932717997</v>
+        <v>4.450906795762883</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1226,16 +1640,16 @@
         <v>42</v>
       </c>
       <c r="B39">
-        <v>3.729281157202516</v>
+        <v>3.400762859362339</v>
       </c>
       <c r="C39">
-        <v>11.15384627511879</v>
+        <v>11.58983785982779</v>
       </c>
       <c r="D39">
-        <v>58.07055937174093</v>
+        <v>46.25506299709609</v>
       </c>
       <c r="E39">
-        <v>4.136622376101713</v>
+        <v>4.44680516837233</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1243,16 +1657,16 @@
         <v>43</v>
       </c>
       <c r="B40">
-        <v>4.50724611159575</v>
+        <v>2.80411785148322</v>
       </c>
       <c r="C40">
-        <v>10.82045677851542</v>
+        <v>11.43702043149429</v>
       </c>
       <c r="D40">
-        <v>58.2106514687913</v>
+        <v>46.40731534756513</v>
       </c>
       <c r="E40">
-        <v>4.796524111595251</v>
+        <v>4.275419191041058</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1260,16 +1674,16 @@
         <v>44</v>
       </c>
       <c r="B41">
-        <v>3.741038158005865</v>
+        <v>4.113643579944989</v>
       </c>
       <c r="C41">
-        <v>10.9824666167172</v>
+        <v>11.1992120067787</v>
       </c>
       <c r="D41">
-        <v>58.38670588400702</v>
+        <v>46.47424625972825</v>
       </c>
       <c r="E41">
-        <v>4.603732157087524</v>
+        <v>4.355272927963736</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1277,16 +1691,16 @@
         <v>45</v>
       </c>
       <c r="B42">
-        <v>4.158137873220882</v>
+        <v>4.186935996046884</v>
       </c>
       <c r="C42">
-        <v>10.58611983109481</v>
+        <v>11.1293757483571</v>
       </c>
       <c r="D42">
-        <v>58.16745141830921</v>
+        <v>46.44924265590506</v>
       </c>
       <c r="E42">
-        <v>4.001440877409491</v>
+        <v>4.277457760340726</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1294,16 +1708,16 @@
         <v>46</v>
       </c>
       <c r="B43">
-        <v>4.322977560503189</v>
+        <v>2.87761426974912</v>
       </c>
       <c r="C43">
-        <v>11.33909513006751</v>
+        <v>12.04545467676927</v>
       </c>
       <c r="D43">
-        <v>58.59288458892543</v>
+        <v>46.37568715541753</v>
       </c>
       <c r="E43">
-        <v>4.329051678890899</v>
+        <v>4.239831410630667</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1311,16 +1725,16 @@
         <v>47</v>
       </c>
       <c r="B44">
-        <v>3.966201838464502</v>
+        <v>3.752528079876015</v>
       </c>
       <c r="C44">
-        <v>10.6173647390689</v>
+        <v>11.88476249633435</v>
       </c>
       <c r="D44">
-        <v>58.0661978237506</v>
+        <v>46.23775798936099</v>
       </c>
       <c r="E44">
-        <v>4.200260644052557</v>
+        <v>3.772794224093606</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1328,16 +1742,16 @@
         <v>48</v>
       </c>
       <c r="B45">
-        <v>4.605110874906122</v>
+        <v>4.06872284054792</v>
       </c>
       <c r="C45">
-        <v>11.34124416592363</v>
+        <v>11.13315584312171</v>
       </c>
       <c r="D45">
-        <v>58.07259049128589</v>
+        <v>46.40389177038348</v>
       </c>
       <c r="E45">
-        <v>3.96799116259711</v>
+        <v>4.154441637746042</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1345,16 +1759,16 @@
         <v>49</v>
       </c>
       <c r="B46">
-        <v>4.207071193488013</v>
+        <v>3.62087709840288</v>
       </c>
       <c r="C46">
-        <v>11.33956284452664</v>
+        <v>11.91782263541489</v>
       </c>
       <c r="D46">
-        <v>58.34141773709212</v>
+        <v>46.23746876479829</v>
       </c>
       <c r="E46">
-        <v>3.939731982261516</v>
+        <v>3.982698632911618</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1362,16 +1776,16 @@
         <v>50</v>
       </c>
       <c r="B47">
-        <v>4.062984580288219</v>
+        <v>2.758473109249307</v>
       </c>
       <c r="C47">
-        <v>11.30499693762522</v>
+        <v>10.64466043099167</v>
       </c>
       <c r="D47">
-        <v>57.94614460417733</v>
+        <v>46.236929731858</v>
       </c>
       <c r="E47">
-        <v>4.568845160133243</v>
+        <v>4.027017083550675</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1379,16 +1793,16 @@
         <v>51</v>
       </c>
       <c r="B48">
-        <v>4.516251274623459</v>
+        <v>2.736279850641532</v>
       </c>
       <c r="C48">
-        <v>10.78130377715124</v>
+        <v>10.95711446167158</v>
       </c>
       <c r="D48">
-        <v>58.84768293500954</v>
+        <v>46.05037498526803</v>
       </c>
       <c r="E48">
-        <v>3.990751690980165</v>
+        <v>4.186914389941607</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1396,16 +1810,16 @@
         <v>52</v>
       </c>
       <c r="B49">
-        <v>4.128476673809213</v>
+        <v>3.893342012962855</v>
       </c>
       <c r="C49">
-        <v>10.96150147524279</v>
+        <v>11.12063030566085</v>
       </c>
       <c r="D49">
-        <v>58.00347181925085</v>
+        <v>46.1489083379501</v>
       </c>
       <c r="E49">
-        <v>4.255585058221368</v>
+        <v>4.354419633910084</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1413,16 +1827,16 @@
         <v>53</v>
       </c>
       <c r="B50">
-        <v>4.286857857489832</v>
+        <v>4.252359381357781</v>
       </c>
       <c r="C50">
-        <v>10.80697201510794</v>
+        <v>10.61376242279276</v>
       </c>
       <c r="D50">
-        <v>58.00796003264891</v>
+        <v>46.1057000894879</v>
       </c>
       <c r="E50">
-        <v>4.475819996910926</v>
+        <v>4.40459905403821</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1430,16 +1844,16 @@
         <v>54</v>
       </c>
       <c r="B51">
-        <v>4.355527470836111</v>
+        <v>4.086152875188926</v>
       </c>
       <c r="C51">
-        <v>11.23855818214176</v>
+        <v>10.73415030132847</v>
       </c>
       <c r="D51">
-        <v>58.06002297573419</v>
+        <v>46.38547364082829</v>
       </c>
       <c r="E51">
-        <v>4.748100001499514</v>
+        <v>3.848010257097002</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1447,16 +1861,16 @@
         <v>55</v>
       </c>
       <c r="B52">
-        <v>4.120479900660207</v>
+        <v>3.969425858976026</v>
       </c>
       <c r="C52">
-        <v>10.49422530557173</v>
+        <v>10.66320911769062</v>
       </c>
       <c r="D52">
-        <v>58.83279878947428</v>
+        <v>46.1214127723951</v>
       </c>
       <c r="E52">
-        <v>4.083188294335631</v>
+        <v>4.367633444970693</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1464,16 +1878,16 @@
         <v>56</v>
       </c>
       <c r="B53">
-        <v>4.060122220385509</v>
+        <v>3.628592024688523</v>
       </c>
       <c r="C53">
-        <v>11.23101910532248</v>
+        <v>11.35419899376532</v>
       </c>
       <c r="D53">
-        <v>58.13416564561713</v>
+        <v>46.44736991716449</v>
       </c>
       <c r="E53">
-        <v>4.036792192851397</v>
+        <v>4.996357218784453</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1481,16 +1895,16 @@
         <v>57</v>
       </c>
       <c r="B54">
-        <v>4.553130339418368</v>
+        <v>2.83778514306829</v>
       </c>
       <c r="C54">
-        <v>11.12262125595198</v>
+        <v>12.10004784013326</v>
       </c>
       <c r="D54">
-        <v>58.5225215968438</v>
+        <v>46.41262625125665</v>
       </c>
       <c r="E54">
-        <v>4.507699082691818</v>
+        <v>3.655847576113219</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1498,16 +1912,16 @@
         <v>58</v>
       </c>
       <c r="B55">
-        <v>4.250004206271269</v>
+        <v>3.605145989369063</v>
       </c>
       <c r="C55">
-        <v>11.23521065633871</v>
+        <v>10.87613852454056</v>
       </c>
       <c r="D55">
-        <v>58.54309309715886</v>
+        <v>46.15590402221442</v>
       </c>
       <c r="E55">
-        <v>4.626253337108354</v>
+        <v>4.989362943154562</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -1515,16 +1929,16 @@
         <v>59</v>
       </c>
       <c r="B56">
-        <v>4.14775708368636</v>
+        <v>3.22273608883096</v>
       </c>
       <c r="C56">
-        <v>10.53147356610449</v>
+        <v>11.77523544527866</v>
       </c>
       <c r="D56">
-        <v>58.56306571250304</v>
+        <v>46.31795686915815</v>
       </c>
       <c r="E56">
-        <v>4.381932705739508</v>
+        <v>4.77439937867784</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -1532,16 +1946,16 @@
         <v>60</v>
       </c>
       <c r="B57">
-        <v>4.086810978033161</v>
+        <v>3.200589948494231</v>
       </c>
       <c r="C57">
-        <v>10.9613364559051</v>
+        <v>12.1350648766846</v>
       </c>
       <c r="D57">
-        <v>58.54695093925778</v>
+        <v>46.15799298899801</v>
       </c>
       <c r="E57">
-        <v>4.047726166581732</v>
+        <v>3.680420730930585</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1549,16 +1963,16 @@
         <v>61</v>
       </c>
       <c r="B58">
-        <v>4.155527259765547</v>
+        <v>3.302235998344965</v>
       </c>
       <c r="C58">
-        <v>10.61307583446344</v>
+        <v>11.281537952942</v>
       </c>
       <c r="D58">
-        <v>58.36125382234674</v>
+        <v>46.20458333495078</v>
       </c>
       <c r="E58">
-        <v>4.056693568033556</v>
+        <v>5.08309686310514</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1566,16 +1980,16 @@
         <v>62</v>
       </c>
       <c r="B59">
-        <v>3.656043039425559</v>
+        <v>3.54065776068353</v>
       </c>
       <c r="C59">
-        <v>11.01044812654511</v>
+        <v>11.53573899019073</v>
       </c>
       <c r="D59">
-        <v>57.88068223365742</v>
+        <v>46.08557121560457</v>
       </c>
       <c r="E59">
-        <v>4.646785634861819</v>
+        <v>4.823256530131275</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1583,16 +1997,16 @@
         <v>63</v>
       </c>
       <c r="B60">
-        <v>4.205034098734986</v>
+        <v>4.028392438048671</v>
       </c>
       <c r="C60">
-        <v>10.93761440598363</v>
+        <v>11.13338080049813</v>
       </c>
       <c r="D60">
-        <v>58.7404943957885</v>
+        <v>46.33495597982929</v>
       </c>
       <c r="E60">
-        <v>4.824609539813955</v>
+        <v>4.115537320264857</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1600,16 +2014,16 @@
         <v>64</v>
       </c>
       <c r="B61">
-        <v>4.001721990941616</v>
+        <v>3.110848828382514</v>
       </c>
       <c r="C61">
-        <v>11.26007556988904</v>
+        <v>12.13968568315545</v>
       </c>
       <c r="D61">
-        <v>58.24284616822056</v>
+        <v>46.24566501847352</v>
       </c>
       <c r="E61">
-        <v>4.466588456498664</v>
+        <v>4.120479675775366</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1617,16 +2031,16 @@
         <v>65</v>
       </c>
       <c r="B62">
-        <v>4.417037884345704</v>
+        <v>3.243477345829332</v>
       </c>
       <c r="C62">
-        <v>11.20875262351858</v>
+        <v>11.38747194353881</v>
       </c>
       <c r="D62">
-        <v>58.50299756512472</v>
+        <v>46.38128664572512</v>
       </c>
       <c r="E62">
-        <v>4.10339720116556</v>
+        <v>3.833798491798211</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1634,16 +2048,2362 @@
         <v>66</v>
       </c>
       <c r="B63">
-        <v>4.163239834450339</v>
+        <v>3.950928883704919</v>
       </c>
       <c r="C63">
-        <v>11.12897177904903</v>
+        <v>11.46624788943533</v>
       </c>
       <c r="D63">
-        <v>58.83951163182618</v>
+        <v>46.0808680638352</v>
       </c>
       <c r="E63">
-        <v>4.855750484731708</v>
+        <v>4.705604663967398</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
+        <v>67</v>
+      </c>
+      <c r="B64">
+        <v>4.216562907476051</v>
+      </c>
+      <c r="C64">
+        <v>11.30017926726872</v>
+      </c>
+      <c r="D64">
+        <v>46.22256562318555</v>
+      </c>
+      <c r="E64">
+        <v>3.654940526833854</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
+        <v>68</v>
+      </c>
+      <c r="B65">
+        <v>3.814426706597072</v>
+      </c>
+      <c r="C65">
+        <v>10.83801847997656</v>
+      </c>
+      <c r="D65">
+        <v>46.01187008759192</v>
+      </c>
+      <c r="E65">
+        <v>3.943272726828185</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
+        <v>69</v>
+      </c>
+      <c r="B66">
+        <v>3.198396467120755</v>
+      </c>
+      <c r="C66">
+        <v>11.38948673900856</v>
+      </c>
+      <c r="D66">
+        <v>46.2556985904742</v>
+      </c>
+      <c r="E66">
+        <v>4.719458530353291</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
+        <v>70</v>
+      </c>
+      <c r="B67">
+        <v>2.569245360189521</v>
+      </c>
+      <c r="C67">
+        <v>12.09590394343027</v>
+      </c>
+      <c r="D67">
+        <v>46.09097752390279</v>
+      </c>
+      <c r="E67">
+        <v>4.48276255941877</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>71</v>
+      </c>
+      <c r="B68">
+        <v>3.801711069368571</v>
+      </c>
+      <c r="C68">
+        <v>11.77897049604158</v>
+      </c>
+      <c r="D68">
+        <v>46.24792065345931</v>
+      </c>
+      <c r="E68">
+        <v>4.568227874882478</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" t="s">
+        <v>72</v>
+      </c>
+      <c r="B69">
+        <v>4.289755697617033</v>
+      </c>
+      <c r="C69">
+        <v>11.79480603568319</v>
+      </c>
+      <c r="D69">
+        <v>46.2380575140478</v>
+      </c>
+      <c r="E69">
+        <v>4.296533656632108</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>73</v>
+      </c>
+      <c r="B70">
+        <v>4.043787607979899</v>
+      </c>
+      <c r="C70">
+        <v>10.88395573192282</v>
+      </c>
+      <c r="D70">
+        <v>46.33467570640756</v>
+      </c>
+      <c r="E70">
+        <v>4.471257406581785</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" t="s">
+        <v>74</v>
+      </c>
+      <c r="B71">
+        <v>2.757922456522351</v>
+      </c>
+      <c r="C71">
+        <v>11.53727238046428</v>
+      </c>
+      <c r="D71">
+        <v>46.26001855365536</v>
+      </c>
+      <c r="E71">
+        <v>4.647724544933252</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" t="s">
+        <v>75</v>
+      </c>
+      <c r="B72">
+        <v>3.029915697652812</v>
+      </c>
+      <c r="C72">
+        <v>11.70140041361511</v>
+      </c>
+      <c r="D72">
+        <v>46.45011499153905</v>
+      </c>
+      <c r="E72">
+        <v>3.860393725757524</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
+        <v>76</v>
+      </c>
+      <c r="B73">
+        <v>3.157412516932481</v>
+      </c>
+      <c r="C73">
+        <v>10.82195248196243</v>
+      </c>
+      <c r="D73">
+        <v>46.18092322071766</v>
+      </c>
+      <c r="E73">
+        <v>3.718708970090021</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" t="s">
+        <v>77</v>
+      </c>
+      <c r="B74">
+        <v>4.491395378365481</v>
+      </c>
+      <c r="C74">
+        <v>23.54920808690757</v>
+      </c>
+      <c r="D74">
+        <v>22.41714370146981</v>
+      </c>
+      <c r="E74">
+        <v>6.936260411663577</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
+        <v>78</v>
+      </c>
+      <c r="B75">
+        <v>4.686634871645299</v>
+      </c>
+      <c r="C75">
+        <v>23.51805314771532</v>
+      </c>
+      <c r="D75">
+        <v>22.29706110054634</v>
+      </c>
+      <c r="E75">
+        <v>6.174704589921488</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
+        <v>79</v>
+      </c>
+      <c r="B76">
+        <v>3.717524901868765</v>
+      </c>
+      <c r="C76">
+        <v>24.18268197222917</v>
+      </c>
+      <c r="D76">
+        <v>22.2185391481419</v>
+      </c>
+      <c r="E76">
+        <v>7.417777469260153</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" t="s">
+        <v>80</v>
+      </c>
+      <c r="B77">
+        <v>4.743190664825947</v>
+      </c>
+      <c r="C77">
+        <v>24.06532175999295</v>
+      </c>
+      <c r="D77">
+        <v>22.28682278211021</v>
+      </c>
+      <c r="E77">
+        <v>6.176993517739152</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" t="s">
+        <v>81</v>
+      </c>
+      <c r="B78">
+        <v>3.933970951598246</v>
+      </c>
+      <c r="C78">
+        <v>23.6091570268159</v>
+      </c>
+      <c r="D78">
+        <v>22.40091341261507</v>
+      </c>
+      <c r="E78">
+        <v>6.865608939524316</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" t="s">
+        <v>82</v>
+      </c>
+      <c r="B79">
+        <v>3.017678675845426</v>
+      </c>
+      <c r="C79">
+        <v>24.09693232970253</v>
+      </c>
+      <c r="D79">
+        <v>22.17068338894756</v>
+      </c>
+      <c r="E79">
+        <v>5.95005340272021</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" t="s">
+        <v>83</v>
+      </c>
+      <c r="B80">
+        <v>3.362458563683292</v>
+      </c>
+      <c r="C80">
+        <v>23.43549161030057</v>
+      </c>
+      <c r="D80">
+        <v>22.07596265134971</v>
+      </c>
+      <c r="E80">
+        <v>7.296587677426117</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" t="s">
+        <v>84</v>
+      </c>
+      <c r="B81">
+        <v>3.320070792033388</v>
+      </c>
+      <c r="C81">
+        <v>24.17838997545056</v>
+      </c>
+      <c r="D81">
+        <v>22.40679142376089</v>
+      </c>
+      <c r="E81">
+        <v>6.209265648715087</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" t="s">
+        <v>85</v>
+      </c>
+      <c r="B82">
+        <v>3.374896683260742</v>
+      </c>
+      <c r="C82">
+        <v>23.53846473466524</v>
+      </c>
+      <c r="D82">
+        <v>22.34736977221827</v>
+      </c>
+      <c r="E82">
+        <v>6.479817439431301</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" t="s">
+        <v>86</v>
+      </c>
+      <c r="B83">
+        <v>3.947806636073709</v>
+      </c>
+      <c r="C83">
+        <v>23.71681910996577</v>
+      </c>
+      <c r="D83">
+        <v>22.19143733540422</v>
+      </c>
+      <c r="E83">
+        <v>6.050987063069512</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" t="s">
+        <v>87</v>
+      </c>
+      <c r="B84">
+        <v>3.229989569374899</v>
+      </c>
+      <c r="C84">
+        <v>24.238690267492</v>
+      </c>
+      <c r="D84">
+        <v>22.26105588833888</v>
+      </c>
+      <c r="E84">
+        <v>7.063729101457799</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" t="s">
+        <v>88</v>
+      </c>
+      <c r="B85">
+        <v>3.490385246291587</v>
+      </c>
+      <c r="C85">
+        <v>24.17391801863201</v>
+      </c>
+      <c r="D85">
+        <v>22.53444499169558</v>
+      </c>
+      <c r="E85">
+        <v>6.054911190299125</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" t="s">
+        <v>89</v>
+      </c>
+      <c r="B86">
+        <v>4.639998115049358</v>
+      </c>
+      <c r="C86">
+        <v>23.59417356017168</v>
+      </c>
+      <c r="D86">
+        <v>22.24983200239922</v>
+      </c>
+      <c r="E86">
+        <v>5.849905953004901</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" t="s">
+        <v>90</v>
+      </c>
+      <c r="B87">
+        <v>3.058841622099688</v>
+      </c>
+      <c r="C87">
+        <v>23.98321257041765</v>
+      </c>
+      <c r="D87">
+        <v>22.14927446604872</v>
+      </c>
+      <c r="E87">
+        <v>6.459916547717751</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" t="s">
+        <v>91</v>
+      </c>
+      <c r="B88">
+        <v>4.520737688127776</v>
+      </c>
+      <c r="C88">
+        <v>23.10792790331983</v>
+      </c>
+      <c r="D88">
+        <v>22.22068816323734</v>
+      </c>
+      <c r="E88">
+        <v>7.263312002213215</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" t="s">
+        <v>92</v>
+      </c>
+      <c r="B89">
+        <v>3.692684621196571</v>
+      </c>
+      <c r="C89">
+        <v>23.73735575258467</v>
+      </c>
+      <c r="D89">
+        <v>22.13065728075355</v>
+      </c>
+      <c r="E89">
+        <v>7.272213020011122</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" t="s">
+        <v>93</v>
+      </c>
+      <c r="B90">
+        <v>3.741660892052552</v>
+      </c>
+      <c r="C90">
+        <v>23.09409797460791</v>
+      </c>
+      <c r="D90">
+        <v>22.31985174587813</v>
+      </c>
+      <c r="E90">
+        <v>6.871742304036822</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" t="s">
+        <v>94</v>
+      </c>
+      <c r="B91">
+        <v>3.981572527309215</v>
+      </c>
+      <c r="C91">
+        <v>24.60397034212309</v>
+      </c>
+      <c r="D91">
+        <v>22.48973717711587</v>
+      </c>
+      <c r="E91">
+        <v>7.225674029219084</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" t="s">
+        <v>95</v>
+      </c>
+      <c r="B92">
+        <v>3.669786308356444</v>
+      </c>
+      <c r="C92">
+        <v>23.15126287463177</v>
+      </c>
+      <c r="D92">
+        <v>22.3314499908658</v>
+      </c>
+      <c r="E92">
+        <v>6.405623634331124</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" t="s">
+        <v>96</v>
+      </c>
+      <c r="B93">
+        <v>4.73995182216871</v>
+      </c>
+      <c r="C93">
+        <v>24.1783207683782</v>
+      </c>
+      <c r="D93">
+        <v>22.24602619243903</v>
+      </c>
+      <c r="E93">
+        <v>5.855861982061471</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" t="s">
+        <v>97</v>
+      </c>
+      <c r="B94">
+        <v>4.697365114128981</v>
+      </c>
+      <c r="C94">
+        <v>23.03122682175178</v>
+      </c>
+      <c r="D94">
+        <v>22.36852510367061</v>
+      </c>
+      <c r="E94">
+        <v>6.564273463086951</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" t="s">
+        <v>98</v>
+      </c>
+      <c r="B95">
+        <v>4.650696522589138</v>
+      </c>
+      <c r="C95">
+        <v>23.02061484005776</v>
+      </c>
+      <c r="D95">
+        <v>22.52177730718781</v>
+      </c>
+      <c r="E95">
+        <v>6.14853964001624</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" t="s">
+        <v>99</v>
+      </c>
+      <c r="B96">
+        <v>3.311465711886054</v>
+      </c>
+      <c r="C96">
+        <v>23.96766169924933</v>
+      </c>
+      <c r="D96">
+        <v>22.21192226468796</v>
+      </c>
+      <c r="E96">
+        <v>6.371372808217133</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" t="s">
+        <v>100</v>
+      </c>
+      <c r="B97">
+        <v>3.891335744750759</v>
+      </c>
+      <c r="C97">
+        <v>24.33079303378701</v>
+      </c>
+      <c r="D97">
+        <v>22.41921560554027</v>
+      </c>
+      <c r="E97">
+        <v>6.483388941291347</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" t="s">
+        <v>101</v>
+      </c>
+      <c r="B98">
+        <v>3.287125730797768</v>
+      </c>
+      <c r="C98">
+        <v>24.26274921404852</v>
+      </c>
+      <c r="D98">
+        <v>22.09799543797209</v>
+      </c>
+      <c r="E98">
+        <v>7.175023444361512</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" t="s">
+        <v>102</v>
+      </c>
+      <c r="B99">
+        <v>3.389428691331712</v>
+      </c>
+      <c r="C99">
+        <v>24.33511577792539</v>
+      </c>
+      <c r="D99">
+        <v>22.42305389450829</v>
+      </c>
+      <c r="E99">
+        <v>6.690984766736893</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" t="s">
+        <v>103</v>
+      </c>
+      <c r="B100">
+        <v>4.228437151248781</v>
+      </c>
+      <c r="C100">
+        <v>23.18022113442091</v>
+      </c>
+      <c r="D100">
+        <v>22.28343357819457</v>
+      </c>
+      <c r="E100">
+        <v>6.641487013643598</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" t="s">
+        <v>104</v>
+      </c>
+      <c r="B101">
+        <v>4.196118007311299</v>
+      </c>
+      <c r="C101">
+        <v>24.12963730394532</v>
+      </c>
+      <c r="D101">
+        <v>22.2495118981008</v>
+      </c>
+      <c r="E101">
+        <v>7.384267861174644</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" t="s">
+        <v>105</v>
+      </c>
+      <c r="B102">
+        <v>3.598778750622449</v>
+      </c>
+      <c r="C102">
+        <v>23.44456411924635</v>
+      </c>
+      <c r="D102">
+        <v>22.11008738036448</v>
+      </c>
+      <c r="E102">
+        <v>7.058769237074244</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" t="s">
+        <v>106</v>
+      </c>
+      <c r="B103">
+        <v>4.267745404009058</v>
+      </c>
+      <c r="C103">
+        <v>23.15126089956526</v>
+      </c>
+      <c r="D103">
+        <v>22.42584549689982</v>
+      </c>
+      <c r="E103">
+        <v>6.75866676782397</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" t="s">
+        <v>107</v>
+      </c>
+      <c r="B104">
+        <v>3.90033896490817</v>
+      </c>
+      <c r="C104">
+        <v>23.88984035837589</v>
+      </c>
+      <c r="D104">
+        <v>22.37647588558914</v>
+      </c>
+      <c r="E104">
+        <v>6.194591124078285</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" t="s">
+        <v>108</v>
+      </c>
+      <c r="B105">
+        <v>4.532038247758644</v>
+      </c>
+      <c r="C105">
+        <v>23.30651513396478</v>
+      </c>
+      <c r="D105">
+        <v>22.16213460926763</v>
+      </c>
+      <c r="E105">
+        <v>5.907482126313923</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" t="s">
+        <v>109</v>
+      </c>
+      <c r="B106">
+        <v>3.725316301235879</v>
+      </c>
+      <c r="C106">
+        <v>23.59740161344593</v>
+      </c>
+      <c r="D106">
+        <v>22.51460687488497</v>
+      </c>
+      <c r="E106">
+        <v>6.450701348553107</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" t="s">
+        <v>110</v>
+      </c>
+      <c r="B107">
+        <v>3.436239249984642</v>
+      </c>
+      <c r="C107">
+        <v>23.53692646097545</v>
+      </c>
+      <c r="D107">
+        <v>22.45865466855257</v>
+      </c>
+      <c r="E107">
+        <v>6.586941167306009</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" t="s">
+        <v>111</v>
+      </c>
+      <c r="B108">
+        <v>3.292784922057378</v>
+      </c>
+      <c r="C108">
+        <v>23.30404741798739</v>
+      </c>
+      <c r="D108">
+        <v>22.53499509251692</v>
+      </c>
+      <c r="E108">
+        <v>6.185824986569746</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" t="s">
+        <v>112</v>
+      </c>
+      <c r="B109">
+        <v>3.261213769286174</v>
+      </c>
+      <c r="C109">
+        <v>23.17756036616867</v>
+      </c>
+      <c r="D109">
+        <v>22.16451485710722</v>
+      </c>
+      <c r="E109">
+        <v>6.40595391445279</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" t="s">
+        <v>113</v>
+      </c>
+      <c r="B110">
+        <v>4.436282776285319</v>
+      </c>
+      <c r="C110">
+        <v>24.27658562794789</v>
+      </c>
+      <c r="D110">
+        <v>22.10415169059317</v>
+      </c>
+      <c r="E110">
+        <v>5.900143421436911</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" t="s">
+        <v>114</v>
+      </c>
+      <c r="B111">
+        <v>4.473421806083631</v>
+      </c>
+      <c r="C111">
+        <v>24.53657335913989</v>
+      </c>
+      <c r="D111">
+        <v>22.23185660932747</v>
+      </c>
+      <c r="E111">
+        <v>6.739450622599175</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" t="s">
+        <v>115</v>
+      </c>
+      <c r="B112">
+        <v>4.25889380509336</v>
+      </c>
+      <c r="C112">
+        <v>24.10470484203698</v>
+      </c>
+      <c r="D112">
+        <v>22.21079017932838</v>
+      </c>
+      <c r="E112">
+        <v>6.457320015407744</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" t="s">
+        <v>116</v>
+      </c>
+      <c r="B113">
+        <v>3.83478496028847</v>
+      </c>
+      <c r="C113">
+        <v>24.27722832149465</v>
+      </c>
+      <c r="D113">
+        <v>22.32053986619856</v>
+      </c>
+      <c r="E113">
+        <v>6.001822702628609</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" t="s">
+        <v>117</v>
+      </c>
+      <c r="B114">
+        <v>4.535819105056272</v>
+      </c>
+      <c r="C114">
+        <v>23.62498021878592</v>
+      </c>
+      <c r="D114">
+        <v>22.4660072275705</v>
+      </c>
+      <c r="E114">
+        <v>6.648623461026879</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" t="s">
+        <v>118</v>
+      </c>
+      <c r="B115">
+        <v>4.474171746426778</v>
+      </c>
+      <c r="C115">
+        <v>23.19792207356172</v>
+      </c>
+      <c r="D115">
+        <v>22.15833072767166</v>
+      </c>
+      <c r="E115">
+        <v>6.891088529848497</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" t="s">
+        <v>119</v>
+      </c>
+      <c r="B116">
+        <v>3.790667591914751</v>
+      </c>
+      <c r="C116">
+        <v>23.77366605173301</v>
+      </c>
+      <c r="D116">
+        <v>22.51258317513687</v>
+      </c>
+      <c r="E116">
+        <v>6.623549264322209</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" t="s">
+        <v>120</v>
+      </c>
+      <c r="B117">
+        <v>3.571722008657339</v>
+      </c>
+      <c r="C117">
+        <v>24.61388225016708</v>
+      </c>
+      <c r="D117">
+        <v>22.47110576953441</v>
+      </c>
+      <c r="E117">
+        <v>5.893495900895561</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" t="s">
+        <v>121</v>
+      </c>
+      <c r="B118">
+        <v>4.300035928219137</v>
+      </c>
+      <c r="C118">
+        <v>24.29534431629209</v>
+      </c>
+      <c r="D118">
+        <v>22.20664749594107</v>
+      </c>
+      <c r="E118">
+        <v>6.607607093342246</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" t="s">
+        <v>122</v>
+      </c>
+      <c r="B119">
+        <v>3.473459427873948</v>
+      </c>
+      <c r="C119">
+        <v>24.60780519552524</v>
+      </c>
+      <c r="D119">
+        <v>22.13448080656849</v>
+      </c>
+      <c r="E119">
+        <v>7.230674228673893</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" t="s">
+        <v>123</v>
+      </c>
+      <c r="B120">
+        <v>4.489272211448138</v>
+      </c>
+      <c r="C120">
+        <v>23.22261877904942</v>
+      </c>
+      <c r="D120">
+        <v>22.0723111705093</v>
+      </c>
+      <c r="E120">
+        <v>6.273308220410219</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" t="s">
+        <v>124</v>
+      </c>
+      <c r="B121">
+        <v>4.68494927494195</v>
+      </c>
+      <c r="C121">
+        <v>23.59694252897203</v>
+      </c>
+      <c r="D121">
+        <v>22.34581777727729</v>
+      </c>
+      <c r="E121">
+        <v>7.080949653708248</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" t="s">
+        <v>125</v>
+      </c>
+      <c r="B122">
+        <v>3.076808848053165</v>
+      </c>
+      <c r="C122">
+        <v>23.52739454114128</v>
+      </c>
+      <c r="D122">
+        <v>22.18007729298435</v>
+      </c>
+      <c r="E122">
+        <v>5.895478819829314</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" t="s">
+        <v>126</v>
+      </c>
+      <c r="B123">
+        <v>4.116492849881802</v>
+      </c>
+      <c r="C123">
+        <v>23.32241401682748</v>
+      </c>
+      <c r="D123">
+        <v>22.50475038562728</v>
+      </c>
+      <c r="E123">
+        <v>6.360192162108575</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" t="s">
+        <v>127</v>
+      </c>
+      <c r="B124">
+        <v>3.857423049725385</v>
+      </c>
+      <c r="C124">
+        <v>23.87225423464977</v>
+      </c>
+      <c r="D124">
+        <v>22.38805805182392</v>
+      </c>
+      <c r="E124">
+        <v>6.079463929182874</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" t="s">
+        <v>128</v>
+      </c>
+      <c r="B125">
+        <v>4.6644452337347</v>
+      </c>
+      <c r="C125">
+        <v>23.55877132854017</v>
+      </c>
+      <c r="D125">
+        <v>22.15529446712052</v>
+      </c>
+      <c r="E125">
+        <v>6.790221158266363</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" t="s">
+        <v>129</v>
+      </c>
+      <c r="B126">
+        <v>3.026461265784518</v>
+      </c>
+      <c r="C126">
+        <v>24.58197110843553</v>
+      </c>
+      <c r="D126">
+        <v>22.14618872931766</v>
+      </c>
+      <c r="E126">
+        <v>7.252645486909048</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" t="s">
+        <v>130</v>
+      </c>
+      <c r="B127">
+        <v>3.547116754278294</v>
+      </c>
+      <c r="C127">
+        <v>24.58492583754007</v>
+      </c>
+      <c r="D127">
+        <v>22.15024068106232</v>
+      </c>
+      <c r="E127">
+        <v>6.004724192933878</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128" t="s">
+        <v>131</v>
+      </c>
+      <c r="B128">
+        <v>3.311777518663423</v>
+      </c>
+      <c r="C128">
+        <v>24.43101114522127</v>
+      </c>
+      <c r="D128">
+        <v>22.29921420060684</v>
+      </c>
+      <c r="E128">
+        <v>7.375004876986092</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129" t="s">
+        <v>132</v>
+      </c>
+      <c r="B129">
+        <v>3.371625927664508</v>
+      </c>
+      <c r="C129">
+        <v>23.95679355168051</v>
+      </c>
+      <c r="D129">
+        <v>22.16725032092899</v>
+      </c>
+      <c r="E129">
+        <v>6.515265549129269</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" t="s">
+        <v>133</v>
+      </c>
+      <c r="B130">
+        <v>3.314762665729685</v>
+      </c>
+      <c r="C130">
+        <v>23.79766405197084</v>
+      </c>
+      <c r="D130">
+        <v>22.33631536813169</v>
+      </c>
+      <c r="E130">
+        <v>6.782154842811714</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" t="s">
+        <v>134</v>
+      </c>
+      <c r="B131">
+        <v>4.489468718787683</v>
+      </c>
+      <c r="C131">
+        <v>23.87122305122065</v>
+      </c>
+      <c r="D131">
+        <v>22.128114789823</v>
+      </c>
+      <c r="E131">
+        <v>7.376613663061942</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132" t="s">
+        <v>135</v>
+      </c>
+      <c r="B132">
+        <v>4.207477973784236</v>
+      </c>
+      <c r="C132">
+        <v>24.24412686544413</v>
+      </c>
+      <c r="D132">
+        <v>22.4770086396921</v>
+      </c>
+      <c r="E132">
+        <v>7.165233996410575</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" t="s">
+        <v>136</v>
+      </c>
+      <c r="B133">
+        <v>3.868404541051228</v>
+      </c>
+      <c r="C133">
+        <v>23.61240675508558</v>
+      </c>
+      <c r="D133">
+        <v>22.50011936294289</v>
+      </c>
+      <c r="E133">
+        <v>6.899639756615514</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" t="s">
+        <v>137</v>
+      </c>
+      <c r="B134">
+        <v>4.113389977803976</v>
+      </c>
+      <c r="C134">
+        <v>23.19691888834114</v>
+      </c>
+      <c r="D134">
+        <v>22.20085411110019</v>
+      </c>
+      <c r="E134">
+        <v>6.562895931024742</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" t="s">
+        <v>138</v>
+      </c>
+      <c r="B135">
+        <v>4.723524998128919</v>
+      </c>
+      <c r="C135">
+        <v>24.34139761129558</v>
+      </c>
+      <c r="D135">
+        <v>22.47996195378967</v>
+      </c>
+      <c r="E135">
+        <v>5.869911255732032</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" t="s">
+        <v>139</v>
+      </c>
+      <c r="B136">
+        <v>3.892168663818386</v>
+      </c>
+      <c r="C136">
+        <v>23.68517727007667</v>
+      </c>
+      <c r="D136">
+        <v>22.06063281591977</v>
+      </c>
+      <c r="E136">
+        <v>5.955183734363333</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" t="s">
+        <v>140</v>
+      </c>
+      <c r="B137">
+        <v>4.735998488654214</v>
+      </c>
+      <c r="C137">
+        <v>24.1173558383786</v>
+      </c>
+      <c r="D137">
+        <v>22.26129392475127</v>
+      </c>
+      <c r="E137">
+        <v>6.065895612993689</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" t="s">
+        <v>141</v>
+      </c>
+      <c r="B138">
+        <v>3.884487721428056</v>
+      </c>
+      <c r="C138">
+        <v>24.59418326561599</v>
+      </c>
+      <c r="D138">
+        <v>22.16582264805286</v>
+      </c>
+      <c r="E138">
+        <v>7.090450974030063</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" t="s">
+        <v>142</v>
+      </c>
+      <c r="B139">
+        <v>4.444252775721847</v>
+      </c>
+      <c r="C139">
+        <v>23.10029758146855</v>
+      </c>
+      <c r="D139">
+        <v>22.43192723200213</v>
+      </c>
+      <c r="E139">
+        <v>5.845504918032761</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" t="s">
+        <v>143</v>
+      </c>
+      <c r="B140">
+        <v>3.815299915667213</v>
+      </c>
+      <c r="C140">
+        <v>10.52702831998528</v>
+      </c>
+      <c r="D140">
+        <v>58.11867938484536</v>
+      </c>
+      <c r="E140">
+        <v>5.527652413069777</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" t="s">
+        <v>144</v>
+      </c>
+      <c r="B141">
+        <v>3.707618029337414</v>
+      </c>
+      <c r="C141">
+        <v>11.53415233777361</v>
+      </c>
+      <c r="D141">
+        <v>58.16203327309057</v>
+      </c>
+      <c r="E141">
+        <v>5.378769478829215</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" t="s">
+        <v>145</v>
+      </c>
+      <c r="B142">
+        <v>3.73388344487589</v>
+      </c>
+      <c r="C142">
+        <v>11.93888038772659</v>
+      </c>
+      <c r="D142">
+        <v>58.33883112650513</v>
+      </c>
+      <c r="E142">
+        <v>5.253928577924537</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" t="s">
+        <v>146</v>
+      </c>
+      <c r="B143">
+        <v>4.794033524600832</v>
+      </c>
+      <c r="C143">
+        <v>11.0507801793602</v>
+      </c>
+      <c r="D143">
+        <v>58.35690083605509</v>
+      </c>
+      <c r="E143">
+        <v>4.467618025323793</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" t="s">
+        <v>147</v>
+      </c>
+      <c r="B144">
+        <v>4.415090194243957</v>
+      </c>
+      <c r="C144">
+        <v>10.69178057283313</v>
+      </c>
+      <c r="D144">
+        <v>57.95302278095252</v>
+      </c>
+      <c r="E144">
+        <v>5.064625021310896</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
+      <c r="A145" t="s">
+        <v>148</v>
+      </c>
+      <c r="B145">
+        <v>4.397111360010806</v>
+      </c>
+      <c r="C145">
+        <v>10.72633392415312</v>
+      </c>
+      <c r="D145">
+        <v>57.9404143658713</v>
+      </c>
+      <c r="E145">
+        <v>4.907575583705779</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
+      <c r="A146" t="s">
+        <v>149</v>
+      </c>
+      <c r="B146">
+        <v>4.295529491938978</v>
+      </c>
+      <c r="C146">
+        <v>10.44974773727008</v>
+      </c>
+      <c r="D146">
+        <v>58.09686133190402</v>
+      </c>
+      <c r="E146">
+        <v>5.523310378557897</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
+      <c r="A147" t="s">
+        <v>150</v>
+      </c>
+      <c r="B147">
+        <v>4.804649225792574</v>
+      </c>
+      <c r="C147">
+        <v>11.60093601565428</v>
+      </c>
+      <c r="D147">
+        <v>58.07206253497338</v>
+      </c>
+      <c r="E147">
+        <v>4.341921083247745</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" t="s">
+        <v>151</v>
+      </c>
+      <c r="B148">
+        <v>3.952720077400519</v>
+      </c>
+      <c r="C148">
+        <v>11.97053649421465</v>
+      </c>
+      <c r="D148">
+        <v>57.96932550492496</v>
+      </c>
+      <c r="E148">
+        <v>4.484519183843837</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" t="s">
+        <v>152</v>
+      </c>
+      <c r="B149">
+        <v>4.704481111429771</v>
+      </c>
+      <c r="C149">
+        <v>11.17845549528116</v>
+      </c>
+      <c r="D149">
+        <v>58.01076121682099</v>
+      </c>
+      <c r="E149">
+        <v>5.301917875421404</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" t="s">
+        <v>153</v>
+      </c>
+      <c r="B150">
+        <v>4.941383282174591</v>
+      </c>
+      <c r="C150">
+        <v>11.97832226962456</v>
+      </c>
+      <c r="D150">
+        <v>58.2777747166657</v>
+      </c>
+      <c r="E150">
+        <v>4.109070938571062</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" t="s">
+        <v>154</v>
+      </c>
+      <c r="B151">
+        <v>4.311914228795456</v>
+      </c>
+      <c r="C151">
+        <v>11.51805043777329</v>
+      </c>
+      <c r="D151">
+        <v>57.8738768730855</v>
+      </c>
+      <c r="E151">
+        <v>5.207294743711063</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" t="s">
+        <v>155</v>
+      </c>
+      <c r="B152">
+        <v>5.192907979731388</v>
+      </c>
+      <c r="C152">
+        <v>11.2583542488395</v>
+      </c>
+      <c r="D152">
+        <v>58.28263675475788</v>
+      </c>
+      <c r="E152">
+        <v>4.826165232681451</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" t="s">
+        <v>156</v>
+      </c>
+      <c r="B153">
+        <v>4.331161704640291</v>
+      </c>
+      <c r="C153">
+        <v>10.47127136832854</v>
+      </c>
+      <c r="D153">
+        <v>57.87656176248175</v>
+      </c>
+      <c r="E153">
+        <v>4.746573103279819</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" t="s">
+        <v>157</v>
+      </c>
+      <c r="B154">
+        <v>4.575651167073865</v>
+      </c>
+      <c r="C154">
+        <v>10.52370769375213</v>
+      </c>
+      <c r="D154">
+        <v>58.16101310472088</v>
+      </c>
+      <c r="E154">
+        <v>5.514570275491305</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" t="s">
+        <v>158</v>
+      </c>
+      <c r="B155">
+        <v>5.094298421603918</v>
+      </c>
+      <c r="C155">
+        <v>11.85311615717603</v>
+      </c>
+      <c r="D155">
+        <v>57.91516886349542</v>
+      </c>
+      <c r="E155">
+        <v>3.969304756717393</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" t="s">
+        <v>159</v>
+      </c>
+      <c r="B156">
+        <v>4.815952560854033</v>
+      </c>
+      <c r="C156">
+        <v>10.61356412697811</v>
+      </c>
+      <c r="D156">
+        <v>58.19120107053238</v>
+      </c>
+      <c r="E156">
+        <v>4.93363941511409</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" t="s">
+        <v>160</v>
+      </c>
+      <c r="B157">
+        <v>4.59310769576026</v>
+      </c>
+      <c r="C157">
+        <v>11.56284328876628</v>
+      </c>
+      <c r="D157">
+        <v>57.88502925092892</v>
+      </c>
+      <c r="E157">
+        <v>5.438076840032263</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" t="s">
+        <v>161</v>
+      </c>
+      <c r="B158">
+        <v>4.135799268901335</v>
+      </c>
+      <c r="C158">
+        <v>10.47422383598606</v>
+      </c>
+      <c r="D158">
+        <v>58.13947964616288</v>
+      </c>
+      <c r="E158">
+        <v>4.193678710167687</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" t="s">
+        <v>162</v>
+      </c>
+      <c r="B159">
+        <v>4.175054067885314</v>
+      </c>
+      <c r="C159">
+        <v>10.80444671541383</v>
+      </c>
+      <c r="D159">
+        <v>58.28386607978612</v>
+      </c>
+      <c r="E159">
+        <v>4.207174706922912</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" t="s">
+        <v>163</v>
+      </c>
+      <c r="B160">
+        <v>5.087742308640857</v>
+      </c>
+      <c r="C160">
+        <v>11.12604905989355</v>
+      </c>
+      <c r="D160">
+        <v>58.16754581429872</v>
+      </c>
+      <c r="E160">
+        <v>5.243672895511232</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161" t="s">
+        <v>164</v>
+      </c>
+      <c r="B161">
+        <v>4.251450219619333</v>
+      </c>
+      <c r="C161">
+        <v>11.85479871292777</v>
+      </c>
+      <c r="D161">
+        <v>58.25254824153814</v>
+      </c>
+      <c r="E161">
+        <v>4.713048211587251</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162" t="s">
+        <v>165</v>
+      </c>
+      <c r="B162">
+        <v>4.743761935363501</v>
+      </c>
+      <c r="C162">
+        <v>10.70699679214975</v>
+      </c>
+      <c r="D162">
+        <v>57.98416398740632</v>
+      </c>
+      <c r="E162">
+        <v>4.119991975634629</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" t="s">
+        <v>166</v>
+      </c>
+      <c r="B163">
+        <v>4.503050810623442</v>
+      </c>
+      <c r="C163">
+        <v>11.55805289849107</v>
+      </c>
+      <c r="D163">
+        <v>57.96404411725785</v>
+      </c>
+      <c r="E163">
+        <v>5.498839006417653</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164" t="s">
+        <v>167</v>
+      </c>
+      <c r="B164">
+        <v>4.661219023036178</v>
+      </c>
+      <c r="C164">
+        <v>11.30602746116154</v>
+      </c>
+      <c r="D164">
+        <v>58.22509389240942</v>
+      </c>
+      <c r="E164">
+        <v>5.156258657234256</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" t="s">
+        <v>168</v>
+      </c>
+      <c r="B165">
+        <v>4.064461428691275</v>
+      </c>
+      <c r="C165">
+        <v>11.75102131421965</v>
+      </c>
+      <c r="D165">
+        <v>58.18595999358797</v>
+      </c>
+      <c r="E165">
+        <v>4.59845141633137</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" t="s">
+        <v>169</v>
+      </c>
+      <c r="B166">
+        <v>4.685496788276565</v>
+      </c>
+      <c r="C166">
+        <v>10.84810990115909</v>
+      </c>
+      <c r="D166">
+        <v>58.2677354614009</v>
+      </c>
+      <c r="E166">
+        <v>4.314681578368798</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" t="s">
+        <v>170</v>
+      </c>
+      <c r="B167">
+        <v>4.325792964844818</v>
+      </c>
+      <c r="C167">
+        <v>11.94338734109863</v>
+      </c>
+      <c r="D167">
+        <v>58.1501610816216</v>
+      </c>
+      <c r="E167">
+        <v>5.353933430646886</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" t="s">
+        <v>171</v>
+      </c>
+      <c r="B168">
+        <v>5.123217358186366</v>
+      </c>
+      <c r="C168">
+        <v>11.62298949921636</v>
+      </c>
+      <c r="D168">
+        <v>58.12885990645893</v>
+      </c>
+      <c r="E168">
+        <v>5.231758858111885</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" t="s">
+        <v>172</v>
+      </c>
+      <c r="B169">
+        <v>5.375011922233893</v>
+      </c>
+      <c r="C169">
+        <v>11.58589530127978</v>
+      </c>
+      <c r="D169">
+        <v>57.90656282160673</v>
+      </c>
+      <c r="E169">
+        <v>5.33164389578821</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" t="s">
+        <v>173</v>
+      </c>
+      <c r="B170">
+        <v>4.413848142948467</v>
+      </c>
+      <c r="C170">
+        <v>11.31593856678969</v>
+      </c>
+      <c r="D170">
+        <v>57.9040991803442</v>
+      </c>
+      <c r="E170">
+        <v>4.513489510565317</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" t="s">
+        <v>174</v>
+      </c>
+      <c r="B171">
+        <v>5.107784218926265</v>
+      </c>
+      <c r="C171">
+        <v>11.12654802226494</v>
+      </c>
+      <c r="D171">
+        <v>58.26260822318849</v>
+      </c>
+      <c r="E171">
+        <v>5.511869319544438</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" t="s">
+        <v>175</v>
+      </c>
+      <c r="B172">
+        <v>4.511463287790414</v>
+      </c>
+      <c r="C172">
+        <v>11.37991851368749</v>
+      </c>
+      <c r="D172">
+        <v>58.14158410686092</v>
+      </c>
+      <c r="E172">
+        <v>5.087645030874725</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" t="s">
+        <v>176</v>
+      </c>
+      <c r="B173">
+        <v>3.916138816387428</v>
+      </c>
+      <c r="C173">
+        <v>10.8696213471505</v>
+      </c>
+      <c r="D173">
+        <v>58.26700239821506</v>
+      </c>
+      <c r="E173">
+        <v>4.496805148627925</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" t="s">
+        <v>177</v>
+      </c>
+      <c r="B174">
+        <v>4.977972201626691</v>
+      </c>
+      <c r="C174">
+        <v>10.84213946514946</v>
+      </c>
+      <c r="D174">
+        <v>58.22509487885686</v>
+      </c>
+      <c r="E174">
+        <v>4.985786282171635</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" t="s">
+        <v>178</v>
+      </c>
+      <c r="B175">
+        <v>4.464327954890958</v>
+      </c>
+      <c r="C175">
+        <v>11.57947648390842</v>
+      </c>
+      <c r="D175">
+        <v>58.12757722893608</v>
+      </c>
+      <c r="E175">
+        <v>4.652103471370348</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" t="s">
+        <v>179</v>
+      </c>
+      <c r="B176">
+        <v>4.774881927872182</v>
+      </c>
+      <c r="C176">
+        <v>11.42169747613482</v>
+      </c>
+      <c r="D176">
+        <v>58.00231700940452</v>
+      </c>
+      <c r="E176">
+        <v>5.024789944236319</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" t="s">
+        <v>180</v>
+      </c>
+      <c r="B177">
+        <v>4.218422822348662</v>
+      </c>
+      <c r="C177">
+        <v>12.02068625196092</v>
+      </c>
+      <c r="D177">
+        <v>57.94775568715082</v>
+      </c>
+      <c r="E177">
+        <v>4.170083660163352</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" t="s">
+        <v>181</v>
+      </c>
+      <c r="B178">
+        <v>3.97256630504839</v>
+      </c>
+      <c r="C178">
+        <v>10.94373524848427</v>
+      </c>
+      <c r="D178">
+        <v>58.06804465669358</v>
+      </c>
+      <c r="E178">
+        <v>4.437452033777749</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" t="s">
+        <v>182</v>
+      </c>
+      <c r="B179">
+        <v>3.662192713572371</v>
+      </c>
+      <c r="C179">
+        <v>10.73356400418518</v>
+      </c>
+      <c r="D179">
+        <v>58.27607920415637</v>
+      </c>
+      <c r="E179">
+        <v>4.493694279527765</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" t="s">
+        <v>183</v>
+      </c>
+      <c r="B180">
+        <v>3.989025162270262</v>
+      </c>
+      <c r="C180">
+        <v>12.03260753281214</v>
+      </c>
+      <c r="D180">
+        <v>58.05778467048648</v>
+      </c>
+      <c r="E180">
+        <v>5.155470934897435</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" t="s">
+        <v>184</v>
+      </c>
+      <c r="B181">
+        <v>4.167411595218544</v>
+      </c>
+      <c r="C181">
+        <v>11.73264716869</v>
+      </c>
+      <c r="D181">
+        <v>58.29667406737926</v>
+      </c>
+      <c r="E181">
+        <v>5.246582536314231</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" t="s">
+        <v>185</v>
+      </c>
+      <c r="B182">
+        <v>4.943108071422698</v>
+      </c>
+      <c r="C182">
+        <v>10.50220031868463</v>
+      </c>
+      <c r="D182">
+        <v>58.20010430862562</v>
+      </c>
+      <c r="E182">
+        <v>4.321929998808208</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" t="s">
+        <v>186</v>
+      </c>
+      <c r="B183">
+        <v>4.95379354689231</v>
+      </c>
+      <c r="C183">
+        <v>11.82820001216314</v>
+      </c>
+      <c r="D183">
+        <v>58.03708823250565</v>
+      </c>
+      <c r="E183">
+        <v>4.630047778769034</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184" t="s">
+        <v>187</v>
+      </c>
+      <c r="B184">
+        <v>4.298236559200835</v>
+      </c>
+      <c r="C184">
+        <v>10.65915398295772</v>
+      </c>
+      <c r="D184">
+        <v>57.94011673976323</v>
+      </c>
+      <c r="E184">
+        <v>4.073698975592784</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" t="s">
+        <v>188</v>
+      </c>
+      <c r="B185">
+        <v>4.250379554172611</v>
+      </c>
+      <c r="C185">
+        <v>10.51051766201274</v>
+      </c>
+      <c r="D185">
+        <v>58.15448175397982</v>
+      </c>
+      <c r="E185">
+        <v>5.038136932385457</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186" t="s">
+        <v>189</v>
+      </c>
+      <c r="B186">
+        <v>3.789094848119826</v>
+      </c>
+      <c r="C186">
+        <v>11.24693320204975</v>
+      </c>
+      <c r="D186">
+        <v>58.2701553398857</v>
+      </c>
+      <c r="E186">
+        <v>4.857018977694608</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187" t="s">
+        <v>190</v>
+      </c>
+      <c r="B187">
+        <v>4.78606090989263</v>
+      </c>
+      <c r="C187">
+        <v>11.33603017357279</v>
+      </c>
+      <c r="D187">
+        <v>58.11426909759213</v>
+      </c>
+      <c r="E187">
+        <v>4.585129089368613</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" t="s">
+        <v>191</v>
+      </c>
+      <c r="B188">
+        <v>3.630166488684654</v>
+      </c>
+      <c r="C188">
+        <v>11.96519267147695</v>
+      </c>
+      <c r="D188">
+        <v>57.92522010753181</v>
+      </c>
+      <c r="E188">
+        <v>4.408994831678815</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" t="s">
+        <v>192</v>
+      </c>
+      <c r="B189">
+        <v>4.724048250361102</v>
+      </c>
+      <c r="C189">
+        <v>11.82078385490359</v>
+      </c>
+      <c r="D189">
+        <v>58.34111087254214</v>
+      </c>
+      <c r="E189">
+        <v>4.961728845406984</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" t="s">
+        <v>193</v>
+      </c>
+      <c r="B190">
+        <v>3.711119416223276</v>
+      </c>
+      <c r="C190">
+        <v>11.76796525145208</v>
+      </c>
+      <c r="D190">
+        <v>58.14570041165831</v>
+      </c>
+      <c r="E190">
+        <v>4.139824042033241</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" t="s">
+        <v>194</v>
+      </c>
+      <c r="B191">
+        <v>4.616994609705058</v>
+      </c>
+      <c r="C191">
+        <v>11.62727694571072</v>
+      </c>
+      <c r="D191">
+        <v>58.21855229932787</v>
+      </c>
+      <c r="E191">
+        <v>4.570077797818092</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" t="s">
+        <v>195</v>
+      </c>
+      <c r="B192">
+        <v>4.086190086290542</v>
+      </c>
+      <c r="C192">
+        <v>10.74581246498064</v>
+      </c>
+      <c r="D192">
+        <v>58.19573299360207</v>
+      </c>
+      <c r="E192">
+        <v>4.240323980687292</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" t="s">
+        <v>196</v>
+      </c>
+      <c r="B193">
+        <v>3.778074383078823</v>
+      </c>
+      <c r="C193">
+        <v>11.06729097616003</v>
+      </c>
+      <c r="D193">
+        <v>58.11122099013663</v>
+      </c>
+      <c r="E193">
+        <v>4.12266811238665</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" t="s">
+        <v>197</v>
+      </c>
+      <c r="B194">
+        <v>4.739990933971864</v>
+      </c>
+      <c r="C194">
+        <v>10.54474123176728</v>
+      </c>
+      <c r="D194">
+        <v>57.88563541862897</v>
+      </c>
+      <c r="E194">
+        <v>4.646406108741412</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" t="s">
+        <v>198</v>
+      </c>
+      <c r="B195">
+        <v>4.747586235914038</v>
+      </c>
+      <c r="C195">
+        <v>10.54606897281035</v>
+      </c>
+      <c r="D195">
+        <v>57.89790764649764</v>
+      </c>
+      <c r="E195">
+        <v>4.591851028508266</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" t="s">
+        <v>199</v>
+      </c>
+      <c r="B196">
+        <v>3.998811421411794</v>
+      </c>
+      <c r="C196">
+        <v>10.65340538254843</v>
+      </c>
+      <c r="D196">
+        <v>57.89288900706848</v>
+      </c>
+      <c r="E196">
+        <v>4.216993707637991</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" t="s">
+        <v>200</v>
+      </c>
+      <c r="B197">
+        <v>5.114399382175607</v>
+      </c>
+      <c r="C197">
+        <v>11.28417763309868</v>
+      </c>
+      <c r="D197">
+        <v>58.00077968783313</v>
+      </c>
+      <c r="E197">
+        <v>4.909025965232378</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" t="s">
+        <v>201</v>
+      </c>
+      <c r="B198">
+        <v>5.413784469287366</v>
+      </c>
+      <c r="C198">
+        <v>10.95952389789693</v>
+      </c>
+      <c r="D198">
+        <v>58.3089140011118</v>
+      </c>
+      <c r="E198">
+        <v>4.585140003836924</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" t="s">
+        <v>202</v>
+      </c>
+      <c r="B199">
+        <v>4.684003228941163</v>
+      </c>
+      <c r="C199">
+        <v>10.84393052923461</v>
+      </c>
+      <c r="D199">
+        <v>58.35318102179378</v>
+      </c>
+      <c r="E199">
+        <v>5.462879052609913</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" t="s">
+        <v>203</v>
+      </c>
+      <c r="B200">
+        <v>4.900469911682878</v>
+      </c>
+      <c r="C200">
+        <v>10.92261494224622</v>
+      </c>
+      <c r="D200">
+        <v>57.92849877960999</v>
+      </c>
+      <c r="E200">
+        <v>5.251762390529578</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" t="s">
+        <v>204</v>
+      </c>
+      <c r="B201">
+        <v>4.483194896078555</v>
+      </c>
+      <c r="C201">
+        <v>10.74278458134518</v>
+      </c>
+      <c r="D201">
+        <v>57.93969822365695</v>
+      </c>
+      <c r="E201">
+        <v>4.174463352133113</v>
       </c>
     </row>
   </sheetData>

--- a/FFT on froth/data_dep_augm_Pb.xlsx
+++ b/FFT on froth/data_dep_augm_Pb.xlsx
@@ -1011,16 +1011,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>2.592698573507437</v>
+        <v>2.757381616354195</v>
       </c>
       <c r="C2">
-        <v>11.05923870183131</v>
+        <v>11.34818044350621</v>
       </c>
       <c r="D2">
-        <v>46.35799449797148</v>
+        <v>46.01319356256182</v>
       </c>
       <c r="E2">
-        <v>3.858969251400384</v>
+        <v>5.18740803740175</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1028,16 +1028,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>3.367116014035259</v>
+        <v>2.982826840804259</v>
       </c>
       <c r="C3">
-        <v>11.57426947970576</v>
+        <v>12.00019782358377</v>
       </c>
       <c r="D3">
-        <v>46.03188535751384</v>
+        <v>46.46099704888201</v>
       </c>
       <c r="E3">
-        <v>4.640204503734958</v>
+        <v>5.032699353401074</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1045,16 +1045,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>3.094719855356766</v>
+        <v>4.175151930805751</v>
       </c>
       <c r="C4">
-        <v>11.26243148372452</v>
+        <v>10.92278091496126</v>
       </c>
       <c r="D4">
-        <v>46.21898037955469</v>
+        <v>46.4377439217233</v>
       </c>
       <c r="E4">
-        <v>4.581931053914289</v>
+        <v>4.814194864931221</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1062,16 +1062,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>2.741092691383249</v>
+        <v>2.614217870638722</v>
       </c>
       <c r="C5">
-        <v>11.41019168259806</v>
+        <v>11.47085414969558</v>
       </c>
       <c r="D5">
-        <v>46.22920288398545</v>
+        <v>46.30436970603042</v>
       </c>
       <c r="E5">
-        <v>3.708986323166551</v>
+        <v>4.400222698399634</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1079,16 +1079,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>3.416922591780453</v>
+        <v>3.594237540696479</v>
       </c>
       <c r="C6">
-        <v>10.62565399755671</v>
+        <v>12.00447796216923</v>
       </c>
       <c r="D6">
-        <v>46.2066097972874</v>
+        <v>46.45345316521495</v>
       </c>
       <c r="E6">
-        <v>4.184496129779569</v>
+        <v>4.020930584336943</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1096,16 +1096,16 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>3.197121101822475</v>
+        <v>3.514262304584879</v>
       </c>
       <c r="C7">
-        <v>11.66241553222376</v>
+        <v>11.5811578057191</v>
       </c>
       <c r="D7">
-        <v>46.06386946356611</v>
+        <v>46.48734520750948</v>
       </c>
       <c r="E7">
-        <v>4.473419075065475</v>
+        <v>4.069729670414358</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1113,16 +1113,16 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>4.268195496708804</v>
+        <v>3.301793225687989</v>
       </c>
       <c r="C8">
-        <v>11.39155662048191</v>
+        <v>11.30046174109061</v>
       </c>
       <c r="D8">
-        <v>46.23575220041424</v>
+        <v>46.25297815584412</v>
       </c>
       <c r="E8">
-        <v>4.046763525873202</v>
+        <v>5.037614972785901</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1130,16 +1130,16 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>3.315010633931984</v>
+        <v>2.913102966812922</v>
       </c>
       <c r="C9">
-        <v>11.12949779109028</v>
+        <v>10.97120648772685</v>
       </c>
       <c r="D9">
-        <v>46.40714409363097</v>
+        <v>46.19638723953521</v>
       </c>
       <c r="E9">
-        <v>3.967153519021084</v>
+        <v>4.441609206053489</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1147,16 +1147,16 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>4.158112742181768</v>
+        <v>3.055569568915269</v>
       </c>
       <c r="C10">
-        <v>11.81240710171963</v>
+        <v>11.22374693546434</v>
       </c>
       <c r="D10">
-        <v>46.461972481563</v>
+        <v>46.03498947726427</v>
       </c>
       <c r="E10">
-        <v>4.476263578564923</v>
+        <v>4.10019288601179</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1164,16 +1164,16 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>4.155642399316388</v>
+        <v>2.934249914105143</v>
       </c>
       <c r="C11">
-        <v>12.14773769759149</v>
+        <v>11.01683310061246</v>
       </c>
       <c r="D11">
-        <v>46.13792858241298</v>
+        <v>46.42799142722718</v>
       </c>
       <c r="E11">
-        <v>4.619374970217462</v>
+        <v>4.020586157963145</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1181,16 +1181,16 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>3.666622155506706</v>
+        <v>3.82131105330361</v>
       </c>
       <c r="C12">
-        <v>10.66173690743789</v>
+        <v>10.62220116760111</v>
       </c>
       <c r="D12">
-        <v>46.47004488049367</v>
+        <v>46.26753597185883</v>
       </c>
       <c r="E12">
-        <v>4.297849575826643</v>
+        <v>4.387803451731176</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1198,16 +1198,16 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>3.756626455739708</v>
+        <v>4.028364640768604</v>
       </c>
       <c r="C13">
-        <v>11.99773590140614</v>
+        <v>11.25937041514192</v>
       </c>
       <c r="D13">
-        <v>46.17323382731013</v>
+        <v>46.17317012620253</v>
       </c>
       <c r="E13">
-        <v>4.967009291693021</v>
+        <v>3.935556289970697</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1215,16 +1215,16 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>3.914718448596162</v>
+        <v>2.925272923525985</v>
       </c>
       <c r="C14">
-        <v>11.21381440538855</v>
+        <v>10.60855475057293</v>
       </c>
       <c r="D14">
-        <v>46.25416369083036</v>
+        <v>46.47986194308895</v>
       </c>
       <c r="E14">
-        <v>3.8684970331327</v>
+        <v>4.833983337632436</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1232,16 +1232,16 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>3.428272079597806</v>
+        <v>3.386622972097432</v>
       </c>
       <c r="C15">
-        <v>12.11768069308611</v>
+        <v>11.08099938433673</v>
       </c>
       <c r="D15">
-        <v>46.07982985095677</v>
+        <v>46.47981235461592</v>
       </c>
       <c r="E15">
-        <v>4.079893670579892</v>
+        <v>4.967372258052427</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1249,16 +1249,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>4.191664595472147</v>
+        <v>3.676922642281911</v>
       </c>
       <c r="C16">
-        <v>12.09329126355431</v>
+        <v>11.03203985931743</v>
       </c>
       <c r="D16">
-        <v>46.10490999856153</v>
+        <v>46.31840177473769</v>
       </c>
       <c r="E16">
-        <v>4.666855972014259</v>
+        <v>4.122027897474188</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1266,16 +1266,16 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>4.234658943097203</v>
+        <v>4.054369745072236</v>
       </c>
       <c r="C17">
-        <v>11.94428083716397</v>
+        <v>10.64301082091363</v>
       </c>
       <c r="D17">
-        <v>46.20259485379988</v>
+        <v>46.22337543213364</v>
       </c>
       <c r="E17">
-        <v>4.551522961870388</v>
+        <v>3.886819591150367</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1283,16 +1283,16 @@
         <v>21</v>
       </c>
       <c r="B18">
-        <v>2.787732421518615</v>
+        <v>2.788202603885348</v>
       </c>
       <c r="C18">
-        <v>11.66927889059096</v>
+        <v>10.72234045716999</v>
       </c>
       <c r="D18">
-        <v>46.12089687847315</v>
+        <v>46.3562172565642</v>
       </c>
       <c r="E18">
-        <v>5.020240596683117</v>
+        <v>4.074629615270285</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1300,16 +1300,16 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>4.114541748131536</v>
+        <v>3.330924439716487</v>
       </c>
       <c r="C19">
-        <v>11.65780355714616</v>
+        <v>11.63895545119737</v>
       </c>
       <c r="D19">
-        <v>46.04436249133353</v>
+        <v>46.135627845131</v>
       </c>
       <c r="E19">
-        <v>4.282470103913346</v>
+        <v>3.657212424325628</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1317,16 +1317,16 @@
         <v>23</v>
       </c>
       <c r="B20">
-        <v>2.716123015905106</v>
+        <v>3.672371732657828</v>
       </c>
       <c r="C20">
-        <v>11.83580600734514</v>
+        <v>11.57244495757037</v>
       </c>
       <c r="D20">
-        <v>46.31785435773973</v>
+        <v>46.345918402164</v>
       </c>
       <c r="E20">
-        <v>3.722762310455626</v>
+        <v>4.208668964392125</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1334,16 +1334,16 @@
         <v>24</v>
       </c>
       <c r="B21">
-        <v>2.881744841673688</v>
+        <v>4.237659598023563</v>
       </c>
       <c r="C21">
-        <v>12.06040823787726</v>
+        <v>11.72224111786595</v>
       </c>
       <c r="D21">
-        <v>46.39893128133419</v>
+        <v>46.26680354789194</v>
       </c>
       <c r="E21">
-        <v>4.790314626767479</v>
+        <v>4.138968455281173</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1351,16 +1351,16 @@
         <v>25</v>
       </c>
       <c r="B22">
-        <v>3.193705657676086</v>
+        <v>2.571204215697343</v>
       </c>
       <c r="C22">
-        <v>10.94768252592088</v>
+        <v>10.74314123243207</v>
       </c>
       <c r="D22">
-        <v>46.0185791648141</v>
+        <v>46.48266356155609</v>
       </c>
       <c r="E22">
-        <v>5.146938686696585</v>
+        <v>5.105298746463955</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1368,16 +1368,16 @@
         <v>26</v>
       </c>
       <c r="B23">
-        <v>3.095040738973983</v>
+        <v>3.180448319991008</v>
       </c>
       <c r="C23">
-        <v>11.09648541553623</v>
+        <v>10.69938455137191</v>
       </c>
       <c r="D23">
-        <v>46.431163205678</v>
+        <v>46.27436411873408</v>
       </c>
       <c r="E23">
-        <v>3.946684164790486</v>
+        <v>4.754224334668828</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1385,16 +1385,16 @@
         <v>27</v>
       </c>
       <c r="B24">
-        <v>3.933795718861304</v>
+        <v>3.43807892019269</v>
       </c>
       <c r="C24">
-        <v>10.9654734835479</v>
+        <v>11.37389428721096</v>
       </c>
       <c r="D24">
-        <v>46.1586750144742</v>
+        <v>46.31685594305563</v>
       </c>
       <c r="E24">
-        <v>4.033460663229741</v>
+        <v>3.894551502699747</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1402,16 +1402,16 @@
         <v>28</v>
       </c>
       <c r="B25">
-        <v>3.538113196008861</v>
+        <v>2.93627331882577</v>
       </c>
       <c r="C25">
-        <v>11.42261396079351</v>
+        <v>11.52478946848889</v>
       </c>
       <c r="D25">
-        <v>46.36969128797122</v>
+        <v>46.40562211201954</v>
       </c>
       <c r="E25">
-        <v>4.220635412646967</v>
+        <v>4.878272815983753</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1419,16 +1419,16 @@
         <v>29</v>
       </c>
       <c r="B26">
-        <v>3.832810990834187</v>
+        <v>4.090800738133553</v>
       </c>
       <c r="C26">
-        <v>11.88398476713655</v>
+        <v>12.10005023291877</v>
       </c>
       <c r="D26">
-        <v>46.02860076958173</v>
+        <v>46.34996229383756</v>
       </c>
       <c r="E26">
-        <v>3.926174798128974</v>
+        <v>3.841276832760108</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1436,16 +1436,16 @@
         <v>30</v>
       </c>
       <c r="B27">
-        <v>3.410716527592298</v>
+        <v>3.592907172664678</v>
       </c>
       <c r="C27">
-        <v>10.95655873701188</v>
+        <v>10.86967680294519</v>
       </c>
       <c r="D27">
-        <v>46.06012146672988</v>
+        <v>46.20269641780515</v>
       </c>
       <c r="E27">
-        <v>5.124620938409272</v>
+        <v>4.008180249474557</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1453,16 +1453,16 @@
         <v>31</v>
       </c>
       <c r="B28">
-        <v>3.797463664373693</v>
+        <v>3.084143749116077</v>
       </c>
       <c r="C28">
-        <v>10.75656059499682</v>
+        <v>12.05066345790545</v>
       </c>
       <c r="D28">
-        <v>46.41447321443887</v>
+        <v>46.29979798317702</v>
       </c>
       <c r="E28">
-        <v>4.291195620682204</v>
+        <v>3.879494773992772</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1470,16 +1470,16 @@
         <v>32</v>
       </c>
       <c r="B29">
-        <v>2.543381798356851</v>
+        <v>2.822130497059981</v>
       </c>
       <c r="C29">
-        <v>11.24438423843446</v>
+        <v>11.86452609624654</v>
       </c>
       <c r="D29">
-        <v>46.07621014547986</v>
+        <v>46.31757453524999</v>
       </c>
       <c r="E29">
-        <v>5.056000712594136</v>
+        <v>4.421262529697543</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1487,16 +1487,16 @@
         <v>33</v>
       </c>
       <c r="B30">
-        <v>3.634050135703158</v>
+        <v>2.71574199200735</v>
       </c>
       <c r="C30">
-        <v>12.05037579339043</v>
+        <v>10.82364162658937</v>
       </c>
       <c r="D30">
-        <v>46.02992124664228</v>
+        <v>46.38545331514937</v>
       </c>
       <c r="E30">
-        <v>5.078874462479693</v>
+        <v>4.6250926972904</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1504,16 +1504,16 @@
         <v>34</v>
       </c>
       <c r="B31">
-        <v>3.301667540055715</v>
+        <v>2.82600409831989</v>
       </c>
       <c r="C31">
-        <v>11.40808510011583</v>
+        <v>11.10571566910315</v>
       </c>
       <c r="D31">
-        <v>46.18741399901288</v>
+        <v>46.10741298144301</v>
       </c>
       <c r="E31">
-        <v>4.507326397186617</v>
+        <v>5.009497042214591</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1521,16 +1521,16 @@
         <v>35</v>
       </c>
       <c r="B32">
-        <v>2.621098977109415</v>
+        <v>4.196300381966299</v>
       </c>
       <c r="C32">
-        <v>10.91458215970433</v>
+        <v>10.97210754680191</v>
       </c>
       <c r="D32">
-        <v>46.21659060704211</v>
+        <v>46.04024453239744</v>
       </c>
       <c r="E32">
-        <v>4.877018232143378</v>
+        <v>3.904850641696084</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1538,16 +1538,16 @@
         <v>36</v>
       </c>
       <c r="B33">
-        <v>2.705871952325335</v>
+        <v>3.60857846457635</v>
       </c>
       <c r="C33">
-        <v>11.87380428071107</v>
+        <v>11.13883692243338</v>
       </c>
       <c r="D33">
-        <v>45.99337335691192</v>
+        <v>46.16769150555169</v>
       </c>
       <c r="E33">
-        <v>4.03408400742885</v>
+        <v>3.705416532275292</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1555,16 +1555,16 @@
         <v>37</v>
       </c>
       <c r="B34">
-        <v>2.839997752409716</v>
+        <v>2.540958454180367</v>
       </c>
       <c r="C34">
-        <v>12.08660538563952</v>
+        <v>11.80567081369132</v>
       </c>
       <c r="D34">
-        <v>46.39851339178372</v>
+        <v>46.41189478621228</v>
       </c>
       <c r="E34">
-        <v>4.23541138629222</v>
+        <v>3.784222445929775</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1572,16 +1572,16 @@
         <v>38</v>
       </c>
       <c r="B35">
-        <v>4.097138674412497</v>
+        <v>3.308018927010258</v>
       </c>
       <c r="C35">
-        <v>10.68587015694093</v>
+        <v>11.93298261833351</v>
       </c>
       <c r="D35">
-        <v>46.12785399178848</v>
+        <v>46.29611384839371</v>
       </c>
       <c r="E35">
-        <v>4.170620399312092</v>
+        <v>4.629899070186363</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1589,16 +1589,16 @@
         <v>39</v>
       </c>
       <c r="B36">
-        <v>2.849125014365681</v>
+        <v>4.25596689462573</v>
       </c>
       <c r="C36">
-        <v>11.13375920747506</v>
+        <v>11.12689285584495</v>
       </c>
       <c r="D36">
-        <v>46.43949385055539</v>
+        <v>46.19613759880554</v>
       </c>
       <c r="E36">
-        <v>4.319547990683203</v>
+        <v>4.55940537409735</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1606,16 +1606,16 @@
         <v>40</v>
       </c>
       <c r="B37">
-        <v>3.119832016051373</v>
+        <v>2.619384236476705</v>
       </c>
       <c r="C37">
-        <v>11.79896471043419</v>
+        <v>10.99748544667396</v>
       </c>
       <c r="D37">
-        <v>46.30204625223075</v>
+        <v>46.32580631836573</v>
       </c>
       <c r="E37">
-        <v>4.690015342600688</v>
+        <v>4.571833702483235</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1623,16 +1623,16 @@
         <v>41</v>
       </c>
       <c r="B38">
-        <v>3.802153920489048</v>
+        <v>3.480484518774445</v>
       </c>
       <c r="C38">
-        <v>12.07680517545809</v>
+        <v>10.9879717371019</v>
       </c>
       <c r="D38">
-        <v>46.46204610628803</v>
+        <v>46.16110004527254</v>
       </c>
       <c r="E38">
-        <v>4.450906795762883</v>
+        <v>3.97699589294626</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1640,16 +1640,16 @@
         <v>42</v>
       </c>
       <c r="B39">
-        <v>3.400762859362339</v>
+        <v>3.356870769909786</v>
       </c>
       <c r="C39">
-        <v>11.58983785982779</v>
+        <v>11.40022919936526</v>
       </c>
       <c r="D39">
-        <v>46.25506299709609</v>
+        <v>46.07143551782704</v>
       </c>
       <c r="E39">
-        <v>4.44680516837233</v>
+        <v>5.211847660342093</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1657,16 +1657,16 @@
         <v>43</v>
       </c>
       <c r="B40">
-        <v>2.80411785148322</v>
+        <v>3.78413977753584</v>
       </c>
       <c r="C40">
-        <v>11.43702043149429</v>
+        <v>11.7797687161634</v>
       </c>
       <c r="D40">
-        <v>46.40731534756513</v>
+        <v>46.03393621453882</v>
       </c>
       <c r="E40">
-        <v>4.275419191041058</v>
+        <v>4.938367739941548</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1674,16 +1674,16 @@
         <v>44</v>
       </c>
       <c r="B41">
-        <v>4.113643579944989</v>
+        <v>4.307380152417686</v>
       </c>
       <c r="C41">
-        <v>11.1992120067787</v>
+        <v>10.88997015310732</v>
       </c>
       <c r="D41">
-        <v>46.47424625972825</v>
+        <v>46.417299515616</v>
       </c>
       <c r="E41">
-        <v>4.355272927963736</v>
+        <v>4.901354179015323</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1691,16 +1691,16 @@
         <v>45</v>
       </c>
       <c r="B42">
-        <v>4.186935996046884</v>
+        <v>4.258911390269409</v>
       </c>
       <c r="C42">
-        <v>11.1293757483571</v>
+        <v>10.94480328129828</v>
       </c>
       <c r="D42">
-        <v>46.44924265590506</v>
+        <v>46.31304271970593</v>
       </c>
       <c r="E42">
-        <v>4.277457760340726</v>
+        <v>4.900265632051599</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1708,16 +1708,16 @@
         <v>46</v>
       </c>
       <c r="B43">
-        <v>2.87761426974912</v>
+        <v>4.169073379586525</v>
       </c>
       <c r="C43">
-        <v>12.04545467676927</v>
+        <v>11.45355002372524</v>
       </c>
       <c r="D43">
-        <v>46.37568715541753</v>
+        <v>46.33312792289466</v>
       </c>
       <c r="E43">
-        <v>4.239831410630667</v>
+        <v>4.25633760881104</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1725,16 +1725,16 @@
         <v>47</v>
       </c>
       <c r="B44">
-        <v>3.752528079876015</v>
+        <v>4.130246429696141</v>
       </c>
       <c r="C44">
-        <v>11.88476249633435</v>
+        <v>11.15358813216524</v>
       </c>
       <c r="D44">
-        <v>46.23775798936099</v>
+        <v>46.17452669738267</v>
       </c>
       <c r="E44">
-        <v>3.772794224093606</v>
+        <v>5.056288935009409</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1742,16 +1742,16 @@
         <v>48</v>
       </c>
       <c r="B45">
-        <v>4.06872284054792</v>
+        <v>4.150630296407892</v>
       </c>
       <c r="C45">
-        <v>11.13315584312171</v>
+        <v>11.67556314862849</v>
       </c>
       <c r="D45">
-        <v>46.40389177038348</v>
+        <v>46.12504703567567</v>
       </c>
       <c r="E45">
-        <v>4.154441637746042</v>
+        <v>3.721452614608772</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1759,16 +1759,16 @@
         <v>49</v>
       </c>
       <c r="B46">
-        <v>3.62087709840288</v>
+        <v>3.969120452955463</v>
       </c>
       <c r="C46">
-        <v>11.91782263541489</v>
+        <v>11.53996736703745</v>
       </c>
       <c r="D46">
-        <v>46.23746876479829</v>
+        <v>46.37464958547724</v>
       </c>
       <c r="E46">
-        <v>3.982698632911618</v>
+        <v>4.830514549544301</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1776,16 +1776,16 @@
         <v>50</v>
       </c>
       <c r="B47">
-        <v>2.758473109249307</v>
+        <v>3.235724124300606</v>
       </c>
       <c r="C47">
-        <v>10.64466043099167</v>
+        <v>11.93695248584653</v>
       </c>
       <c r="D47">
-        <v>46.236929731858</v>
+        <v>46.3296690808125</v>
       </c>
       <c r="E47">
-        <v>4.027017083550675</v>
+        <v>4.728842929834507</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1793,16 +1793,16 @@
         <v>51</v>
       </c>
       <c r="B48">
-        <v>2.736279850641532</v>
+        <v>4.059358303617003</v>
       </c>
       <c r="C48">
-        <v>10.95711446167158</v>
+        <v>11.99675704448542</v>
       </c>
       <c r="D48">
-        <v>46.05037498526803</v>
+        <v>46.2199892399174</v>
       </c>
       <c r="E48">
-        <v>4.186914389941607</v>
+        <v>4.062600221915793</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1810,16 +1810,16 @@
         <v>52</v>
       </c>
       <c r="B49">
-        <v>3.893342012962855</v>
+        <v>3.015053506743306</v>
       </c>
       <c r="C49">
-        <v>11.12063030566085</v>
+        <v>12.16860826989706</v>
       </c>
       <c r="D49">
-        <v>46.1489083379501</v>
+        <v>46.27477754208107</v>
       </c>
       <c r="E49">
-        <v>4.354419633910084</v>
+        <v>3.79500023336464</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1827,16 +1827,16 @@
         <v>53</v>
       </c>
       <c r="B50">
-        <v>4.252359381357781</v>
+        <v>3.710844746845255</v>
       </c>
       <c r="C50">
-        <v>10.61376242279276</v>
+        <v>11.08401730648536</v>
       </c>
       <c r="D50">
-        <v>46.1057000894879</v>
+        <v>46.2013018299788</v>
       </c>
       <c r="E50">
-        <v>4.40459905403821</v>
+        <v>4.814702378121113</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1844,16 +1844,16 @@
         <v>54</v>
       </c>
       <c r="B51">
-        <v>4.086152875188926</v>
+        <v>4.041460869075729</v>
       </c>
       <c r="C51">
-        <v>10.73415030132847</v>
+        <v>11.0817904353982</v>
       </c>
       <c r="D51">
-        <v>46.38547364082829</v>
+        <v>46.07031398405795</v>
       </c>
       <c r="E51">
-        <v>3.848010257097002</v>
+        <v>4.594421537848532</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1861,16 +1861,16 @@
         <v>55</v>
       </c>
       <c r="B52">
-        <v>3.969425858976026</v>
+        <v>3.503924007346509</v>
       </c>
       <c r="C52">
-        <v>10.66320911769062</v>
+        <v>11.38333410554071</v>
       </c>
       <c r="D52">
-        <v>46.1214127723951</v>
+        <v>46.43033150370334</v>
       </c>
       <c r="E52">
-        <v>4.367633444970693</v>
+        <v>4.572573876602213</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1878,16 +1878,16 @@
         <v>56</v>
       </c>
       <c r="B53">
-        <v>3.628592024688523</v>
+        <v>3.023417079382898</v>
       </c>
       <c r="C53">
-        <v>11.35419899376532</v>
+        <v>11.12650877579357</v>
       </c>
       <c r="D53">
-        <v>46.44736991716449</v>
+        <v>46.12110736287037</v>
       </c>
       <c r="E53">
-        <v>4.996357218784453</v>
+        <v>3.961541758077681</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1895,16 +1895,16 @@
         <v>57</v>
       </c>
       <c r="B54">
-        <v>2.83778514306829</v>
+        <v>3.575235566742747</v>
       </c>
       <c r="C54">
-        <v>12.10004784013326</v>
+        <v>11.68166660931919</v>
       </c>
       <c r="D54">
-        <v>46.41262625125665</v>
+        <v>46.21621989435784</v>
       </c>
       <c r="E54">
-        <v>3.655847576113219</v>
+        <v>4.787090444763534</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1912,16 +1912,16 @@
         <v>58</v>
       </c>
       <c r="B55">
-        <v>3.605145989369063</v>
+        <v>2.742316611609952</v>
       </c>
       <c r="C55">
-        <v>10.87613852454056</v>
+        <v>11.43948298838299</v>
       </c>
       <c r="D55">
-        <v>46.15590402221442</v>
+        <v>46.23409475894199</v>
       </c>
       <c r="E55">
-        <v>4.989362943154562</v>
+        <v>4.708447367070358</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -1929,16 +1929,16 @@
         <v>59</v>
       </c>
       <c r="B56">
-        <v>3.22273608883096</v>
+        <v>3.794735855572295</v>
       </c>
       <c r="C56">
-        <v>11.77523544527866</v>
+        <v>11.05862539657176</v>
       </c>
       <c r="D56">
-        <v>46.31795686915815</v>
+        <v>46.20595693922869</v>
       </c>
       <c r="E56">
-        <v>4.77439937867784</v>
+        <v>4.038071669623157</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -1946,16 +1946,16 @@
         <v>60</v>
       </c>
       <c r="B57">
-        <v>3.200589948494231</v>
+        <v>2.659353061001493</v>
       </c>
       <c r="C57">
-        <v>12.1350648766846</v>
+        <v>11.60292953944642</v>
       </c>
       <c r="D57">
-        <v>46.15799298899801</v>
+        <v>46.16733119414872</v>
       </c>
       <c r="E57">
-        <v>3.680420730930585</v>
+        <v>4.153015218672889</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1963,16 +1963,16 @@
         <v>61</v>
       </c>
       <c r="B58">
-        <v>3.302235998344965</v>
+        <v>3.756862453225539</v>
       </c>
       <c r="C58">
-        <v>11.281537952942</v>
+        <v>11.09732708152296</v>
       </c>
       <c r="D58">
-        <v>46.20458333495078</v>
+        <v>46.16606444043051</v>
       </c>
       <c r="E58">
-        <v>5.08309686310514</v>
+        <v>5.13124118240969</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1980,16 +1980,16 @@
         <v>62</v>
       </c>
       <c r="B59">
-        <v>3.54065776068353</v>
+        <v>2.664643853928094</v>
       </c>
       <c r="C59">
-        <v>11.53573899019073</v>
+        <v>11.87618790479138</v>
       </c>
       <c r="D59">
-        <v>46.08557121560457</v>
+        <v>46.29578416053641</v>
       </c>
       <c r="E59">
-        <v>4.823256530131275</v>
+        <v>3.62868772153239</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1997,16 +1997,16 @@
         <v>63</v>
       </c>
       <c r="B60">
-        <v>4.028392438048671</v>
+        <v>4.296107716116662</v>
       </c>
       <c r="C60">
-        <v>11.13338080049813</v>
+        <v>10.85197752095363</v>
       </c>
       <c r="D60">
-        <v>46.33495597982929</v>
+        <v>46.10761217625337</v>
       </c>
       <c r="E60">
-        <v>4.115537320264857</v>
+        <v>4.309811320246655</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2014,16 +2014,16 @@
         <v>64</v>
       </c>
       <c r="B61">
-        <v>3.110848828382514</v>
+        <v>4.221976386593653</v>
       </c>
       <c r="C61">
-        <v>12.13968568315545</v>
+        <v>11.73686301534168</v>
       </c>
       <c r="D61">
-        <v>46.24566501847352</v>
+        <v>46.21521799426642</v>
       </c>
       <c r="E61">
-        <v>4.120479675775366</v>
+        <v>4.825339511438282</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2031,16 +2031,16 @@
         <v>65</v>
       </c>
       <c r="B62">
-        <v>3.243477345829332</v>
+        <v>2.576034879446234</v>
       </c>
       <c r="C62">
-        <v>11.38747194353881</v>
+        <v>10.66455303453423</v>
       </c>
       <c r="D62">
-        <v>46.38128664572512</v>
+        <v>46.11615457391158</v>
       </c>
       <c r="E62">
-        <v>3.833798491798211</v>
+        <v>4.579861539883749</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -2048,16 +2048,16 @@
         <v>66</v>
       </c>
       <c r="B63">
-        <v>3.950928883704919</v>
+        <v>3.868979538421561</v>
       </c>
       <c r="C63">
-        <v>11.46624788943533</v>
+        <v>11.54576150816269</v>
       </c>
       <c r="D63">
-        <v>46.0808680638352</v>
+        <v>46.12489905688923</v>
       </c>
       <c r="E63">
-        <v>4.705604663967398</v>
+        <v>4.367366989807302</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -2065,16 +2065,16 @@
         <v>67</v>
       </c>
       <c r="B64">
-        <v>4.216562907476051</v>
+        <v>3.553343483052684</v>
       </c>
       <c r="C64">
-        <v>11.30017926726872</v>
+        <v>10.65678867957886</v>
       </c>
       <c r="D64">
-        <v>46.22256562318555</v>
+        <v>46.05001549273599</v>
       </c>
       <c r="E64">
-        <v>3.654940526833854</v>
+        <v>4.35426108439979</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2082,16 +2082,16 @@
         <v>68</v>
       </c>
       <c r="B65">
-        <v>3.814426706597072</v>
+        <v>2.720457849578082</v>
       </c>
       <c r="C65">
-        <v>10.83801847997656</v>
+        <v>11.63409671989015</v>
       </c>
       <c r="D65">
-        <v>46.01187008759192</v>
+        <v>46.47767179165287</v>
       </c>
       <c r="E65">
-        <v>3.943272726828185</v>
+        <v>4.772924159599397</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2099,16 +2099,16 @@
         <v>69</v>
       </c>
       <c r="B66">
-        <v>3.198396467120755</v>
+        <v>3.165339480338374</v>
       </c>
       <c r="C66">
-        <v>11.38948673900856</v>
+        <v>11.70508135876184</v>
       </c>
       <c r="D66">
-        <v>46.2556985904742</v>
+        <v>46.3664220058999</v>
       </c>
       <c r="E66">
-        <v>4.719458530353291</v>
+        <v>4.583296895798471</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -2116,16 +2116,16 @@
         <v>70</v>
       </c>
       <c r="B67">
-        <v>2.569245360189521</v>
+        <v>2.837678981446741</v>
       </c>
       <c r="C67">
-        <v>12.09590394343027</v>
+        <v>11.12013969175339</v>
       </c>
       <c r="D67">
-        <v>46.09097752390279</v>
+        <v>46.1662310528887</v>
       </c>
       <c r="E67">
-        <v>4.48276255941877</v>
+        <v>3.649722112899334</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -2133,16 +2133,16 @@
         <v>71</v>
       </c>
       <c r="B68">
-        <v>3.801711069368571</v>
+        <v>3.238075982543603</v>
       </c>
       <c r="C68">
-        <v>11.77897049604158</v>
+        <v>12.14017609685584</v>
       </c>
       <c r="D68">
-        <v>46.24792065345931</v>
+        <v>46.22661414649826</v>
       </c>
       <c r="E68">
-        <v>4.568227874882478</v>
+        <v>4.522900523290362</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -2150,16 +2150,16 @@
         <v>72</v>
       </c>
       <c r="B69">
-        <v>4.289755697617033</v>
+        <v>3.167340675629806</v>
       </c>
       <c r="C69">
-        <v>11.79480603568319</v>
+        <v>10.93346393464005</v>
       </c>
       <c r="D69">
-        <v>46.2380575140478</v>
+        <v>46.26015768809766</v>
       </c>
       <c r="E69">
-        <v>4.296533656632108</v>
+        <v>4.577459061402656</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2167,16 +2167,16 @@
         <v>73</v>
       </c>
       <c r="B70">
-        <v>4.043787607979899</v>
+        <v>3.299352434706138</v>
       </c>
       <c r="C70">
-        <v>10.88395573192282</v>
+        <v>11.93678992743669</v>
       </c>
       <c r="D70">
-        <v>46.33467570640756</v>
+        <v>46.0567901165506</v>
       </c>
       <c r="E70">
-        <v>4.471257406581785</v>
+        <v>4.695602555489089</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -2184,16 +2184,16 @@
         <v>74</v>
       </c>
       <c r="B71">
-        <v>2.757922456522351</v>
+        <v>3.515989792918153</v>
       </c>
       <c r="C71">
-        <v>11.53727238046428</v>
+        <v>12.01285300953116</v>
       </c>
       <c r="D71">
-        <v>46.26001855365536</v>
+        <v>46.12978593979871</v>
       </c>
       <c r="E71">
-        <v>4.647724544933252</v>
+        <v>4.874564232044111</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2201,16 +2201,16 @@
         <v>75</v>
       </c>
       <c r="B72">
-        <v>3.029915697652812</v>
+        <v>3.681619605989857</v>
       </c>
       <c r="C72">
-        <v>11.70140041361511</v>
+        <v>10.67624170441521</v>
       </c>
       <c r="D72">
-        <v>46.45011499153905</v>
+        <v>46.05667552681244</v>
       </c>
       <c r="E72">
-        <v>3.860393725757524</v>
+        <v>5.141289135762713</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2218,16 +2218,16 @@
         <v>76</v>
       </c>
       <c r="B73">
-        <v>3.157412516932481</v>
+        <v>4.224007182408271</v>
       </c>
       <c r="C73">
-        <v>10.82195248196243</v>
+        <v>11.94290443155489</v>
       </c>
       <c r="D73">
-        <v>46.18092322071766</v>
+        <v>46.17194557433139</v>
       </c>
       <c r="E73">
-        <v>3.718708970090021</v>
+        <v>4.651990396417483</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2235,16 +2235,16 @@
         <v>77</v>
       </c>
       <c r="B74">
-        <v>4.491395378365481</v>
+        <v>4.399324224767986</v>
       </c>
       <c r="C74">
-        <v>23.54920808690757</v>
+        <v>23.85108249889416</v>
       </c>
       <c r="D74">
-        <v>22.41714370146981</v>
+        <v>22.29919080520088</v>
       </c>
       <c r="E74">
-        <v>6.936260411663577</v>
+        <v>6.914480769764558</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2252,16 +2252,16 @@
         <v>78</v>
       </c>
       <c r="B75">
-        <v>4.686634871645299</v>
+        <v>3.683744152055119</v>
       </c>
       <c r="C75">
-        <v>23.51805314771532</v>
+        <v>23.41558226457136</v>
       </c>
       <c r="D75">
-        <v>22.29706110054634</v>
+        <v>22.23129464920467</v>
       </c>
       <c r="E75">
-        <v>6.174704589921488</v>
+        <v>7.23296408739183</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2269,16 +2269,16 @@
         <v>79</v>
       </c>
       <c r="B76">
-        <v>3.717524901868765</v>
+        <v>3.464697581360423</v>
       </c>
       <c r="C76">
-        <v>24.18268197222917</v>
+        <v>23.98651648105942</v>
       </c>
       <c r="D76">
-        <v>22.2185391481419</v>
+        <v>22.40158704994271</v>
       </c>
       <c r="E76">
-        <v>7.417777469260153</v>
+        <v>6.690042761408365</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2286,16 +2286,16 @@
         <v>80</v>
       </c>
       <c r="B77">
-        <v>4.743190664825947</v>
+        <v>4.35474638011239</v>
       </c>
       <c r="C77">
-        <v>24.06532175999295</v>
+        <v>24.37145379495676</v>
       </c>
       <c r="D77">
-        <v>22.28682278211021</v>
+        <v>22.10715957526275</v>
       </c>
       <c r="E77">
-        <v>6.176993517739152</v>
+        <v>6.93942318554018</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2303,16 +2303,16 @@
         <v>81</v>
       </c>
       <c r="B78">
-        <v>3.933970951598246</v>
+        <v>4.174237478243071</v>
       </c>
       <c r="C78">
-        <v>23.6091570268159</v>
+        <v>23.65123098177441</v>
       </c>
       <c r="D78">
-        <v>22.40091341261507</v>
+        <v>22.43169462710454</v>
       </c>
       <c r="E78">
-        <v>6.865608939524316</v>
+        <v>5.917281582607638</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2320,16 +2320,16 @@
         <v>82</v>
       </c>
       <c r="B79">
-        <v>3.017678675845426</v>
+        <v>3.657368765808844</v>
       </c>
       <c r="C79">
-        <v>24.09693232970253</v>
+        <v>24.61502507973876</v>
       </c>
       <c r="D79">
-        <v>22.17068338894756</v>
+        <v>22.51340578434533</v>
       </c>
       <c r="E79">
-        <v>5.95005340272021</v>
+        <v>7.2422898089699</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2337,16 +2337,16 @@
         <v>83</v>
       </c>
       <c r="B80">
-        <v>3.362458563683292</v>
+        <v>4.156491445420914</v>
       </c>
       <c r="C80">
-        <v>23.43549161030057</v>
+        <v>23.7566809976619</v>
       </c>
       <c r="D80">
-        <v>22.07596265134971</v>
+        <v>22.33691869740168</v>
       </c>
       <c r="E80">
-        <v>7.296587677426117</v>
+        <v>6.961809262456333</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2354,16 +2354,16 @@
         <v>84</v>
       </c>
       <c r="B81">
-        <v>3.320070792033388</v>
+        <v>3.525184536842168</v>
       </c>
       <c r="C81">
-        <v>24.17838997545056</v>
+        <v>23.56887577526547</v>
       </c>
       <c r="D81">
-        <v>22.40679142376089</v>
+        <v>22.26814940021937</v>
       </c>
       <c r="E81">
-        <v>6.209265648715087</v>
+        <v>5.926363155393899</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2371,16 +2371,16 @@
         <v>85</v>
       </c>
       <c r="B82">
-        <v>3.374896683260742</v>
+        <v>4.146054387013271</v>
       </c>
       <c r="C82">
-        <v>23.53846473466524</v>
+        <v>24.57457590127774</v>
       </c>
       <c r="D82">
-        <v>22.34736977221827</v>
+        <v>22.34271216140865</v>
       </c>
       <c r="E82">
-        <v>6.479817439431301</v>
+        <v>5.828042031554903</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2388,16 +2388,16 @@
         <v>86</v>
       </c>
       <c r="B83">
-        <v>3.947806636073709</v>
+        <v>3.554759718996304</v>
       </c>
       <c r="C83">
-        <v>23.71681910996577</v>
+        <v>23.75589673710953</v>
       </c>
       <c r="D83">
-        <v>22.19143733540422</v>
+        <v>22.24641633293803</v>
       </c>
       <c r="E83">
-        <v>6.050987063069512</v>
+        <v>7.207433415868923</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2405,16 +2405,16 @@
         <v>87</v>
       </c>
       <c r="B84">
-        <v>3.229989569374899</v>
+        <v>3.180076387510017</v>
       </c>
       <c r="C84">
-        <v>24.238690267492</v>
+        <v>23.91608039313525</v>
       </c>
       <c r="D84">
-        <v>22.26105588833888</v>
+        <v>22.2058090305873</v>
       </c>
       <c r="E84">
-        <v>7.063729101457799</v>
+        <v>7.110697664287819</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2422,16 +2422,16 @@
         <v>88</v>
       </c>
       <c r="B85">
-        <v>3.490385246291587</v>
+        <v>3.09732611793466</v>
       </c>
       <c r="C85">
-        <v>24.17391801863201</v>
+        <v>24.50112336185139</v>
       </c>
       <c r="D85">
-        <v>22.53444499169558</v>
+        <v>22.07593768352436</v>
       </c>
       <c r="E85">
-        <v>6.054911190299125</v>
+        <v>7.390507293238752</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2439,16 +2439,16 @@
         <v>89</v>
       </c>
       <c r="B86">
-        <v>4.639998115049358</v>
+        <v>3.934040347958595</v>
       </c>
       <c r="C86">
-        <v>23.59417356017168</v>
+        <v>23.17210702731392</v>
       </c>
       <c r="D86">
-        <v>22.24983200239922</v>
+        <v>22.44622765628415</v>
       </c>
       <c r="E86">
-        <v>5.849905953004901</v>
+        <v>7.355637441767543</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2456,16 +2456,16 @@
         <v>90</v>
       </c>
       <c r="B87">
-        <v>3.058841622099688</v>
+        <v>4.600968817967299</v>
       </c>
       <c r="C87">
-        <v>23.98321257041765</v>
+        <v>23.44287179822775</v>
       </c>
       <c r="D87">
-        <v>22.14927446604872</v>
+        <v>22.26331883468324</v>
       </c>
       <c r="E87">
-        <v>6.459916547717751</v>
+        <v>7.139377885889704</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2473,16 +2473,16 @@
         <v>91</v>
       </c>
       <c r="B88">
-        <v>4.520737688127776</v>
+        <v>3.546244972592953</v>
       </c>
       <c r="C88">
-        <v>23.10792790331983</v>
+        <v>23.20851829066574</v>
       </c>
       <c r="D88">
-        <v>22.22068816323734</v>
+        <v>22.17664394593371</v>
       </c>
       <c r="E88">
-        <v>7.263312002213215</v>
+        <v>6.474128785712056</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2490,16 +2490,16 @@
         <v>92</v>
       </c>
       <c r="B89">
-        <v>3.692684621196571</v>
+        <v>3.85783714523968</v>
       </c>
       <c r="C89">
-        <v>23.73735575258467</v>
+        <v>23.76625649558027</v>
       </c>
       <c r="D89">
-        <v>22.13065728075355</v>
+        <v>22.10326329388646</v>
       </c>
       <c r="E89">
-        <v>7.272213020011122</v>
+        <v>5.984833402986919</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2507,16 +2507,16 @@
         <v>93</v>
       </c>
       <c r="B90">
-        <v>3.741660892052552</v>
+        <v>4.781253581649449</v>
       </c>
       <c r="C90">
-        <v>23.09409797460791</v>
+        <v>24.07535337675235</v>
       </c>
       <c r="D90">
-        <v>22.31985174587813</v>
+        <v>22.14618827539431</v>
       </c>
       <c r="E90">
-        <v>6.871742304036822</v>
+        <v>6.865397853415132</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2524,16 +2524,16 @@
         <v>94</v>
       </c>
       <c r="B91">
-        <v>3.981572527309215</v>
+        <v>4.722268941936585</v>
       </c>
       <c r="C91">
-        <v>24.60397034212309</v>
+        <v>23.63164076022532</v>
       </c>
       <c r="D91">
-        <v>22.48973717711587</v>
+        <v>22.515217750471</v>
       </c>
       <c r="E91">
-        <v>7.225674029219084</v>
+        <v>6.796002947333091</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2541,16 +2541,16 @@
         <v>95</v>
       </c>
       <c r="B92">
-        <v>3.669786308356444</v>
+        <v>4.454859395005461</v>
       </c>
       <c r="C92">
-        <v>23.15126287463177</v>
+        <v>23.26081744533297</v>
       </c>
       <c r="D92">
-        <v>22.3314499908658</v>
+        <v>22.31301135925932</v>
       </c>
       <c r="E92">
-        <v>6.405623634331124</v>
+        <v>6.49478638627599</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2558,16 +2558,16 @@
         <v>96</v>
       </c>
       <c r="B93">
-        <v>4.73995182216871</v>
+        <v>4.22492987936123</v>
       </c>
       <c r="C93">
-        <v>24.1783207683782</v>
+        <v>23.19187722867106</v>
       </c>
       <c r="D93">
-        <v>22.24602619243903</v>
+        <v>22.4072378638825</v>
       </c>
       <c r="E93">
-        <v>5.855861982061471</v>
+        <v>6.815955976401023</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2575,16 +2575,16 @@
         <v>97</v>
       </c>
       <c r="B94">
-        <v>4.697365114128981</v>
+        <v>3.748041841143617</v>
       </c>
       <c r="C94">
-        <v>23.03122682175178</v>
+        <v>24.04116532090539</v>
       </c>
       <c r="D94">
-        <v>22.36852510367061</v>
+        <v>22.21109256650037</v>
       </c>
       <c r="E94">
-        <v>6.564273463086951</v>
+        <v>6.712859177725427</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2592,16 +2592,16 @@
         <v>98</v>
       </c>
       <c r="B95">
-        <v>4.650696522589138</v>
+        <v>4.259796475208833</v>
       </c>
       <c r="C95">
-        <v>23.02061484005776</v>
+        <v>23.72170797822919</v>
       </c>
       <c r="D95">
-        <v>22.52177730718781</v>
+        <v>22.22440504972731</v>
       </c>
       <c r="E95">
-        <v>6.14853964001624</v>
+        <v>6.708699705161182</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2609,16 +2609,16 @@
         <v>99</v>
       </c>
       <c r="B96">
-        <v>3.311465711886054</v>
+        <v>3.614787788132196</v>
       </c>
       <c r="C96">
-        <v>23.96766169924933</v>
+        <v>24.19611234474743</v>
       </c>
       <c r="D96">
-        <v>22.21192226468796</v>
+        <v>22.21415505407149</v>
       </c>
       <c r="E96">
-        <v>6.371372808217133</v>
+        <v>6.454749578260532</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2626,16 +2626,16 @@
         <v>100</v>
       </c>
       <c r="B97">
-        <v>3.891335744750759</v>
+        <v>4.173821826336177</v>
       </c>
       <c r="C97">
-        <v>24.33079303378701</v>
+        <v>24.19734640034859</v>
       </c>
       <c r="D97">
-        <v>22.41921560554027</v>
+        <v>22.34305980869476</v>
       </c>
       <c r="E97">
-        <v>6.483388941291347</v>
+        <v>5.972246592028983</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2643,16 +2643,16 @@
         <v>101</v>
       </c>
       <c r="B98">
-        <v>3.287125730797768</v>
+        <v>3.785852665652883</v>
       </c>
       <c r="C98">
-        <v>24.26274921404852</v>
+        <v>23.47205811936714</v>
       </c>
       <c r="D98">
-        <v>22.09799543797209</v>
+        <v>22.10324482530073</v>
       </c>
       <c r="E98">
-        <v>7.175023444361512</v>
+        <v>6.098086100505157</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2660,16 +2660,16 @@
         <v>102</v>
       </c>
       <c r="B99">
-        <v>3.389428691331712</v>
+        <v>3.815267842247092</v>
       </c>
       <c r="C99">
-        <v>24.33511577792539</v>
+        <v>23.54466900221568</v>
       </c>
       <c r="D99">
-        <v>22.42305389450829</v>
+        <v>22.12318454373586</v>
       </c>
       <c r="E99">
-        <v>6.690984766736893</v>
+        <v>6.068027292099083</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2677,16 +2677,16 @@
         <v>103</v>
       </c>
       <c r="B100">
-        <v>4.228437151248781</v>
+        <v>4.14932841423474</v>
       </c>
       <c r="C100">
-        <v>23.18022113442091</v>
+        <v>23.8592574974745</v>
       </c>
       <c r="D100">
-        <v>22.28343357819457</v>
+        <v>22.33275678945785</v>
       </c>
       <c r="E100">
-        <v>6.641487013643598</v>
+        <v>6.385864259507873</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2694,16 +2694,16 @@
         <v>104</v>
       </c>
       <c r="B101">
-        <v>4.196118007311299</v>
+        <v>3.840579934828259</v>
       </c>
       <c r="C101">
-        <v>24.12963730394532</v>
+        <v>23.13212864994795</v>
       </c>
       <c r="D101">
-        <v>22.2495118981008</v>
+        <v>22.34982257208148</v>
       </c>
       <c r="E101">
-        <v>7.384267861174644</v>
+        <v>7.149632325150229</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2711,16 +2711,16 @@
         <v>105</v>
       </c>
       <c r="B102">
-        <v>3.598778750622449</v>
+        <v>4.576593804797136</v>
       </c>
       <c r="C102">
-        <v>23.44456411924635</v>
+        <v>23.87759216493476</v>
       </c>
       <c r="D102">
-        <v>22.11008738036448</v>
+        <v>22.29198376216454</v>
       </c>
       <c r="E102">
-        <v>7.058769237074244</v>
+        <v>5.886653579525221</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2728,16 +2728,16 @@
         <v>106</v>
       </c>
       <c r="B103">
-        <v>4.267745404009058</v>
+        <v>3.173430902928969</v>
       </c>
       <c r="C103">
-        <v>23.15126089956526</v>
+        <v>23.76110644833502</v>
       </c>
       <c r="D103">
-        <v>22.42584549689982</v>
+        <v>22.13957370835899</v>
       </c>
       <c r="E103">
-        <v>6.75866676782397</v>
+        <v>6.232678615055962</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2745,16 +2745,16 @@
         <v>107</v>
       </c>
       <c r="B104">
-        <v>3.90033896490817</v>
+        <v>4.273863400637951</v>
       </c>
       <c r="C104">
-        <v>23.88984035837589</v>
+        <v>23.31329453501295</v>
       </c>
       <c r="D104">
-        <v>22.37647588558914</v>
+        <v>22.18631601593569</v>
       </c>
       <c r="E104">
-        <v>6.194591124078285</v>
+        <v>6.984424245653939</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2762,16 +2762,16 @@
         <v>108</v>
       </c>
       <c r="B105">
-        <v>4.532038247758644</v>
+        <v>4.796750858452325</v>
       </c>
       <c r="C105">
-        <v>23.30651513396478</v>
+        <v>24.05480959626664</v>
       </c>
       <c r="D105">
-        <v>22.16213460926763</v>
+        <v>22.393438703458</v>
       </c>
       <c r="E105">
-        <v>5.907482126313923</v>
+        <v>6.67262400373372</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2779,16 +2779,16 @@
         <v>109</v>
       </c>
       <c r="B106">
-        <v>3.725316301235879</v>
+        <v>3.608248915883875</v>
       </c>
       <c r="C106">
-        <v>23.59740161344593</v>
+        <v>23.26544155974885</v>
       </c>
       <c r="D106">
-        <v>22.51460687488497</v>
+        <v>22.13882476811396</v>
       </c>
       <c r="E106">
-        <v>6.450701348553107</v>
+        <v>5.859814832332856</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2796,16 +2796,16 @@
         <v>110</v>
       </c>
       <c r="B107">
-        <v>3.436239249984642</v>
+        <v>3.720371741519171</v>
       </c>
       <c r="C107">
-        <v>23.53692646097545</v>
+        <v>23.89396357649068</v>
       </c>
       <c r="D107">
-        <v>22.45865466855257</v>
+        <v>22.38086150448657</v>
       </c>
       <c r="E107">
-        <v>6.586941167306009</v>
+        <v>6.852927239558769</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2813,16 +2813,16 @@
         <v>111</v>
       </c>
       <c r="B108">
-        <v>3.292784922057378</v>
+        <v>4.321285811401701</v>
       </c>
       <c r="C108">
-        <v>23.30404741798739</v>
+        <v>24.33898617803281</v>
       </c>
       <c r="D108">
-        <v>22.53499509251692</v>
+        <v>22.16133313310171</v>
       </c>
       <c r="E108">
-        <v>6.185824986569746</v>
+        <v>6.968561332531994</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -2830,16 +2830,16 @@
         <v>112</v>
       </c>
       <c r="B109">
-        <v>3.261213769286174</v>
+        <v>3.905413994093131</v>
       </c>
       <c r="C109">
-        <v>23.17756036616867</v>
+        <v>24.16906150059692</v>
       </c>
       <c r="D109">
-        <v>22.16451485710722</v>
+        <v>22.13021717671799</v>
       </c>
       <c r="E109">
-        <v>6.40595391445279</v>
+        <v>5.999283333073778</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2847,16 +2847,16 @@
         <v>113</v>
       </c>
       <c r="B110">
-        <v>4.436282776285319</v>
+        <v>4.109501710492636</v>
       </c>
       <c r="C110">
-        <v>24.27658562794789</v>
+        <v>24.2590574272743</v>
       </c>
       <c r="D110">
-        <v>22.10415169059317</v>
+        <v>22.22843197113195</v>
       </c>
       <c r="E110">
-        <v>5.900143421436911</v>
+        <v>6.24626455487527</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -2864,16 +2864,16 @@
         <v>114</v>
       </c>
       <c r="B111">
-        <v>4.473421806083631</v>
+        <v>4.04581471413139</v>
       </c>
       <c r="C111">
-        <v>24.53657335913989</v>
+        <v>23.76438114807772</v>
       </c>
       <c r="D111">
-        <v>22.23185660932747</v>
+        <v>22.53212864334143</v>
       </c>
       <c r="E111">
-        <v>6.739450622599175</v>
+        <v>5.828176295049185</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -2881,16 +2881,16 @@
         <v>115</v>
       </c>
       <c r="B112">
-        <v>4.25889380509336</v>
+        <v>4.151639093005184</v>
       </c>
       <c r="C112">
-        <v>24.10470484203698</v>
+        <v>24.3354931394499</v>
       </c>
       <c r="D112">
-        <v>22.21079017932838</v>
+        <v>22.4511587272827</v>
       </c>
       <c r="E112">
-        <v>6.457320015407744</v>
+        <v>6.290381894808027</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -2898,16 +2898,16 @@
         <v>116</v>
       </c>
       <c r="B113">
-        <v>3.83478496028847</v>
+        <v>3.444490018073612</v>
       </c>
       <c r="C113">
-        <v>24.27722832149465</v>
+        <v>23.44127961203356</v>
       </c>
       <c r="D113">
-        <v>22.32053986619856</v>
+        <v>22.43940240457613</v>
       </c>
       <c r="E113">
-        <v>6.001822702628609</v>
+        <v>7.019135195261843</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -2915,16 +2915,16 @@
         <v>117</v>
       </c>
       <c r="B114">
-        <v>4.535819105056272</v>
+        <v>4.55976514025267</v>
       </c>
       <c r="C114">
-        <v>23.62498021878592</v>
+        <v>24.05993079739482</v>
       </c>
       <c r="D114">
-        <v>22.4660072275705</v>
+        <v>22.08857005415002</v>
       </c>
       <c r="E114">
-        <v>6.648623461026879</v>
+        <v>6.455606330314247</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -2932,16 +2932,16 @@
         <v>118</v>
       </c>
       <c r="B115">
-        <v>4.474171746426778</v>
+        <v>3.26915714860126</v>
       </c>
       <c r="C115">
-        <v>23.19792207356172</v>
+        <v>24.10476082287853</v>
       </c>
       <c r="D115">
-        <v>22.15833072767166</v>
+        <v>22.42256801931898</v>
       </c>
       <c r="E115">
-        <v>6.891088529848497</v>
+        <v>7.288560068189469</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -2949,16 +2949,16 @@
         <v>119</v>
       </c>
       <c r="B116">
-        <v>3.790667591914751</v>
+        <v>3.566048937004025</v>
       </c>
       <c r="C116">
-        <v>23.77366605173301</v>
+        <v>23.74218523507577</v>
       </c>
       <c r="D116">
-        <v>22.51258317513687</v>
+        <v>22.09653795111561</v>
       </c>
       <c r="E116">
-        <v>6.623549264322209</v>
+        <v>6.751810535623092</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -2966,16 +2966,16 @@
         <v>120</v>
       </c>
       <c r="B117">
-        <v>3.571722008657339</v>
+        <v>3.675399134295726</v>
       </c>
       <c r="C117">
-        <v>24.61388225016708</v>
+        <v>23.46361041582087</v>
       </c>
       <c r="D117">
-        <v>22.47110576953441</v>
+        <v>22.1540734857694</v>
       </c>
       <c r="E117">
-        <v>5.893495900895561</v>
+        <v>6.308818746259108</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -2983,16 +2983,16 @@
         <v>121</v>
       </c>
       <c r="B118">
-        <v>4.300035928219137</v>
+        <v>4.047493001101179</v>
       </c>
       <c r="C118">
-        <v>24.29534431629209</v>
+        <v>24.22469533097467</v>
       </c>
       <c r="D118">
-        <v>22.20664749594107</v>
+        <v>22.31833818449347</v>
       </c>
       <c r="E118">
-        <v>6.607607093342246</v>
+        <v>6.193223072214645</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -3000,16 +3000,16 @@
         <v>122</v>
       </c>
       <c r="B119">
-        <v>3.473459427873948</v>
+        <v>3.98306074837482</v>
       </c>
       <c r="C119">
-        <v>24.60780519552524</v>
+        <v>23.38495493078608</v>
       </c>
       <c r="D119">
-        <v>22.13448080656849</v>
+        <v>22.25459205372093</v>
       </c>
       <c r="E119">
-        <v>7.230674228673893</v>
+        <v>6.468061385305132</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -3017,16 +3017,16 @@
         <v>123</v>
       </c>
       <c r="B120">
-        <v>4.489272211448138</v>
+        <v>3.041269780861001</v>
       </c>
       <c r="C120">
-        <v>23.22261877904942</v>
+        <v>24.2210492700054</v>
       </c>
       <c r="D120">
-        <v>22.0723111705093</v>
+        <v>22.16572179771256</v>
       </c>
       <c r="E120">
-        <v>6.273308220410219</v>
+        <v>7.362780758533205</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -3034,16 +3034,16 @@
         <v>124</v>
       </c>
       <c r="B121">
-        <v>4.68494927494195</v>
+        <v>3.74744688078163</v>
       </c>
       <c r="C121">
-        <v>23.59694252897203</v>
+        <v>23.18188409608253</v>
       </c>
       <c r="D121">
-        <v>22.34581777727729</v>
+        <v>22.1232224727684</v>
       </c>
       <c r="E121">
-        <v>7.080949653708248</v>
+        <v>6.33339668652814</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -3051,16 +3051,16 @@
         <v>125</v>
       </c>
       <c r="B122">
-        <v>3.076808848053165</v>
+        <v>3.665622466669871</v>
       </c>
       <c r="C122">
-        <v>23.52739454114128</v>
+        <v>24.59130170602303</v>
       </c>
       <c r="D122">
-        <v>22.18007729298435</v>
+        <v>22.2928349624616</v>
       </c>
       <c r="E122">
-        <v>5.895478819829314</v>
+        <v>6.740942659347452</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -3068,16 +3068,16 @@
         <v>126</v>
       </c>
       <c r="B123">
-        <v>4.116492849881802</v>
+        <v>4.316529771324116</v>
       </c>
       <c r="C123">
-        <v>23.32241401682748</v>
+        <v>23.73308788995947</v>
       </c>
       <c r="D123">
-        <v>22.50475038562728</v>
+        <v>22.07468007944446</v>
       </c>
       <c r="E123">
-        <v>6.360192162108575</v>
+        <v>7.309759624630105</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -3085,16 +3085,16 @@
         <v>127</v>
       </c>
       <c r="B124">
-        <v>3.857423049725385</v>
+        <v>3.698873705955955</v>
       </c>
       <c r="C124">
-        <v>23.87225423464977</v>
+        <v>23.16880475315794</v>
       </c>
       <c r="D124">
-        <v>22.38805805182392</v>
+        <v>22.45113132092753</v>
       </c>
       <c r="E124">
-        <v>6.079463929182874</v>
+        <v>7.273136092215095</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -3102,16 +3102,16 @@
         <v>128</v>
       </c>
       <c r="B125">
-        <v>4.6644452337347</v>
+        <v>4.438302691596507</v>
       </c>
       <c r="C125">
-        <v>23.55877132854017</v>
+        <v>23.0548097072168</v>
       </c>
       <c r="D125">
-        <v>22.15529446712052</v>
+        <v>22.39753387289618</v>
       </c>
       <c r="E125">
-        <v>6.790221158266363</v>
+        <v>6.064476089204119</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -3119,16 +3119,16 @@
         <v>129</v>
       </c>
       <c r="B126">
-        <v>3.026461265784518</v>
+        <v>4.266338076940419</v>
       </c>
       <c r="C126">
-        <v>24.58197110843553</v>
+        <v>24.38842704312825</v>
       </c>
       <c r="D126">
-        <v>22.14618872931766</v>
+        <v>22.43300628170448</v>
       </c>
       <c r="E126">
-        <v>7.252645486909048</v>
+        <v>7.312856587765617</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -3136,16 +3136,16 @@
         <v>130</v>
       </c>
       <c r="B127">
-        <v>3.547116754278294</v>
+        <v>4.253524822472951</v>
       </c>
       <c r="C127">
-        <v>24.58492583754007</v>
+        <v>24.42534304172345</v>
       </c>
       <c r="D127">
-        <v>22.15024068106232</v>
+        <v>22.21715088312759</v>
       </c>
       <c r="E127">
-        <v>6.004724192933878</v>
+        <v>7.223248557558712</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -3153,16 +3153,16 @@
         <v>131</v>
       </c>
       <c r="B128">
-        <v>3.311777518663423</v>
+        <v>3.642780104056734</v>
       </c>
       <c r="C128">
-        <v>24.43101114522127</v>
+        <v>23.28698217694993</v>
       </c>
       <c r="D128">
-        <v>22.29921420060684</v>
+        <v>22.22114109502513</v>
       </c>
       <c r="E128">
-        <v>7.375004876986092</v>
+        <v>7.193614848685778</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -3170,16 +3170,16 @@
         <v>132</v>
       </c>
       <c r="B129">
-        <v>3.371625927664508</v>
+        <v>3.112344355786897</v>
       </c>
       <c r="C129">
-        <v>23.95679355168051</v>
+        <v>24.56613277838057</v>
       </c>
       <c r="D129">
-        <v>22.16725032092899</v>
+        <v>22.45509516643898</v>
       </c>
       <c r="E129">
-        <v>6.515265549129269</v>
+        <v>6.301375013489579</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -3187,16 +3187,16 @@
         <v>133</v>
       </c>
       <c r="B130">
-        <v>3.314762665729685</v>
+        <v>4.472316933246656</v>
       </c>
       <c r="C130">
-        <v>23.79766405197084</v>
+        <v>24.30458344475278</v>
       </c>
       <c r="D130">
-        <v>22.33631536813169</v>
+        <v>22.24760710330002</v>
       </c>
       <c r="E130">
-        <v>6.782154842811714</v>
+        <v>5.868598204451108</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -3204,16 +3204,16 @@
         <v>134</v>
       </c>
       <c r="B131">
-        <v>4.489468718787683</v>
+        <v>4.544347366403556</v>
       </c>
       <c r="C131">
-        <v>23.87122305122065</v>
+        <v>23.06516833172662</v>
       </c>
       <c r="D131">
-        <v>22.128114789823</v>
+        <v>22.15876628297598</v>
       </c>
       <c r="E131">
-        <v>7.376613663061942</v>
+        <v>6.180835712855165</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -3221,16 +3221,16 @@
         <v>135</v>
       </c>
       <c r="B132">
-        <v>4.207477973784236</v>
+        <v>4.217455810487815</v>
       </c>
       <c r="C132">
-        <v>24.24412686544413</v>
+        <v>24.22577286171857</v>
       </c>
       <c r="D132">
-        <v>22.4770086396921</v>
+        <v>22.43877820651103</v>
       </c>
       <c r="E132">
-        <v>7.165233996410575</v>
+        <v>6.917500448565155</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -3238,16 +3238,16 @@
         <v>136</v>
       </c>
       <c r="B133">
-        <v>3.868404541051228</v>
+        <v>4.267715629346564</v>
       </c>
       <c r="C133">
-        <v>23.61240675508558</v>
+        <v>23.90303275365036</v>
       </c>
       <c r="D133">
-        <v>22.50011936294289</v>
+        <v>22.13436453480638</v>
       </c>
       <c r="E133">
-        <v>6.899639756615514</v>
+        <v>6.044192136507978</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -3255,16 +3255,16 @@
         <v>137</v>
       </c>
       <c r="B134">
-        <v>4.113389977803976</v>
+        <v>3.598490614962072</v>
       </c>
       <c r="C134">
-        <v>23.19691888834114</v>
+        <v>24.13579511775654</v>
       </c>
       <c r="D134">
-        <v>22.20085411110019</v>
+        <v>22.50135462911356</v>
       </c>
       <c r="E134">
-        <v>6.562895931024742</v>
+        <v>7.115771484669461</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -3272,16 +3272,16 @@
         <v>138</v>
       </c>
       <c r="B135">
-        <v>4.723524998128919</v>
+        <v>3.719032957369942</v>
       </c>
       <c r="C135">
-        <v>24.34139761129558</v>
+        <v>24.22628548756268</v>
       </c>
       <c r="D135">
-        <v>22.47996195378967</v>
+        <v>22.19818808812927</v>
       </c>
       <c r="E135">
-        <v>5.869911255732032</v>
+        <v>7.124599486526654</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -3289,16 +3289,16 @@
         <v>139</v>
       </c>
       <c r="B136">
-        <v>3.892168663818386</v>
+        <v>3.880029579173211</v>
       </c>
       <c r="C136">
-        <v>23.68517727007667</v>
+        <v>24.59172352420584</v>
       </c>
       <c r="D136">
-        <v>22.06063281591977</v>
+        <v>22.32522087160774</v>
       </c>
       <c r="E136">
-        <v>5.955183734363333</v>
+        <v>6.445670938680683</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -3306,16 +3306,16 @@
         <v>140</v>
       </c>
       <c r="B137">
-        <v>4.735998488654214</v>
+        <v>3.677153228364773</v>
       </c>
       <c r="C137">
-        <v>24.1173558383786</v>
+        <v>24.36908617937579</v>
       </c>
       <c r="D137">
-        <v>22.26129392475127</v>
+        <v>22.23435301292437</v>
       </c>
       <c r="E137">
-        <v>6.065895612993689</v>
+        <v>6.838220866498262</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -3323,16 +3323,16 @@
         <v>141</v>
       </c>
       <c r="B138">
-        <v>3.884487721428056</v>
+        <v>3.498811779222124</v>
       </c>
       <c r="C138">
-        <v>24.59418326561599</v>
+        <v>24.26048787157525</v>
       </c>
       <c r="D138">
-        <v>22.16582264805286</v>
+        <v>22.42162716734233</v>
       </c>
       <c r="E138">
-        <v>7.090450974030063</v>
+        <v>5.920807392738246</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -3340,16 +3340,16 @@
         <v>142</v>
       </c>
       <c r="B139">
-        <v>4.444252775721847</v>
+        <v>4.461795439847823</v>
       </c>
       <c r="C139">
-        <v>23.10029758146855</v>
+        <v>23.98544338119048</v>
       </c>
       <c r="D139">
-        <v>22.43192723200213</v>
+        <v>22.32380346728942</v>
       </c>
       <c r="E139">
-        <v>5.845504918032761</v>
+        <v>6.237564455429165</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -3357,16 +3357,16 @@
         <v>143</v>
       </c>
       <c r="B140">
-        <v>3.815299915667213</v>
+        <v>5.204641138352886</v>
       </c>
       <c r="C140">
-        <v>10.52702831998528</v>
+        <v>10.57850766670785</v>
       </c>
       <c r="D140">
-        <v>58.11867938484536</v>
+        <v>58.01330084143785</v>
       </c>
       <c r="E140">
-        <v>5.527652413069777</v>
+        <v>4.480058276590777</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -3374,16 +3374,16 @@
         <v>144</v>
       </c>
       <c r="B141">
-        <v>3.707618029337414</v>
+        <v>5.068543032234778</v>
       </c>
       <c r="C141">
-        <v>11.53415233777361</v>
+        <v>11.35778462188344</v>
       </c>
       <c r="D141">
-        <v>58.16203327309057</v>
+        <v>58.32974214349128</v>
       </c>
       <c r="E141">
-        <v>5.378769478829215</v>
+        <v>5.145167071698831</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -3391,16 +3391,16 @@
         <v>145</v>
       </c>
       <c r="B142">
-        <v>3.73388344487589</v>
+        <v>5.265328702773238</v>
       </c>
       <c r="C142">
-        <v>11.93888038772659</v>
+        <v>11.63757316639679</v>
       </c>
       <c r="D142">
-        <v>58.33883112650513</v>
+        <v>57.96336998771954</v>
       </c>
       <c r="E142">
-        <v>5.253928577924537</v>
+        <v>4.057165268454375</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -3408,16 +3408,16 @@
         <v>146</v>
       </c>
       <c r="B143">
-        <v>4.794033524600832</v>
+        <v>4.527677213747778</v>
       </c>
       <c r="C143">
-        <v>11.0507801793602</v>
+        <v>10.44002006412855</v>
       </c>
       <c r="D143">
-        <v>58.35690083605509</v>
+        <v>58.11813291612406</v>
       </c>
       <c r="E143">
-        <v>4.467618025323793</v>
+        <v>4.077552249687722</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -3425,16 +3425,16 @@
         <v>147</v>
       </c>
       <c r="B144">
-        <v>4.415090194243957</v>
+        <v>4.539840589609216</v>
       </c>
       <c r="C144">
-        <v>10.69178057283313</v>
+        <v>11.52762539129147</v>
       </c>
       <c r="D144">
-        <v>57.95302278095252</v>
+        <v>57.98437686971623</v>
       </c>
       <c r="E144">
-        <v>5.064625021310896</v>
+        <v>4.243564821055753</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -3442,16 +3442,16 @@
         <v>148</v>
       </c>
       <c r="B145">
-        <v>4.397111360010806</v>
+        <v>4.123335900789752</v>
       </c>
       <c r="C145">
-        <v>10.72633392415312</v>
+        <v>10.66138570123391</v>
       </c>
       <c r="D145">
-        <v>57.9404143658713</v>
+        <v>57.99134841443398</v>
       </c>
       <c r="E145">
-        <v>4.907575583705779</v>
+        <v>3.955678365709686</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -3459,16 +3459,16 @@
         <v>149</v>
       </c>
       <c r="B146">
-        <v>4.295529491938978</v>
+        <v>4.442684042952989</v>
       </c>
       <c r="C146">
-        <v>10.44974773727008</v>
+        <v>11.24117335244102</v>
       </c>
       <c r="D146">
-        <v>58.09686133190402</v>
+        <v>58.1286179915968</v>
       </c>
       <c r="E146">
-        <v>5.523310378557897</v>
+        <v>4.721669778217374</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -3476,16 +3476,16 @@
         <v>150</v>
       </c>
       <c r="B147">
-        <v>4.804649225792574</v>
+        <v>4.351630267091351</v>
       </c>
       <c r="C147">
-        <v>11.60093601565428</v>
+        <v>11.00645828216745</v>
       </c>
       <c r="D147">
-        <v>58.07206253497338</v>
+        <v>58.01969024457924</v>
       </c>
       <c r="E147">
-        <v>4.341921083247745</v>
+        <v>4.132661175391663</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -3493,16 +3493,16 @@
         <v>151</v>
       </c>
       <c r="B148">
-        <v>3.952720077400519</v>
+        <v>4.967917533235584</v>
       </c>
       <c r="C148">
-        <v>11.97053649421465</v>
+        <v>11.29674536365576</v>
       </c>
       <c r="D148">
-        <v>57.96932550492496</v>
+        <v>58.17980614394576</v>
       </c>
       <c r="E148">
-        <v>4.484519183843837</v>
+        <v>5.200202404459692</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -3510,16 +3510,16 @@
         <v>152</v>
       </c>
       <c r="B149">
-        <v>4.704481111429771</v>
+        <v>4.945492030869582</v>
       </c>
       <c r="C149">
-        <v>11.17845549528116</v>
+        <v>11.97449589569999</v>
       </c>
       <c r="D149">
-        <v>58.01076121682099</v>
+        <v>58.34616495561335</v>
       </c>
       <c r="E149">
-        <v>5.301917875421404</v>
+        <v>5.467352508016267</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -3527,16 +3527,16 @@
         <v>153</v>
       </c>
       <c r="B150">
-        <v>4.941383282174591</v>
+        <v>3.939731420295905</v>
       </c>
       <c r="C150">
-        <v>11.97832226962456</v>
+        <v>11.49920452006783</v>
       </c>
       <c r="D150">
-        <v>58.2777747166657</v>
+        <v>58.26230863886199</v>
       </c>
       <c r="E150">
-        <v>4.109070938571062</v>
+        <v>4.206370763847851</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -3544,16 +3544,16 @@
         <v>154</v>
       </c>
       <c r="B151">
-        <v>4.311914228795456</v>
+        <v>4.229804886171381</v>
       </c>
       <c r="C151">
-        <v>11.51805043777329</v>
+        <v>11.48333878864691</v>
       </c>
       <c r="D151">
-        <v>57.8738768730855</v>
+        <v>58.34078769880976</v>
       </c>
       <c r="E151">
-        <v>5.207294743711063</v>
+        <v>4.680283906774958</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -3561,16 +3561,16 @@
         <v>155</v>
       </c>
       <c r="B152">
-        <v>5.192907979731388</v>
+        <v>5.353253232939656</v>
       </c>
       <c r="C152">
-        <v>11.2583542488395</v>
+        <v>11.84456789403854</v>
       </c>
       <c r="D152">
-        <v>58.28263675475788</v>
+        <v>57.9908075107928</v>
       </c>
       <c r="E152">
-        <v>4.826165232681451</v>
+        <v>5.299838339649208</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -3578,16 +3578,16 @@
         <v>156</v>
       </c>
       <c r="B153">
-        <v>4.331161704640291</v>
+        <v>5.415486381314928</v>
       </c>
       <c r="C153">
-        <v>10.47127136832854</v>
+        <v>10.67566285686609</v>
       </c>
       <c r="D153">
-        <v>57.87656176248175</v>
+        <v>58.32936531702889</v>
       </c>
       <c r="E153">
-        <v>4.746573103279819</v>
+        <v>4.067249961158257</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -3595,16 +3595,16 @@
         <v>157</v>
       </c>
       <c r="B154">
-        <v>4.575651167073865</v>
+        <v>4.325353606657083</v>
       </c>
       <c r="C154">
-        <v>10.52370769375213</v>
+        <v>10.49941340262622</v>
       </c>
       <c r="D154">
-        <v>58.16101310472088</v>
+        <v>58.12815109213481</v>
       </c>
       <c r="E154">
-        <v>5.514570275491305</v>
+        <v>4.020231706226117</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -3612,16 +3612,16 @@
         <v>158</v>
       </c>
       <c r="B155">
-        <v>5.094298421603918</v>
+        <v>3.645044446612963</v>
       </c>
       <c r="C155">
-        <v>11.85311615717603</v>
+        <v>11.75818591498935</v>
       </c>
       <c r="D155">
-        <v>57.91516886349542</v>
+        <v>58.31436356539404</v>
       </c>
       <c r="E155">
-        <v>3.969304756717393</v>
+        <v>5.243924019354322</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -3629,16 +3629,16 @@
         <v>159</v>
       </c>
       <c r="B156">
-        <v>4.815952560854033</v>
+        <v>4.706082391147952</v>
       </c>
       <c r="C156">
-        <v>10.61356412697811</v>
+        <v>11.31322111942308</v>
       </c>
       <c r="D156">
-        <v>58.19120107053238</v>
+        <v>57.89138609607163</v>
       </c>
       <c r="E156">
-        <v>4.93363941511409</v>
+        <v>5.351103891705498</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -3646,16 +3646,16 @@
         <v>160</v>
       </c>
       <c r="B157">
-        <v>4.59310769576026</v>
+        <v>3.688494402874192</v>
       </c>
       <c r="C157">
-        <v>11.56284328876628</v>
+        <v>11.10050079223624</v>
       </c>
       <c r="D157">
-        <v>57.88502925092892</v>
+        <v>57.89736125521701</v>
       </c>
       <c r="E157">
-        <v>5.438076840032263</v>
+        <v>4.170914389070058</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -3663,16 +3663,16 @@
         <v>161</v>
       </c>
       <c r="B158">
-        <v>4.135799268901335</v>
+        <v>4.838077814861493</v>
       </c>
       <c r="C158">
-        <v>10.47422383598606</v>
+        <v>11.42543218438798</v>
       </c>
       <c r="D158">
-        <v>58.13947964616288</v>
+        <v>57.89406154326921</v>
       </c>
       <c r="E158">
-        <v>4.193678710167687</v>
+        <v>4.807783673335969</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -3680,16 +3680,16 @@
         <v>162</v>
       </c>
       <c r="B159">
-        <v>4.175054067885314</v>
+        <v>4.338865927930423</v>
       </c>
       <c r="C159">
-        <v>10.80444671541383</v>
+        <v>11.52582809396588</v>
       </c>
       <c r="D159">
-        <v>58.28386607978612</v>
+        <v>57.93471804761807</v>
       </c>
       <c r="E159">
-        <v>4.207174706922912</v>
+        <v>4.661354167667467</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -3697,16 +3697,16 @@
         <v>163</v>
       </c>
       <c r="B160">
-        <v>5.087742308640857</v>
+        <v>3.669304636590025</v>
       </c>
       <c r="C160">
-        <v>11.12604905989355</v>
+        <v>11.07653917868026</v>
       </c>
       <c r="D160">
-        <v>58.16754581429872</v>
+        <v>58.18632785740515</v>
       </c>
       <c r="E160">
-        <v>5.243672895511232</v>
+        <v>5.12158611038433</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -3714,16 +3714,16 @@
         <v>164</v>
       </c>
       <c r="B161">
-        <v>4.251450219619333</v>
+        <v>5.286789990182497</v>
       </c>
       <c r="C161">
-        <v>11.85479871292777</v>
+        <v>11.60876285526746</v>
       </c>
       <c r="D161">
-        <v>58.25254824153814</v>
+        <v>58.31443116980026</v>
       </c>
       <c r="E161">
-        <v>4.713048211587251</v>
+        <v>4.174605017814363</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -3731,16 +3731,16 @@
         <v>165</v>
       </c>
       <c r="B162">
-        <v>4.743761935363501</v>
+        <v>4.125646759104187</v>
       </c>
       <c r="C162">
-        <v>10.70699679214975</v>
+        <v>11.47242979505111</v>
       </c>
       <c r="D162">
-        <v>57.98416398740632</v>
+        <v>58.18080208920193</v>
       </c>
       <c r="E162">
-        <v>4.119991975634629</v>
+        <v>4.670484347575141</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -3748,16 +3748,16 @@
         <v>166</v>
       </c>
       <c r="B163">
-        <v>4.503050810623442</v>
+        <v>4.215605321317608</v>
       </c>
       <c r="C163">
-        <v>11.55805289849107</v>
+        <v>11.28975737530301</v>
       </c>
       <c r="D163">
-        <v>57.96404411725785</v>
+        <v>58.21683692288725</v>
       </c>
       <c r="E163">
-        <v>5.498839006417653</v>
+        <v>4.237026257194607</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -3765,16 +3765,16 @@
         <v>167</v>
       </c>
       <c r="B164">
-        <v>4.661219023036178</v>
+        <v>3.85180210077151</v>
       </c>
       <c r="C164">
-        <v>11.30602746116154</v>
+        <v>10.72631612919282</v>
       </c>
       <c r="D164">
-        <v>58.22509389240942</v>
+        <v>58.0066360193345</v>
       </c>
       <c r="E164">
-        <v>5.156258657234256</v>
+        <v>5.176659580858527</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -3782,16 +3782,16 @@
         <v>168</v>
       </c>
       <c r="B165">
-        <v>4.064461428691275</v>
+        <v>5.032829808061084</v>
       </c>
       <c r="C165">
-        <v>11.75102131421965</v>
+        <v>10.90316737530921</v>
       </c>
       <c r="D165">
-        <v>58.18595999358797</v>
+        <v>58.18738920925216</v>
       </c>
       <c r="E165">
-        <v>4.59845141633137</v>
+        <v>5.225299909909848</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -3799,16 +3799,16 @@
         <v>169</v>
       </c>
       <c r="B166">
-        <v>4.685496788276565</v>
+        <v>4.959410349152803</v>
       </c>
       <c r="C166">
-        <v>10.84810990115909</v>
+        <v>11.0481122863969</v>
       </c>
       <c r="D166">
-        <v>58.2677354614009</v>
+        <v>58.30488231711913</v>
       </c>
       <c r="E166">
-        <v>4.314681578368798</v>
+        <v>5.247857635584142</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -3816,16 +3816,16 @@
         <v>170</v>
       </c>
       <c r="B167">
-        <v>4.325792964844818</v>
+        <v>3.879883672548218</v>
       </c>
       <c r="C167">
-        <v>11.94338734109863</v>
+        <v>11.11832569683024</v>
       </c>
       <c r="D167">
-        <v>58.1501610816216</v>
+        <v>58.1368793551697</v>
       </c>
       <c r="E167">
-        <v>5.353933430646886</v>
+        <v>4.077092418273513</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -3833,16 +3833,16 @@
         <v>171</v>
       </c>
       <c r="B168">
-        <v>5.123217358186366</v>
+        <v>5.350559659169738</v>
       </c>
       <c r="C168">
-        <v>11.62298949921636</v>
+        <v>10.92052802791809</v>
       </c>
       <c r="D168">
-        <v>58.12885990645893</v>
+        <v>57.92894395279405</v>
       </c>
       <c r="E168">
-        <v>5.231758858111885</v>
+        <v>4.144827595944158</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -3850,16 +3850,16 @@
         <v>172</v>
       </c>
       <c r="B169">
-        <v>5.375011922233893</v>
+        <v>4.749685123257846</v>
       </c>
       <c r="C169">
-        <v>11.58589530127978</v>
+        <v>10.76811331372529</v>
       </c>
       <c r="D169">
-        <v>57.90656282160673</v>
+        <v>58.25875511518781</v>
       </c>
       <c r="E169">
-        <v>5.33164389578821</v>
+        <v>4.19162413327647</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -3867,16 +3867,16 @@
         <v>173</v>
       </c>
       <c r="B170">
-        <v>4.413848142948467</v>
+        <v>3.957148066938929</v>
       </c>
       <c r="C170">
-        <v>11.31593856678969</v>
+        <v>10.99223941406306</v>
       </c>
       <c r="D170">
-        <v>57.9040991803442</v>
+        <v>58.2627243944647</v>
       </c>
       <c r="E170">
-        <v>4.513489510565317</v>
+        <v>3.956602234435108</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -3884,16 +3884,16 @@
         <v>174</v>
       </c>
       <c r="B171">
-        <v>5.107784218926265</v>
+        <v>5.357937725617698</v>
       </c>
       <c r="C171">
-        <v>11.12654802226494</v>
+        <v>11.27764598524807</v>
       </c>
       <c r="D171">
-        <v>58.26260822318849</v>
+        <v>58.18181168868124</v>
       </c>
       <c r="E171">
-        <v>5.511869319544438</v>
+        <v>4.066885408817362</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -3901,16 +3901,16 @@
         <v>175</v>
       </c>
       <c r="B172">
-        <v>4.511463287790414</v>
+        <v>4.672013489359777</v>
       </c>
       <c r="C172">
-        <v>11.37991851368749</v>
+        <v>11.0697188262936</v>
       </c>
       <c r="D172">
-        <v>58.14158410686092</v>
+        <v>58.15042764458137</v>
       </c>
       <c r="E172">
-        <v>5.087645030874725</v>
+        <v>3.997654696371425</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -3918,16 +3918,16 @@
         <v>176</v>
       </c>
       <c r="B173">
-        <v>3.916138816387428</v>
+        <v>4.858720705657497</v>
       </c>
       <c r="C173">
-        <v>10.8696213471505</v>
+        <v>10.78690975819723</v>
       </c>
       <c r="D173">
-        <v>58.26700239821506</v>
+        <v>58.21503769350691</v>
       </c>
       <c r="E173">
-        <v>4.496805148627925</v>
+        <v>4.340236734815991</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -3935,16 +3935,16 @@
         <v>177</v>
       </c>
       <c r="B174">
-        <v>4.977972201626691</v>
+        <v>3.879183599905391</v>
       </c>
       <c r="C174">
-        <v>10.84213946514946</v>
+        <v>11.9173743746187</v>
       </c>
       <c r="D174">
-        <v>58.22509487885686</v>
+        <v>58.27748989291505</v>
       </c>
       <c r="E174">
-        <v>4.985786282171635</v>
+        <v>4.222992769241918</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -3952,16 +3952,16 @@
         <v>178</v>
       </c>
       <c r="B175">
-        <v>4.464327954890958</v>
+        <v>4.058898218162275</v>
       </c>
       <c r="C175">
-        <v>11.57947648390842</v>
+        <v>10.93375665098471</v>
       </c>
       <c r="D175">
-        <v>58.12757722893608</v>
+        <v>58.19671023584569</v>
       </c>
       <c r="E175">
-        <v>4.652103471370348</v>
+        <v>4.123740947470274</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -3969,16 +3969,16 @@
         <v>179</v>
       </c>
       <c r="B176">
-        <v>4.774881927872182</v>
+        <v>4.448697568945459</v>
       </c>
       <c r="C176">
-        <v>11.42169747613482</v>
+        <v>10.6930980157424</v>
       </c>
       <c r="D176">
-        <v>58.00231700940452</v>
+        <v>58.33105787981487</v>
       </c>
       <c r="E176">
-        <v>5.024789944236319</v>
+        <v>4.116629562174077</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -3986,16 +3986,16 @@
         <v>180</v>
       </c>
       <c r="B177">
-        <v>4.218422822348662</v>
+        <v>4.90644304684327</v>
       </c>
       <c r="C177">
-        <v>12.02068625196092</v>
+        <v>11.88879248796705</v>
       </c>
       <c r="D177">
-        <v>57.94775568715082</v>
+        <v>58.22814592706827</v>
       </c>
       <c r="E177">
-        <v>4.170083660163352</v>
+        <v>5.268700593922278</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -4003,16 +4003,16 @@
         <v>181</v>
       </c>
       <c r="B178">
-        <v>3.97256630504839</v>
+        <v>4.80240733871577</v>
       </c>
       <c r="C178">
-        <v>10.94373524848427</v>
+        <v>11.96771688363322</v>
       </c>
       <c r="D178">
-        <v>58.06804465669358</v>
+        <v>58.07010577274842</v>
       </c>
       <c r="E178">
-        <v>4.437452033777749</v>
+        <v>5.255842438939281</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -4020,16 +4020,16 @@
         <v>182</v>
       </c>
       <c r="B179">
-        <v>3.662192713572371</v>
+        <v>3.869358077881013</v>
       </c>
       <c r="C179">
-        <v>10.73356400418518</v>
+        <v>10.57530447226885</v>
       </c>
       <c r="D179">
-        <v>58.27607920415637</v>
+        <v>57.90253012157114</v>
       </c>
       <c r="E179">
-        <v>4.493694279527765</v>
+        <v>5.389524467368588</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -4037,16 +4037,16 @@
         <v>183</v>
       </c>
       <c r="B180">
-        <v>3.989025162270262</v>
+        <v>4.908883152807438</v>
       </c>
       <c r="C180">
-        <v>12.03260753281214</v>
+        <v>10.44720069870407</v>
       </c>
       <c r="D180">
-        <v>58.05778467048648</v>
+        <v>57.89009447410907</v>
       </c>
       <c r="E180">
-        <v>5.155470934897435</v>
+        <v>3.9592922416209</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -4054,16 +4054,16 @@
         <v>184</v>
       </c>
       <c r="B181">
-        <v>4.167411595218544</v>
+        <v>4.019469104268408</v>
       </c>
       <c r="C181">
-        <v>11.73264716869</v>
+        <v>11.51756383360456</v>
       </c>
       <c r="D181">
-        <v>58.29667406737926</v>
+        <v>58.13740502042789</v>
       </c>
       <c r="E181">
-        <v>5.246582536314231</v>
+        <v>4.934529226971828</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -4071,16 +4071,16 @@
         <v>185</v>
       </c>
       <c r="B182">
-        <v>4.943108071422698</v>
+        <v>3.766015419290502</v>
       </c>
       <c r="C182">
-        <v>10.50220031868463</v>
+        <v>11.05838285941235</v>
       </c>
       <c r="D182">
-        <v>58.20010430862562</v>
+        <v>57.95172773164145</v>
       </c>
       <c r="E182">
-        <v>4.321929998808208</v>
+        <v>4.428289455586676</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -4088,16 +4088,16 @@
         <v>186</v>
       </c>
       <c r="B183">
-        <v>4.95379354689231</v>
+        <v>3.903955181366035</v>
       </c>
       <c r="C183">
-        <v>11.82820001216314</v>
+        <v>10.92273811430717</v>
       </c>
       <c r="D183">
-        <v>58.03708823250565</v>
+        <v>58.36425517031542</v>
       </c>
       <c r="E183">
-        <v>4.630047778769034</v>
+        <v>4.318460330661988</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -4105,16 +4105,16 @@
         <v>187</v>
       </c>
       <c r="B184">
-        <v>4.298236559200835</v>
+        <v>3.873459121793744</v>
       </c>
       <c r="C184">
-        <v>10.65915398295772</v>
+        <v>11.6789916929283</v>
       </c>
       <c r="D184">
-        <v>57.94011673976323</v>
+        <v>57.97685422225243</v>
       </c>
       <c r="E184">
-        <v>4.073698975592784</v>
+        <v>4.335428577525468</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -4122,16 +4122,16 @@
         <v>188</v>
       </c>
       <c r="B185">
-        <v>4.250379554172611</v>
+        <v>4.501484062975</v>
       </c>
       <c r="C185">
-        <v>10.51051766201274</v>
+        <v>10.97543476481377</v>
       </c>
       <c r="D185">
-        <v>58.15448175397982</v>
+        <v>58.30562637588079</v>
       </c>
       <c r="E185">
-        <v>5.038136932385457</v>
+        <v>5.511369959884268</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -4139,16 +4139,16 @@
         <v>189</v>
       </c>
       <c r="B186">
-        <v>3.789094848119826</v>
+        <v>5.345255511541469</v>
       </c>
       <c r="C186">
-        <v>11.24693320204975</v>
+        <v>11.01441144215786</v>
       </c>
       <c r="D186">
-        <v>58.2701553398857</v>
+        <v>57.88183688293714</v>
       </c>
       <c r="E186">
-        <v>4.857018977694608</v>
+        <v>5.124879386497911</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -4156,16 +4156,16 @@
         <v>190</v>
       </c>
       <c r="B187">
-        <v>4.78606090989263</v>
+        <v>3.746332526209104</v>
       </c>
       <c r="C187">
-        <v>11.33603017357279</v>
+        <v>11.97096600841115</v>
       </c>
       <c r="D187">
-        <v>58.11426909759213</v>
+        <v>58.0676164873187</v>
       </c>
       <c r="E187">
-        <v>4.585129089368613</v>
+        <v>5.094281263451973</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -4173,16 +4173,16 @@
         <v>191</v>
       </c>
       <c r="B188">
-        <v>3.630166488684654</v>
+        <v>4.86024879358022</v>
       </c>
       <c r="C188">
-        <v>11.96519267147695</v>
+        <v>10.80341845474052</v>
       </c>
       <c r="D188">
-        <v>57.92522010753181</v>
+        <v>58.05909857069993</v>
       </c>
       <c r="E188">
-        <v>4.408994831678815</v>
+        <v>5.270006811761887</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -4190,16 +4190,16 @@
         <v>192</v>
       </c>
       <c r="B189">
-        <v>4.724048250361102</v>
+        <v>4.900877178246582</v>
       </c>
       <c r="C189">
-        <v>11.82078385490359</v>
+        <v>11.04478035393212</v>
       </c>
       <c r="D189">
-        <v>58.34111087254214</v>
+        <v>58.27136478441376</v>
       </c>
       <c r="E189">
-        <v>4.961728845406984</v>
+        <v>5.467882818469581</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -4207,16 +4207,16 @@
         <v>193</v>
       </c>
       <c r="B190">
-        <v>3.711119416223276</v>
+        <v>4.681528236941909</v>
       </c>
       <c r="C190">
-        <v>11.76796525145208</v>
+        <v>11.70562000212696</v>
       </c>
       <c r="D190">
-        <v>58.14570041165831</v>
+        <v>57.93291224835079</v>
       </c>
       <c r="E190">
-        <v>4.139824042033241</v>
+        <v>4.964456179782742</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -4224,16 +4224,16 @@
         <v>194</v>
       </c>
       <c r="B191">
-        <v>4.616994609705058</v>
+        <v>3.62919621480207</v>
       </c>
       <c r="C191">
-        <v>11.62727694571072</v>
+        <v>10.51837365481483</v>
       </c>
       <c r="D191">
-        <v>58.21855229932787</v>
+        <v>58.00318622023838</v>
       </c>
       <c r="E191">
-        <v>4.570077797818092</v>
+        <v>4.963157480842147</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -4241,16 +4241,16 @@
         <v>195</v>
       </c>
       <c r="B192">
-        <v>4.086190086290542</v>
+        <v>3.799810384794264</v>
       </c>
       <c r="C192">
-        <v>10.74581246498064</v>
+        <v>11.32775652181935</v>
       </c>
       <c r="D192">
-        <v>58.19573299360207</v>
+        <v>58.16041661323246</v>
       </c>
       <c r="E192">
-        <v>4.240323980687292</v>
+        <v>5.022777130812081</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -4258,16 +4258,16 @@
         <v>196</v>
       </c>
       <c r="B193">
-        <v>3.778074383078823</v>
+        <v>4.708548663313516</v>
       </c>
       <c r="C193">
-        <v>11.06729097616003</v>
+        <v>11.48241816425793</v>
       </c>
       <c r="D193">
-        <v>58.11122099013663</v>
+        <v>57.91559835158014</v>
       </c>
       <c r="E193">
-        <v>4.12266811238665</v>
+        <v>5.24791396968012</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -4275,16 +4275,16 @@
         <v>197</v>
       </c>
       <c r="B194">
-        <v>4.739990933971864</v>
+        <v>4.047244769004164</v>
       </c>
       <c r="C194">
-        <v>10.54474123176728</v>
+        <v>11.9544957795033</v>
       </c>
       <c r="D194">
-        <v>57.88563541862897</v>
+        <v>58.02645297020218</v>
       </c>
       <c r="E194">
-        <v>4.646406108741412</v>
+        <v>4.373606284948889</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -4292,16 +4292,16 @@
         <v>198</v>
       </c>
       <c r="B195">
-        <v>4.747586235914038</v>
+        <v>3.695845272789291</v>
       </c>
       <c r="C195">
-        <v>10.54606897281035</v>
+        <v>11.43960939085195</v>
       </c>
       <c r="D195">
-        <v>57.89790764649764</v>
+        <v>57.94916489623225</v>
       </c>
       <c r="E195">
-        <v>4.591851028508266</v>
+        <v>5.284721265756035</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -4309,16 +4309,16 @@
         <v>199</v>
       </c>
       <c r="B196">
-        <v>3.998811421411794</v>
+        <v>5.042982132973973</v>
       </c>
       <c r="C196">
-        <v>10.65340538254843</v>
+        <v>11.8019535333152</v>
       </c>
       <c r="D196">
-        <v>57.89288900706848</v>
+        <v>58.36533666840418</v>
       </c>
       <c r="E196">
-        <v>4.216993707637991</v>
+        <v>4.819057262176062</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -4326,16 +4326,16 @@
         <v>200</v>
       </c>
       <c r="B197">
-        <v>5.114399382175607</v>
+        <v>5.155803226574747</v>
       </c>
       <c r="C197">
-        <v>11.28417763309868</v>
+        <v>11.85742850147574</v>
       </c>
       <c r="D197">
-        <v>58.00077968783313</v>
+        <v>58.1086318547852</v>
       </c>
       <c r="E197">
-        <v>4.909025965232378</v>
+        <v>3.985275943790552</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -4343,16 +4343,16 @@
         <v>201</v>
       </c>
       <c r="B198">
-        <v>5.413784469287366</v>
+        <v>4.68953064577143</v>
       </c>
       <c r="C198">
-        <v>10.95952389789693</v>
+        <v>11.62404362893826</v>
       </c>
       <c r="D198">
-        <v>58.3089140011118</v>
+        <v>57.96074001849445</v>
       </c>
       <c r="E198">
-        <v>4.585140003836924</v>
+        <v>5.4111022814162</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -4360,16 +4360,16 @@
         <v>202</v>
       </c>
       <c r="B199">
-        <v>4.684003228941163</v>
+        <v>3.809598418045775</v>
       </c>
       <c r="C199">
-        <v>10.84393052923461</v>
+        <v>11.03363320244439</v>
       </c>
       <c r="D199">
-        <v>58.35318102179378</v>
+        <v>58.26226219983565</v>
       </c>
       <c r="E199">
-        <v>5.462879052609913</v>
+        <v>4.901741297165547</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -4377,16 +4377,16 @@
         <v>203</v>
       </c>
       <c r="B200">
-        <v>4.900469911682878</v>
+        <v>5.035035833554659</v>
       </c>
       <c r="C200">
-        <v>10.92261494224622</v>
+        <v>11.98904568114161</v>
       </c>
       <c r="D200">
-        <v>57.92849877960999</v>
+        <v>58.10253180284654</v>
       </c>
       <c r="E200">
-        <v>5.251762390529578</v>
+        <v>4.478764063882009</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -4394,16 +4394,16 @@
         <v>204</v>
       </c>
       <c r="B201">
-        <v>4.483194896078555</v>
+        <v>4.824862543304049</v>
       </c>
       <c r="C201">
-        <v>10.74278458134518</v>
+        <v>11.42618798247145</v>
       </c>
       <c r="D201">
-        <v>57.93969822365695</v>
+        <v>58.19928269888145</v>
       </c>
       <c r="E201">
-        <v>4.174463352133113</v>
+        <v>4.928022131252842</v>
       </c>
     </row>
   </sheetData>

--- a/FFT on froth/data_dep_augm_Pb.xlsx
+++ b/FFT on froth/data_dep_augm_Pb.xlsx
@@ -1011,16 +1011,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>2.757381616354195</v>
+        <v>2.58256150910238</v>
       </c>
       <c r="C2">
-        <v>11.34818044350621</v>
+        <v>10.68103600712687</v>
       </c>
       <c r="D2">
-        <v>46.01319356256182</v>
+        <v>46.58581602381636</v>
       </c>
       <c r="E2">
-        <v>5.18740803740175</v>
+        <v>3.755116078097543</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1028,16 +1028,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>2.982826840804259</v>
+        <v>2.54414736477497</v>
       </c>
       <c r="C3">
-        <v>12.00019782358377</v>
+        <v>10.89163121393616</v>
       </c>
       <c r="D3">
-        <v>46.46099704888201</v>
+        <v>47.48271176858924</v>
       </c>
       <c r="E3">
-        <v>5.032699353401074</v>
+        <v>3.786347900411333</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1045,16 +1045,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>4.175151930805751</v>
+        <v>2.570213028233522</v>
       </c>
       <c r="C4">
-        <v>10.92278091496126</v>
+        <v>10.92663140890832</v>
       </c>
       <c r="D4">
-        <v>46.4377439217233</v>
+        <v>46.58784391059516</v>
       </c>
       <c r="E4">
-        <v>4.814194864931221</v>
+        <v>3.660131453753828</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1062,16 +1062,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>2.614217870638722</v>
+        <v>2.604223573296413</v>
       </c>
       <c r="C5">
-        <v>11.47085414969558</v>
+        <v>10.76504660131224</v>
       </c>
       <c r="D5">
-        <v>46.30436970603042</v>
+        <v>46.72227051560924</v>
       </c>
       <c r="E5">
-        <v>4.400222698399634</v>
+        <v>3.673735823942153</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1079,16 +1079,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>3.594237540696479</v>
+        <v>2.599669559897779</v>
       </c>
       <c r="C6">
-        <v>12.00447796216923</v>
+        <v>10.61933553150674</v>
       </c>
       <c r="D6">
-        <v>46.45345316521495</v>
+        <v>46.28802109389356</v>
       </c>
       <c r="E6">
-        <v>4.020930584336943</v>
+        <v>3.677885400249278</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1096,16 +1096,16 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>3.514262304584879</v>
+        <v>2.593260979457655</v>
       </c>
       <c r="C7">
-        <v>11.5811578057191</v>
+        <v>10.66153625773054</v>
       </c>
       <c r="D7">
-        <v>46.48734520750948</v>
+        <v>46.53985635251998</v>
       </c>
       <c r="E7">
-        <v>4.069729670414358</v>
+        <v>3.692746368025274</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1113,16 +1113,16 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>3.301793225687989</v>
+        <v>2.650117168092158</v>
       </c>
       <c r="C8">
-        <v>11.30046174109061</v>
+        <v>11.06174368845731</v>
       </c>
       <c r="D8">
-        <v>46.25297815584412</v>
+        <v>46.30320094465038</v>
       </c>
       <c r="E8">
-        <v>5.037614972785901</v>
+        <v>3.753184324239106</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1130,16 +1130,16 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>2.913102966812922</v>
+        <v>2.548806275095592</v>
       </c>
       <c r="C9">
-        <v>10.97120648772685</v>
+        <v>10.67851297706374</v>
       </c>
       <c r="D9">
-        <v>46.19638723953521</v>
+        <v>46.28369858575205</v>
       </c>
       <c r="E9">
-        <v>4.441609206053489</v>
+        <v>3.6523890428677</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -1147,16 +1147,16 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>3.055569568915269</v>
+        <v>2.641825419634544</v>
       </c>
       <c r="C10">
-        <v>11.22374693546434</v>
+        <v>10.84176860720877</v>
       </c>
       <c r="D10">
-        <v>46.03498947726427</v>
+        <v>46.64861145105698</v>
       </c>
       <c r="E10">
-        <v>4.10019288601179</v>
+        <v>3.75362251948584</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1164,16 +1164,16 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>2.934249914105143</v>
+        <v>2.55359336498207</v>
       </c>
       <c r="C11">
-        <v>11.01683310061246</v>
+        <v>11.04997873026008</v>
       </c>
       <c r="D11">
-        <v>46.42799142722718</v>
+        <v>46.26957632612849</v>
       </c>
       <c r="E11">
-        <v>4.020586157963145</v>
+        <v>3.745227537098865</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -1181,16 +1181,16 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>3.82131105330361</v>
+        <v>2.600578798307525</v>
       </c>
       <c r="C12">
-        <v>10.62220116760111</v>
+        <v>11.04712763220408</v>
       </c>
       <c r="D12">
-        <v>46.26753597185883</v>
+        <v>46.98344763478632</v>
       </c>
       <c r="E12">
-        <v>4.387803451731176</v>
+        <v>3.723283696666905</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1198,16 +1198,16 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>4.028364640768604</v>
+        <v>2.629184534657166</v>
       </c>
       <c r="C13">
-        <v>11.25937041514192</v>
+        <v>10.90873657551156</v>
       </c>
       <c r="D13">
-        <v>46.17317012620253</v>
+        <v>46.05659073349453</v>
       </c>
       <c r="E13">
-        <v>3.935556289970697</v>
+        <v>3.704113483994554</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1215,16 +1215,16 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>2.925272923525985</v>
+        <v>2.561870257464012</v>
       </c>
       <c r="C14">
-        <v>10.60855475057293</v>
+        <v>10.72241121232244</v>
       </c>
       <c r="D14">
-        <v>46.47986194308895</v>
+        <v>47.31291757511123</v>
       </c>
       <c r="E14">
-        <v>4.833983337632436</v>
+        <v>3.781933838204835</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1232,16 +1232,16 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>3.386622972097432</v>
+        <v>2.557049910086868</v>
       </c>
       <c r="C15">
-        <v>11.08099938433673</v>
+        <v>10.72769699710623</v>
       </c>
       <c r="D15">
-        <v>46.47981235461592</v>
+        <v>46.00919289115228</v>
       </c>
       <c r="E15">
-        <v>4.967372258052427</v>
+        <v>3.737422979773321</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1249,16 +1249,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>3.676922642281911</v>
+        <v>2.556733915239312</v>
       </c>
       <c r="C16">
-        <v>11.03203985931743</v>
+        <v>10.82774163212236</v>
       </c>
       <c r="D16">
-        <v>46.31840177473769</v>
+        <v>46.32381718929791</v>
       </c>
       <c r="E16">
-        <v>4.122027897474188</v>
+        <v>3.681617505769472</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1266,16 +1266,16 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>4.054369745072236</v>
+        <v>2.559491400723196</v>
       </c>
       <c r="C17">
-        <v>10.64301082091363</v>
+        <v>10.68295557179106</v>
       </c>
       <c r="D17">
-        <v>46.22337543213364</v>
+        <v>47.16016326519749</v>
       </c>
       <c r="E17">
-        <v>3.886819591150367</v>
+        <v>3.675548884786602</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1283,16 +1283,16 @@
         <v>21</v>
       </c>
       <c r="B18">
-        <v>2.788202603885348</v>
+        <v>2.550658765420137</v>
       </c>
       <c r="C18">
-        <v>10.72234045716999</v>
+        <v>10.92583158849531</v>
       </c>
       <c r="D18">
-        <v>46.3562172565642</v>
+        <v>47.11647907089851</v>
       </c>
       <c r="E18">
-        <v>4.074629615270285</v>
+        <v>3.730256873265933</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1300,16 +1300,16 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>3.330924439716487</v>
+        <v>2.650710404041248</v>
       </c>
       <c r="C19">
-        <v>11.63895545119737</v>
+        <v>10.59589659128948</v>
       </c>
       <c r="D19">
-        <v>46.135627845131</v>
+        <v>47.26227260295097</v>
       </c>
       <c r="E19">
-        <v>3.657212424325628</v>
+        <v>3.739509505659933</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1317,16 +1317,16 @@
         <v>23</v>
       </c>
       <c r="B20">
-        <v>3.672371732657828</v>
+        <v>2.650294246698798</v>
       </c>
       <c r="C20">
-        <v>11.57244495757037</v>
+        <v>10.65546310658208</v>
       </c>
       <c r="D20">
-        <v>46.345918402164</v>
+        <v>46.29039718627949</v>
       </c>
       <c r="E20">
-        <v>4.208668964392125</v>
+        <v>3.660088334141127</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1334,16 +1334,16 @@
         <v>24</v>
       </c>
       <c r="B21">
-        <v>4.237659598023563</v>
+        <v>2.654564218697943</v>
       </c>
       <c r="C21">
-        <v>11.72224111786595</v>
+        <v>10.75504716822418</v>
       </c>
       <c r="D21">
-        <v>46.26680354789194</v>
+        <v>46.20605042871782</v>
       </c>
       <c r="E21">
-        <v>4.138968455281173</v>
+        <v>3.672233082413846</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1351,16 +1351,16 @@
         <v>25</v>
       </c>
       <c r="B22">
-        <v>2.571204215697343</v>
+        <v>2.551712666989447</v>
       </c>
       <c r="C22">
-        <v>10.74314123243207</v>
+        <v>10.90411587159767</v>
       </c>
       <c r="D22">
-        <v>46.48266356155609</v>
+        <v>47.24339516239774</v>
       </c>
       <c r="E22">
-        <v>5.105298746463955</v>
+        <v>3.729795756734614</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1368,16 +1368,16 @@
         <v>26</v>
       </c>
       <c r="B23">
-        <v>3.180448319991008</v>
+        <v>2.583793571330213</v>
       </c>
       <c r="C23">
-        <v>10.69938455137191</v>
+        <v>10.88221104327561</v>
       </c>
       <c r="D23">
-        <v>46.27436411873408</v>
+        <v>47.00206597484392</v>
       </c>
       <c r="E23">
-        <v>4.754224334668828</v>
+        <v>3.691950768231382</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1385,16 +1385,16 @@
         <v>27</v>
       </c>
       <c r="B24">
-        <v>3.43807892019269</v>
+        <v>2.600508816485961</v>
       </c>
       <c r="C24">
-        <v>11.37389428721096</v>
+        <v>10.70310504191912</v>
       </c>
       <c r="D24">
-        <v>46.31685594305563</v>
+        <v>46.02448298515465</v>
       </c>
       <c r="E24">
-        <v>3.894551502699747</v>
+        <v>3.733276056614396</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1402,16 +1402,16 @@
         <v>28</v>
       </c>
       <c r="B25">
-        <v>2.93627331882577</v>
+        <v>2.589475006866686</v>
       </c>
       <c r="C25">
-        <v>11.52478946848889</v>
+        <v>10.68125960277979</v>
       </c>
       <c r="D25">
-        <v>46.40562211201954</v>
+        <v>46.28681344860518</v>
       </c>
       <c r="E25">
-        <v>4.878272815983753</v>
+        <v>3.670622982616198</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1419,16 +1419,16 @@
         <v>29</v>
       </c>
       <c r="B26">
-        <v>4.090800738133553</v>
+        <v>2.646628326003739</v>
       </c>
       <c r="C26">
-        <v>12.10005023291877</v>
+        <v>10.77562101083581</v>
       </c>
       <c r="D26">
-        <v>46.34996229383756</v>
+        <v>47.25678634894958</v>
       </c>
       <c r="E26">
-        <v>3.841276832760108</v>
+        <v>3.664661646019177</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1436,16 +1436,16 @@
         <v>30</v>
       </c>
       <c r="B27">
-        <v>3.592907172664678</v>
+        <v>2.592073593679496</v>
       </c>
       <c r="C27">
-        <v>10.86967680294519</v>
+        <v>10.97932358567583</v>
       </c>
       <c r="D27">
-        <v>46.20269641780515</v>
+        <v>47.32772509109261</v>
       </c>
       <c r="E27">
-        <v>4.008180249474557</v>
+        <v>3.733263468503889</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1453,16 +1453,16 @@
         <v>31</v>
       </c>
       <c r="B28">
-        <v>3.084143749116077</v>
+        <v>2.630857125030633</v>
       </c>
       <c r="C28">
-        <v>12.05066345790545</v>
+        <v>10.60060007213122</v>
       </c>
       <c r="D28">
-        <v>46.29979798317702</v>
+        <v>46.17412547342069</v>
       </c>
       <c r="E28">
-        <v>3.879494773992772</v>
+        <v>3.788440193091073</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1470,16 +1470,16 @@
         <v>32</v>
       </c>
       <c r="B29">
-        <v>2.822130497059981</v>
+        <v>2.589430433529857</v>
       </c>
       <c r="C29">
-        <v>11.86452609624654</v>
+        <v>10.84478298383023</v>
       </c>
       <c r="D29">
-        <v>46.31757453524999</v>
+        <v>46.69877518660898</v>
       </c>
       <c r="E29">
-        <v>4.421262529697543</v>
+        <v>3.714099609395144</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -1487,16 +1487,16 @@
         <v>33</v>
       </c>
       <c r="B30">
-        <v>2.71574199200735</v>
+        <v>2.560869272271005</v>
       </c>
       <c r="C30">
-        <v>10.82364162658937</v>
+        <v>10.91126170744799</v>
       </c>
       <c r="D30">
-        <v>46.38545331514937</v>
+        <v>47.35114134796419</v>
       </c>
       <c r="E30">
-        <v>4.6250926972904</v>
+        <v>3.704859702222892</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -1504,16 +1504,16 @@
         <v>34</v>
       </c>
       <c r="B31">
-        <v>2.82600409831989</v>
+        <v>2.603398426373092</v>
       </c>
       <c r="C31">
-        <v>11.10571566910315</v>
+        <v>10.81775622974355</v>
       </c>
       <c r="D31">
-        <v>46.10741298144301</v>
+        <v>47.21782327600773</v>
       </c>
       <c r="E31">
-        <v>5.009497042214591</v>
+        <v>3.70300718550788</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -1521,16 +1521,16 @@
         <v>35</v>
       </c>
       <c r="B32">
-        <v>4.196300381966299</v>
+        <v>2.653001613254042</v>
       </c>
       <c r="C32">
-        <v>10.97210754680191</v>
+        <v>10.74030803156876</v>
       </c>
       <c r="D32">
-        <v>46.04024453239744</v>
+        <v>47.39434517519116</v>
       </c>
       <c r="E32">
-        <v>3.904850641696084</v>
+        <v>3.719496892997976</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -1538,16 +1538,16 @@
         <v>36</v>
       </c>
       <c r="B33">
-        <v>3.60857846457635</v>
+        <v>2.602244276064304</v>
       </c>
       <c r="C33">
-        <v>11.13883692243338</v>
+        <v>10.76318375259006</v>
       </c>
       <c r="D33">
-        <v>46.16769150555169</v>
+        <v>46.43467583672911</v>
       </c>
       <c r="E33">
-        <v>3.705416532275292</v>
+        <v>3.71858592374014</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -1555,16 +1555,16 @@
         <v>37</v>
       </c>
       <c r="B34">
-        <v>2.540958454180367</v>
+        <v>2.598873840136603</v>
       </c>
       <c r="C34">
-        <v>11.80567081369132</v>
+        <v>10.67916702315436</v>
       </c>
       <c r="D34">
-        <v>46.41189478621228</v>
+        <v>46.99777666122691</v>
       </c>
       <c r="E34">
-        <v>3.784222445929775</v>
+        <v>3.636809967700905</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1572,16 +1572,16 @@
         <v>38</v>
       </c>
       <c r="B35">
-        <v>3.308018927010258</v>
+        <v>2.55178265487557</v>
       </c>
       <c r="C35">
-        <v>11.93298261833351</v>
+        <v>10.8606364694216</v>
       </c>
       <c r="D35">
-        <v>46.29611384839371</v>
+        <v>46.1768804722652</v>
       </c>
       <c r="E35">
-        <v>4.629899070186363</v>
+        <v>3.727137156485304</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1589,16 +1589,16 @@
         <v>39</v>
       </c>
       <c r="B36">
-        <v>4.25596689462573</v>
+        <v>2.614513154686683</v>
       </c>
       <c r="C36">
-        <v>11.12689285584495</v>
+        <v>10.8389340023949</v>
       </c>
       <c r="D36">
-        <v>46.19613759880554</v>
+        <v>47.53255612050373</v>
       </c>
       <c r="E36">
-        <v>4.55940537409735</v>
+        <v>3.744239577145343</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1606,16 +1606,16 @@
         <v>40</v>
       </c>
       <c r="B37">
-        <v>2.619384236476705</v>
+        <v>2.60359079494057</v>
       </c>
       <c r="C37">
-        <v>10.99748544667396</v>
+        <v>10.72801037124384</v>
       </c>
       <c r="D37">
-        <v>46.32580631836573</v>
+        <v>46.35460731850331</v>
       </c>
       <c r="E37">
-        <v>4.571833702483235</v>
+        <v>3.676135768422491</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -1623,16 +1623,16 @@
         <v>41</v>
       </c>
       <c r="B38">
-        <v>3.480484518774445</v>
+        <v>2.556633193766271</v>
       </c>
       <c r="C38">
-        <v>10.9879717371019</v>
+        <v>10.66172647921558</v>
       </c>
       <c r="D38">
-        <v>46.16110004527254</v>
+        <v>46.87847625716012</v>
       </c>
       <c r="E38">
-        <v>3.97699589294626</v>
+        <v>3.649399766036487</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1640,16 +1640,16 @@
         <v>42</v>
       </c>
       <c r="B39">
-        <v>3.356870769909786</v>
+        <v>2.564304577753334</v>
       </c>
       <c r="C39">
-        <v>11.40022919936526</v>
+        <v>10.72387369246011</v>
       </c>
       <c r="D39">
-        <v>46.07143551782704</v>
+        <v>47.00270519736701</v>
       </c>
       <c r="E39">
-        <v>5.211847660342093</v>
+        <v>3.624033721677288</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1657,16 +1657,16 @@
         <v>43</v>
       </c>
       <c r="B40">
-        <v>3.78413977753584</v>
+        <v>2.60091604372835</v>
       </c>
       <c r="C40">
-        <v>11.7797687161634</v>
+        <v>10.78689959505027</v>
       </c>
       <c r="D40">
-        <v>46.03393621453882</v>
+        <v>47.10255222154796</v>
       </c>
       <c r="E40">
-        <v>4.938367739941548</v>
+        <v>3.634140222513152</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1674,16 +1674,16 @@
         <v>44</v>
       </c>
       <c r="B41">
-        <v>4.307380152417686</v>
+        <v>2.654654058993977</v>
       </c>
       <c r="C41">
-        <v>10.88997015310732</v>
+        <v>11.06899629150062</v>
       </c>
       <c r="D41">
-        <v>46.417299515616</v>
+        <v>46.99680583939251</v>
       </c>
       <c r="E41">
-        <v>4.901354179015323</v>
+        <v>3.714013088837096</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -1691,16 +1691,16 @@
         <v>45</v>
       </c>
       <c r="B42">
-        <v>4.258911390269409</v>
+        <v>2.556793226511651</v>
       </c>
       <c r="C42">
-        <v>10.94480328129828</v>
+        <v>10.76997760561443</v>
       </c>
       <c r="D42">
-        <v>46.31304271970593</v>
+        <v>47.50174850617359</v>
       </c>
       <c r="E42">
-        <v>4.900265632051599</v>
+        <v>3.768564049730348</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1708,16 +1708,16 @@
         <v>46</v>
       </c>
       <c r="B43">
-        <v>4.169073379586525</v>
+        <v>2.552841781954729</v>
       </c>
       <c r="C43">
-        <v>11.45355002372524</v>
+        <v>10.98053789240228</v>
       </c>
       <c r="D43">
-        <v>46.33312792289466</v>
+        <v>46.08815641503941</v>
       </c>
       <c r="E43">
-        <v>4.25633760881104</v>
+        <v>3.779235383186696</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1725,16 +1725,16 @@
         <v>47</v>
       </c>
       <c r="B44">
-        <v>4.130246429696141</v>
+        <v>2.547614264298266</v>
       </c>
       <c r="C44">
-        <v>11.15358813216524</v>
+        <v>11.05881612552478</v>
       </c>
       <c r="D44">
-        <v>46.17452669738267</v>
+        <v>46.09903517766578</v>
       </c>
       <c r="E44">
-        <v>5.056288935009409</v>
+        <v>3.661166277435166</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1742,16 +1742,16 @@
         <v>48</v>
       </c>
       <c r="B45">
-        <v>4.150630296407892</v>
+        <v>2.628667372781954</v>
       </c>
       <c r="C45">
-        <v>11.67556314862849</v>
+        <v>10.70933101418215</v>
       </c>
       <c r="D45">
-        <v>46.12504703567567</v>
+        <v>47.51269348603635</v>
       </c>
       <c r="E45">
-        <v>3.721452614608772</v>
+        <v>3.649625323586938</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1759,16 +1759,16 @@
         <v>49</v>
       </c>
       <c r="B46">
-        <v>3.969120452955463</v>
+        <v>2.594804735420124</v>
       </c>
       <c r="C46">
-        <v>11.53996736703745</v>
+        <v>10.98442308055112</v>
       </c>
       <c r="D46">
-        <v>46.37464958547724</v>
+        <v>46.14206626589868</v>
       </c>
       <c r="E46">
-        <v>4.830514549544301</v>
+        <v>3.756349453083424</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1776,16 +1776,16 @@
         <v>50</v>
       </c>
       <c r="B47">
-        <v>3.235724124300606</v>
+        <v>2.647632012261401</v>
       </c>
       <c r="C47">
-        <v>11.93695248584653</v>
+        <v>10.8269872091617</v>
       </c>
       <c r="D47">
-        <v>46.3296690808125</v>
+        <v>46.48193582603754</v>
       </c>
       <c r="E47">
-        <v>4.728842929834507</v>
+        <v>3.729760659551504</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1793,16 +1793,16 @@
         <v>51</v>
       </c>
       <c r="B48">
-        <v>4.059358303617003</v>
+        <v>2.623326352886251</v>
       </c>
       <c r="C48">
-        <v>11.99675704448542</v>
+        <v>10.91353029595872</v>
       </c>
       <c r="D48">
-        <v>46.2199892399174</v>
+        <v>46.52328995160956</v>
       </c>
       <c r="E48">
-        <v>4.062600221915793</v>
+        <v>3.761960247868945</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -1810,16 +1810,16 @@
         <v>52</v>
       </c>
       <c r="B49">
-        <v>3.015053506743306</v>
+        <v>2.622906659634782</v>
       </c>
       <c r="C49">
-        <v>12.16860826989706</v>
+        <v>10.64655073910012</v>
       </c>
       <c r="D49">
-        <v>46.27477754208107</v>
+        <v>46.66406936671893</v>
       </c>
       <c r="E49">
-        <v>3.79500023336464</v>
+        <v>3.771355405406957</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1827,16 +1827,16 @@
         <v>53</v>
       </c>
       <c r="B50">
-        <v>3.710844746845255</v>
+        <v>2.584990092836504</v>
       </c>
       <c r="C50">
-        <v>11.08401730648536</v>
+        <v>10.73068298684463</v>
       </c>
       <c r="D50">
-        <v>46.2013018299788</v>
+        <v>46.57766307195805</v>
       </c>
       <c r="E50">
-        <v>4.814702378121113</v>
+        <v>3.712812880674368</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -1844,16 +1844,16 @@
         <v>54</v>
       </c>
       <c r="B51">
-        <v>4.041460869075729</v>
+        <v>2.641710284280726</v>
       </c>
       <c r="C51">
-        <v>11.0817904353982</v>
+        <v>10.72754152122745</v>
       </c>
       <c r="D51">
-        <v>46.07031398405795</v>
+        <v>46.12541817501975</v>
       </c>
       <c r="E51">
-        <v>4.594421537848532</v>
+        <v>3.647267971872106</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -1861,16 +1861,16 @@
         <v>55</v>
       </c>
       <c r="B52">
-        <v>3.503924007346509</v>
+        <v>2.619261811566456</v>
       </c>
       <c r="C52">
-        <v>11.38333410554071</v>
+        <v>10.63189950962369</v>
       </c>
       <c r="D52">
-        <v>46.43033150370334</v>
+        <v>47.34387321263432</v>
       </c>
       <c r="E52">
-        <v>4.572573876602213</v>
+        <v>3.765845430410293</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -1878,16 +1878,16 @@
         <v>56</v>
       </c>
       <c r="B53">
-        <v>3.023417079382898</v>
+        <v>2.607658901263305</v>
       </c>
       <c r="C53">
-        <v>11.12650877579357</v>
+        <v>10.80865906112582</v>
       </c>
       <c r="D53">
-        <v>46.12110736287037</v>
+        <v>47.21648545694557</v>
       </c>
       <c r="E53">
-        <v>3.961541758077681</v>
+        <v>3.730387984247497</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1895,16 +1895,16 @@
         <v>57</v>
       </c>
       <c r="B54">
-        <v>3.575235566742747</v>
+        <v>2.58175421734585</v>
       </c>
       <c r="C54">
-        <v>11.68166660931919</v>
+        <v>10.6789760241639</v>
       </c>
       <c r="D54">
-        <v>46.21621989435784</v>
+        <v>47.46673239506816</v>
       </c>
       <c r="E54">
-        <v>4.787090444763534</v>
+        <v>3.62018466772023</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1912,16 +1912,16 @@
         <v>58</v>
       </c>
       <c r="B55">
-        <v>2.742316611609952</v>
+        <v>2.596201063693357</v>
       </c>
       <c r="C55">
-        <v>11.43948298838299</v>
+        <v>10.75347581606495</v>
       </c>
       <c r="D55">
-        <v>46.23409475894199</v>
+        <v>47.48487239885794</v>
       </c>
       <c r="E55">
-        <v>4.708447367070358</v>
+        <v>3.736693709903987</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -1929,16 +1929,16 @@
         <v>59</v>
       </c>
       <c r="B56">
-        <v>3.794735855572295</v>
+        <v>2.551781205449266</v>
       </c>
       <c r="C56">
-        <v>11.05862539657176</v>
+        <v>10.66894216929348</v>
       </c>
       <c r="D56">
-        <v>46.20595693922869</v>
+        <v>46.49960849925102</v>
       </c>
       <c r="E56">
-        <v>4.038071669623157</v>
+        <v>3.681738904246724</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -1946,16 +1946,16 @@
         <v>60</v>
       </c>
       <c r="B57">
-        <v>2.659353061001493</v>
+        <v>2.576576985541994</v>
       </c>
       <c r="C57">
-        <v>11.60292953944642</v>
+        <v>10.9243666251643</v>
       </c>
       <c r="D57">
-        <v>46.16733119414872</v>
+        <v>46.21473026467495</v>
       </c>
       <c r="E57">
-        <v>4.153015218672889</v>
+        <v>3.772192289641655</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1963,16 +1963,16 @@
         <v>61</v>
       </c>
       <c r="B58">
-        <v>3.756862453225539</v>
+        <v>2.610139072512259</v>
       </c>
       <c r="C58">
-        <v>11.09732708152296</v>
+        <v>10.93865377094709</v>
       </c>
       <c r="D58">
-        <v>46.16606444043051</v>
+        <v>46.56827953160765</v>
       </c>
       <c r="E58">
-        <v>5.13124118240969</v>
+        <v>3.670584971355787</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1980,16 +1980,16 @@
         <v>62</v>
       </c>
       <c r="B59">
-        <v>2.664643853928094</v>
+        <v>2.595801771155505</v>
       </c>
       <c r="C59">
-        <v>11.87618790479138</v>
+        <v>10.76041326583142</v>
       </c>
       <c r="D59">
-        <v>46.29578416053641</v>
+        <v>46.47008034189695</v>
       </c>
       <c r="E59">
-        <v>3.62868772153239</v>
+        <v>3.697990238798968</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1997,16 +1997,16 @@
         <v>63</v>
       </c>
       <c r="B60">
-        <v>4.296107716116662</v>
+        <v>2.641009932811215</v>
       </c>
       <c r="C60">
-        <v>10.85197752095363</v>
+        <v>10.77905857773994</v>
       </c>
       <c r="D60">
-        <v>46.10761217625337</v>
+        <v>47.32240661010093</v>
       </c>
       <c r="E60">
-        <v>4.309811320246655</v>
+        <v>3.773083848353928</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2014,16 +2014,16 @@
         <v>64</v>
       </c>
       <c r="B61">
-        <v>4.221976386593653</v>
+        <v>2.607250001832157</v>
       </c>
       <c r="C61">
-        <v>11.73686301534168</v>
+        <v>10.87950839877277</v>
       </c>
       <c r="D61">
-        <v>46.21521799426642</v>
+        <v>46.29038616998417</v>
       </c>
       <c r="E61">
-        <v>4.825339511438282</v>
+        <v>3.664696844370724</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2031,16 +2031,16 @@
         <v>65</v>
       </c>
       <c r="B62">
-        <v>2.576034879446234</v>
+        <v>2.612063163577224</v>
       </c>
       <c r="C62">
-        <v>10.66455303453423</v>
+        <v>10.72410109931857</v>
       </c>
       <c r="D62">
-        <v>46.11615457391158</v>
+        <v>47.11793376647456</v>
       </c>
       <c r="E62">
-        <v>4.579861539883749</v>
+        <v>3.706504212200197</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -2048,16 +2048,16 @@
         <v>66</v>
       </c>
       <c r="B63">
-        <v>3.868979538421561</v>
+        <v>2.621651909408208</v>
       </c>
       <c r="C63">
-        <v>11.54576150816269</v>
+        <v>11.02583488695882</v>
       </c>
       <c r="D63">
-        <v>46.12489905688923</v>
+        <v>46.59003977535916</v>
       </c>
       <c r="E63">
-        <v>4.367366989807302</v>
+        <v>3.704622553711928</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -2065,16 +2065,16 @@
         <v>67</v>
       </c>
       <c r="B64">
-        <v>3.553343483052684</v>
+        <v>2.562752944208878</v>
       </c>
       <c r="C64">
-        <v>10.65678867957886</v>
+        <v>10.69369195798826</v>
       </c>
       <c r="D64">
-        <v>46.05001549273599</v>
+        <v>47.14984258477266</v>
       </c>
       <c r="E64">
-        <v>4.35426108439979</v>
+        <v>3.760083170337436</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2082,16 +2082,16 @@
         <v>68</v>
       </c>
       <c r="B65">
-        <v>2.720457849578082</v>
+        <v>2.599134377418176</v>
       </c>
       <c r="C65">
-        <v>11.63409671989015</v>
+        <v>10.61200684320634</v>
       </c>
       <c r="D65">
-        <v>46.47767179165287</v>
+        <v>46.44081645334361</v>
       </c>
       <c r="E65">
-        <v>4.772924159599397</v>
+        <v>3.68248982282195</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2099,16 +2099,16 @@
         <v>69</v>
       </c>
       <c r="B66">
-        <v>3.165339480338374</v>
+        <v>2.65343572180196</v>
       </c>
       <c r="C66">
-        <v>11.70508135876184</v>
+        <v>10.92789242095471</v>
       </c>
       <c r="D66">
-        <v>46.3664220058999</v>
+        <v>46.65534720014221</v>
       </c>
       <c r="E66">
-        <v>4.583296895798471</v>
+        <v>3.758554194722445</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -2116,16 +2116,16 @@
         <v>70</v>
       </c>
       <c r="B67">
-        <v>2.837678981446741</v>
+        <v>2.578742582394068</v>
       </c>
       <c r="C67">
-        <v>11.12013969175339</v>
+        <v>11.08066480571343</v>
       </c>
       <c r="D67">
-        <v>46.1662310528887</v>
+        <v>46.90489610333881</v>
       </c>
       <c r="E67">
-        <v>3.649722112899334</v>
+        <v>3.689843624617142</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -2133,16 +2133,16 @@
         <v>71</v>
       </c>
       <c r="B68">
-        <v>3.238075982543603</v>
+        <v>2.594164376753039</v>
       </c>
       <c r="C68">
-        <v>12.14017609685584</v>
+        <v>10.85906901573185</v>
       </c>
       <c r="D68">
-        <v>46.22661414649826</v>
+        <v>46.85918710946249</v>
       </c>
       <c r="E68">
-        <v>4.522900523290362</v>
+        <v>3.742462315976913</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -2150,16 +2150,16 @@
         <v>72</v>
       </c>
       <c r="B69">
-        <v>3.167340675629806</v>
+        <v>2.543430334110815</v>
       </c>
       <c r="C69">
-        <v>10.93346393464005</v>
+        <v>10.91812716835005</v>
       </c>
       <c r="D69">
-        <v>46.26015768809766</v>
+        <v>46.18175435037774</v>
       </c>
       <c r="E69">
-        <v>4.577459061402656</v>
+        <v>3.675774084775104</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2167,16 +2167,16 @@
         <v>73</v>
       </c>
       <c r="B70">
-        <v>3.299352434706138</v>
+        <v>2.639049654183919</v>
       </c>
       <c r="C70">
-        <v>11.93678992743669</v>
+        <v>10.69907745498348</v>
       </c>
       <c r="D70">
-        <v>46.0567901165506</v>
+        <v>47.21576893908212</v>
       </c>
       <c r="E70">
-        <v>4.695602555489089</v>
+        <v>3.624264487078719</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -2184,16 +2184,16 @@
         <v>74</v>
       </c>
       <c r="B71">
-        <v>3.515989792918153</v>
+        <v>2.651083486850568</v>
       </c>
       <c r="C71">
-        <v>12.01285300953116</v>
+        <v>10.84641204353808</v>
       </c>
       <c r="D71">
-        <v>46.12978593979871</v>
+        <v>47.19059869722687</v>
       </c>
       <c r="E71">
-        <v>4.874564232044111</v>
+        <v>3.675024982754331</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -2201,16 +2201,16 @@
         <v>75</v>
       </c>
       <c r="B72">
-        <v>3.681619605989857</v>
+        <v>2.574439239374001</v>
       </c>
       <c r="C72">
-        <v>10.67624170441521</v>
+        <v>10.71285746419812</v>
       </c>
       <c r="D72">
-        <v>46.05667552681244</v>
+        <v>47.13451752290633</v>
       </c>
       <c r="E72">
-        <v>5.141289135762713</v>
+        <v>3.742417136107635</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -2218,16 +2218,16 @@
         <v>76</v>
       </c>
       <c r="B73">
-        <v>4.224007182408271</v>
+        <v>2.616493098753214</v>
       </c>
       <c r="C73">
-        <v>11.94290443155489</v>
+        <v>10.67559754562107</v>
       </c>
       <c r="D73">
-        <v>46.17194557433139</v>
+        <v>46.27254495747098</v>
       </c>
       <c r="E73">
-        <v>4.651990396417483</v>
+        <v>3.629565176495123</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -2235,16 +2235,16 @@
         <v>77</v>
       </c>
       <c r="B74">
-        <v>4.399324224767986</v>
+        <v>3.056867023411823</v>
       </c>
       <c r="C74">
-        <v>23.85108249889416</v>
+        <v>23.13527333238386</v>
       </c>
       <c r="D74">
-        <v>22.29919080520088</v>
+        <v>23.00132699064747</v>
       </c>
       <c r="E74">
-        <v>6.914480769764558</v>
+        <v>5.920027769967669</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -2252,16 +2252,16 @@
         <v>78</v>
       </c>
       <c r="B75">
-        <v>3.683744152055119</v>
+        <v>3.047283164838178</v>
       </c>
       <c r="C75">
-        <v>23.41558226457136</v>
+        <v>23.39145972658913</v>
       </c>
       <c r="D75">
-        <v>22.23129464920467</v>
+        <v>23.11664291659307</v>
       </c>
       <c r="E75">
-        <v>7.23296408739183</v>
+        <v>5.844626166765335</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -2269,16 +2269,16 @@
         <v>79</v>
       </c>
       <c r="B76">
-        <v>3.464697581360423</v>
+        <v>3.03424192595075</v>
       </c>
       <c r="C76">
-        <v>23.98651648105942</v>
+        <v>23.33873852772602</v>
       </c>
       <c r="D76">
-        <v>22.40158704994271</v>
+        <v>23.34857223518232</v>
       </c>
       <c r="E76">
-        <v>6.690042761408365</v>
+        <v>5.840706706077879</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -2286,16 +2286,16 @@
         <v>80</v>
       </c>
       <c r="B77">
-        <v>4.35474638011239</v>
+        <v>3.115069752815936</v>
       </c>
       <c r="C77">
-        <v>24.37145379495676</v>
+        <v>23.09615961137315</v>
       </c>
       <c r="D77">
-        <v>22.10715957526275</v>
+        <v>22.34071833138216</v>
       </c>
       <c r="E77">
-        <v>6.93942318554018</v>
+        <v>5.896112810378793</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -2303,16 +2303,16 @@
         <v>81</v>
       </c>
       <c r="B78">
-        <v>4.174237478243071</v>
+        <v>3.105204553453811</v>
       </c>
       <c r="C78">
-        <v>23.65123098177441</v>
+        <v>23.08725424766066</v>
       </c>
       <c r="D78">
-        <v>22.43169462710454</v>
+        <v>22.19688700813165</v>
       </c>
       <c r="E78">
-        <v>5.917281582607638</v>
+        <v>5.842541253154049</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2320,16 +2320,16 @@
         <v>82</v>
       </c>
       <c r="B79">
-        <v>3.657368765808844</v>
+        <v>3.073726256377485</v>
       </c>
       <c r="C79">
-        <v>24.61502507973876</v>
+        <v>23.16036598690356</v>
       </c>
       <c r="D79">
-        <v>22.51340578434533</v>
+        <v>22.57313030041815</v>
       </c>
       <c r="E79">
-        <v>7.2422898089699</v>
+        <v>5.908732221791126</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -2337,16 +2337,16 @@
         <v>83</v>
       </c>
       <c r="B80">
-        <v>4.156491445420914</v>
+        <v>3.020807704313075</v>
       </c>
       <c r="C80">
-        <v>23.7566809976619</v>
+        <v>23.20960091611599</v>
       </c>
       <c r="D80">
-        <v>22.33691869740168</v>
+        <v>22.43391334623503</v>
       </c>
       <c r="E80">
-        <v>6.961809262456333</v>
+        <v>5.984227065315974</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -2354,16 +2354,16 @@
         <v>84</v>
       </c>
       <c r="B81">
-        <v>3.525184536842168</v>
+        <v>3.022992302002255</v>
       </c>
       <c r="C81">
-        <v>23.56887577526547</v>
+        <v>23.51371947201356</v>
       </c>
       <c r="D81">
-        <v>22.26814940021937</v>
+        <v>22.17565654193589</v>
       </c>
       <c r="E81">
-        <v>5.926363155393899</v>
+        <v>5.938384226704371</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -2371,16 +2371,16 @@
         <v>85</v>
       </c>
       <c r="B82">
-        <v>4.146054387013271</v>
+        <v>3.057033086571572</v>
       </c>
       <c r="C82">
-        <v>24.57457590127774</v>
+        <v>23.10202786854479</v>
       </c>
       <c r="D82">
-        <v>22.34271216140865</v>
+        <v>22.86252195024731</v>
       </c>
       <c r="E82">
-        <v>5.828042031554903</v>
+        <v>5.915427526713749</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -2388,16 +2388,16 @@
         <v>86</v>
       </c>
       <c r="B83">
-        <v>3.554759718996304</v>
+        <v>3.067858049965766</v>
       </c>
       <c r="C83">
-        <v>23.75589673710953</v>
+        <v>23.36237276336542</v>
       </c>
       <c r="D83">
-        <v>22.24641633293803</v>
+        <v>22.18179893293257</v>
       </c>
       <c r="E83">
-        <v>7.207433415868923</v>
+        <v>5.832869276592769</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -2405,16 +2405,16 @@
         <v>87</v>
       </c>
       <c r="B84">
-        <v>3.180076387510017</v>
+        <v>3.084397481402096</v>
       </c>
       <c r="C84">
-        <v>23.91608039313525</v>
+        <v>23.14009025261077</v>
       </c>
       <c r="D84">
-        <v>22.2058090305873</v>
+        <v>22.18812929664411</v>
       </c>
       <c r="E84">
-        <v>7.110697664287819</v>
+        <v>5.863275430070104</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -2422,16 +2422,16 @@
         <v>88</v>
       </c>
       <c r="B85">
-        <v>3.09732611793466</v>
+        <v>3.062702676396636</v>
       </c>
       <c r="C85">
-        <v>24.50112336185139</v>
+        <v>23.34818314744077</v>
       </c>
       <c r="D85">
-        <v>22.07593768352436</v>
+        <v>23.56253670693403</v>
       </c>
       <c r="E85">
-        <v>7.390507293238752</v>
+        <v>5.901161547745615</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -2439,16 +2439,16 @@
         <v>89</v>
       </c>
       <c r="B86">
-        <v>3.934040347958595</v>
+        <v>3.076311964655446</v>
       </c>
       <c r="C86">
-        <v>23.17210702731392</v>
+        <v>23.35748417507447</v>
       </c>
       <c r="D86">
-        <v>22.44622765628415</v>
+        <v>22.13668596719211</v>
       </c>
       <c r="E86">
-        <v>7.355637441767543</v>
+        <v>5.859402678076565</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -2456,16 +2456,16 @@
         <v>90</v>
       </c>
       <c r="B87">
-        <v>4.600968817967299</v>
+        <v>3.119928286868169</v>
       </c>
       <c r="C87">
-        <v>23.44287179822775</v>
+        <v>23.22163907733152</v>
       </c>
       <c r="D87">
-        <v>22.26331883468324</v>
+        <v>22.18658984749543</v>
       </c>
       <c r="E87">
-        <v>7.139377885889704</v>
+        <v>5.954486971351585</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -2473,16 +2473,16 @@
         <v>91</v>
       </c>
       <c r="B88">
-        <v>3.546244972592953</v>
+        <v>3.08095840377212</v>
       </c>
       <c r="C88">
-        <v>23.20851829066574</v>
+        <v>23.28674200012532</v>
       </c>
       <c r="D88">
-        <v>22.17664394593371</v>
+        <v>22.39372743421726</v>
       </c>
       <c r="E88">
-        <v>6.474128785712056</v>
+        <v>5.829868592927843</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -2490,16 +2490,16 @@
         <v>92</v>
       </c>
       <c r="B89">
-        <v>3.85783714523968</v>
+        <v>3.025060227958656</v>
       </c>
       <c r="C89">
-        <v>23.76625649558027</v>
+        <v>23.23772953709602</v>
       </c>
       <c r="D89">
-        <v>22.10326329388646</v>
+        <v>23.41277956487197</v>
       </c>
       <c r="E89">
-        <v>5.984833402986919</v>
+        <v>5.8451954754496</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -2507,16 +2507,16 @@
         <v>93</v>
       </c>
       <c r="B90">
-        <v>4.781253581649449</v>
+        <v>3.055764186184051</v>
       </c>
       <c r="C90">
-        <v>24.07535337675235</v>
+        <v>23.22875753066746</v>
       </c>
       <c r="D90">
-        <v>22.14618827539431</v>
+        <v>23.27840253181606</v>
       </c>
       <c r="E90">
-        <v>6.865397853415132</v>
+        <v>5.945313020367704</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -2524,16 +2524,16 @@
         <v>94</v>
       </c>
       <c r="B91">
-        <v>4.722268941936585</v>
+        <v>3.123769811177259</v>
       </c>
       <c r="C91">
-        <v>23.63164076022532</v>
+        <v>23.41957645557225</v>
       </c>
       <c r="D91">
-        <v>22.515217750471</v>
+        <v>22.20217214096209</v>
       </c>
       <c r="E91">
-        <v>6.796002947333091</v>
+        <v>5.852468097723949</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -2541,16 +2541,16 @@
         <v>95</v>
       </c>
       <c r="B92">
-        <v>4.454859395005461</v>
+        <v>3.033192044705458</v>
       </c>
       <c r="C92">
-        <v>23.26081744533297</v>
+        <v>23.06948405558525</v>
       </c>
       <c r="D92">
-        <v>22.31301135925932</v>
+        <v>23.15562667876795</v>
       </c>
       <c r="E92">
-        <v>6.49478638627599</v>
+        <v>5.851727378472287</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -2558,16 +2558,16 @@
         <v>96</v>
       </c>
       <c r="B93">
-        <v>4.22492987936123</v>
+        <v>3.090447372715059</v>
       </c>
       <c r="C93">
-        <v>23.19187722867106</v>
+        <v>23.04104458387987</v>
       </c>
       <c r="D93">
-        <v>22.4072378638825</v>
+        <v>22.13875106041323</v>
       </c>
       <c r="E93">
-        <v>6.815955976401023</v>
+        <v>5.907074199471078</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -2575,16 +2575,16 @@
         <v>97</v>
       </c>
       <c r="B94">
-        <v>3.748041841143617</v>
+        <v>3.107889728918299</v>
       </c>
       <c r="C94">
-        <v>24.04116532090539</v>
+        <v>23.20491593569658</v>
       </c>
       <c r="D94">
-        <v>22.21109256650037</v>
+        <v>23.58734289308867</v>
       </c>
       <c r="E94">
-        <v>6.712859177725427</v>
+        <v>5.916128500740843</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -2592,16 +2592,16 @@
         <v>98</v>
       </c>
       <c r="B95">
-        <v>4.259796475208833</v>
+        <v>3.013720554069885</v>
       </c>
       <c r="C95">
-        <v>23.72170797822919</v>
+        <v>23.29731555471229</v>
       </c>
       <c r="D95">
-        <v>22.22440504972731</v>
+        <v>23.26797479795344</v>
       </c>
       <c r="E95">
-        <v>6.708699705161182</v>
+        <v>5.873056426554426</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -2609,16 +2609,16 @@
         <v>99</v>
       </c>
       <c r="B96">
-        <v>3.614787788132196</v>
+        <v>3.026083232736605</v>
       </c>
       <c r="C96">
-        <v>24.19611234474743</v>
+        <v>23.26128079809854</v>
       </c>
       <c r="D96">
-        <v>22.21415505407149</v>
+        <v>22.45000981105633</v>
       </c>
       <c r="E96">
-        <v>6.454749578260532</v>
+        <v>5.842555396762204</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2626,16 +2626,16 @@
         <v>100</v>
       </c>
       <c r="B97">
-        <v>4.173821826336177</v>
+        <v>3.038460114678747</v>
       </c>
       <c r="C97">
-        <v>24.19734640034859</v>
+        <v>23.072842298167</v>
       </c>
       <c r="D97">
-        <v>22.34305980869476</v>
+        <v>22.81398890486539</v>
       </c>
       <c r="E97">
-        <v>5.972246592028983</v>
+        <v>5.825011829566134</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2643,16 +2643,16 @@
         <v>101</v>
       </c>
       <c r="B98">
-        <v>3.785852665652883</v>
+        <v>3.051597315151881</v>
       </c>
       <c r="C98">
-        <v>23.47205811936714</v>
+        <v>23.20710003861835</v>
       </c>
       <c r="D98">
-        <v>22.10324482530073</v>
+        <v>23.49696390748734</v>
       </c>
       <c r="E98">
-        <v>6.098086100505157</v>
+        <v>5.847189828375859</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2660,16 +2660,16 @@
         <v>102</v>
       </c>
       <c r="B99">
-        <v>3.815267842247092</v>
+        <v>3.123453834874094</v>
       </c>
       <c r="C99">
-        <v>23.54466900221568</v>
+        <v>23.36927170213019</v>
       </c>
       <c r="D99">
-        <v>22.12318454373586</v>
+        <v>22.07579465786003</v>
       </c>
       <c r="E99">
-        <v>6.068027292099083</v>
+        <v>5.850598445421451</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2677,16 +2677,16 @@
         <v>103</v>
       </c>
       <c r="B100">
-        <v>4.14932841423474</v>
+        <v>3.032104789538771</v>
       </c>
       <c r="C100">
-        <v>23.8592574974745</v>
+        <v>23.31692934878937</v>
       </c>
       <c r="D100">
-        <v>22.33275678945785</v>
+        <v>22.57841662992269</v>
       </c>
       <c r="E100">
-        <v>6.385864259507873</v>
+        <v>5.95098187040121</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2694,16 +2694,16 @@
         <v>104</v>
       </c>
       <c r="B101">
-        <v>3.840579934828259</v>
+        <v>3.025665965583993</v>
       </c>
       <c r="C101">
-        <v>23.13212864994795</v>
+        <v>23.44907747828289</v>
       </c>
       <c r="D101">
-        <v>22.34982257208148</v>
+        <v>23.46616567943082</v>
       </c>
       <c r="E101">
-        <v>7.149632325150229</v>
+        <v>5.827112010817832</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2711,16 +2711,16 @@
         <v>105</v>
       </c>
       <c r="B102">
-        <v>4.576593804797136</v>
+        <v>3.026447013635011</v>
       </c>
       <c r="C102">
-        <v>23.87759216493476</v>
+        <v>23.18312312074282</v>
       </c>
       <c r="D102">
-        <v>22.29198376216454</v>
+        <v>23.02476378002044</v>
       </c>
       <c r="E102">
-        <v>5.886653579525221</v>
+        <v>5.914803285002826</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2728,16 +2728,16 @@
         <v>106</v>
       </c>
       <c r="B103">
-        <v>3.173430902928969</v>
+        <v>3.015259016117112</v>
       </c>
       <c r="C103">
-        <v>23.76110644833502</v>
+        <v>23.1881928324874</v>
       </c>
       <c r="D103">
-        <v>22.13957370835899</v>
+        <v>22.94305248191461</v>
       </c>
       <c r="E103">
-        <v>6.232678615055962</v>
+        <v>5.94274033521821</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2745,16 +2745,16 @@
         <v>107</v>
       </c>
       <c r="B104">
-        <v>4.273863400637951</v>
+        <v>3.109668333845226</v>
       </c>
       <c r="C104">
-        <v>23.31329453501295</v>
+        <v>23.3345572382418</v>
       </c>
       <c r="D104">
-        <v>22.18631601593569</v>
+        <v>23.42812992948871</v>
       </c>
       <c r="E104">
-        <v>6.984424245653939</v>
+        <v>5.849497574415202</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2762,16 +2762,16 @@
         <v>108</v>
       </c>
       <c r="B105">
-        <v>4.796750858452325</v>
+        <v>3.064506747513287</v>
       </c>
       <c r="C105">
-        <v>24.05480959626664</v>
+        <v>23.30005904846447</v>
       </c>
       <c r="D105">
-        <v>22.393438703458</v>
+        <v>22.462710489842</v>
       </c>
       <c r="E105">
-        <v>6.67262400373372</v>
+        <v>5.936195243116737</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2779,16 +2779,16 @@
         <v>109</v>
       </c>
       <c r="B106">
-        <v>3.608248915883875</v>
+        <v>3.065930302822166</v>
       </c>
       <c r="C106">
-        <v>23.26544155974885</v>
+        <v>23.14283365219874</v>
       </c>
       <c r="D106">
-        <v>22.13882476811396</v>
+        <v>22.09490563873087</v>
       </c>
       <c r="E106">
-        <v>5.859814832332856</v>
+        <v>5.980065208801789</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2796,16 +2796,16 @@
         <v>110</v>
       </c>
       <c r="B107">
-        <v>3.720371741519171</v>
+        <v>3.021496139747765</v>
       </c>
       <c r="C107">
-        <v>23.89396357649068</v>
+        <v>23.04354753464174</v>
       </c>
       <c r="D107">
-        <v>22.38086150448657</v>
+        <v>23.44344278882831</v>
       </c>
       <c r="E107">
-        <v>6.852927239558769</v>
+        <v>5.954413612642191</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2813,16 +2813,16 @@
         <v>111</v>
       </c>
       <c r="B108">
-        <v>4.321285811401701</v>
+        <v>3.111459511473214</v>
       </c>
       <c r="C108">
-        <v>24.33898617803281</v>
+        <v>23.48177051591126</v>
       </c>
       <c r="D108">
-        <v>22.16133313310171</v>
+        <v>22.57484945264592</v>
       </c>
       <c r="E108">
-        <v>6.968561332531994</v>
+        <v>5.881897390122989</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -2830,16 +2830,16 @@
         <v>112</v>
       </c>
       <c r="B109">
-        <v>3.905413994093131</v>
+        <v>3.111624122950657</v>
       </c>
       <c r="C109">
-        <v>24.16906150059692</v>
+        <v>23.25809014051733</v>
       </c>
       <c r="D109">
-        <v>22.13021717671799</v>
+        <v>22.25985916238564</v>
       </c>
       <c r="E109">
-        <v>5.999283333073778</v>
+        <v>5.910323138667423</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2847,16 +2847,16 @@
         <v>113</v>
       </c>
       <c r="B110">
-        <v>4.109501710492636</v>
+        <v>3.040932459794573</v>
       </c>
       <c r="C110">
-        <v>24.2590574272743</v>
+        <v>23.07960728846595</v>
       </c>
       <c r="D110">
-        <v>22.22843197113195</v>
+        <v>23.58902732152721</v>
       </c>
       <c r="E110">
-        <v>6.24626455487527</v>
+        <v>5.932849848242061</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -2864,16 +2864,16 @@
         <v>114</v>
       </c>
       <c r="B111">
-        <v>4.04581471413139</v>
+        <v>3.038061473504483</v>
       </c>
       <c r="C111">
-        <v>23.76438114807772</v>
+        <v>23.26542740155436</v>
       </c>
       <c r="D111">
-        <v>22.53212864334143</v>
+        <v>23.17107226091224</v>
       </c>
       <c r="E111">
-        <v>5.828176295049185</v>
+        <v>5.917384024794904</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -2881,16 +2881,16 @@
         <v>115</v>
       </c>
       <c r="B112">
-        <v>4.151639093005184</v>
+        <v>3.036885298225067</v>
       </c>
       <c r="C112">
-        <v>24.3354931394499</v>
+        <v>23.20884153704288</v>
       </c>
       <c r="D112">
-        <v>22.4511587272827</v>
+        <v>22.45932128629551</v>
       </c>
       <c r="E112">
-        <v>6.290381894808027</v>
+        <v>5.876464769182146</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -2898,16 +2898,16 @@
         <v>116</v>
       </c>
       <c r="B113">
-        <v>3.444490018073612</v>
+        <v>3.078602839083616</v>
       </c>
       <c r="C113">
-        <v>23.44127961203356</v>
+        <v>23.15358964039066</v>
       </c>
       <c r="D113">
-        <v>22.43940240457613</v>
+        <v>22.43299073932451</v>
       </c>
       <c r="E113">
-        <v>7.019135195261843</v>
+        <v>5.840384622384157</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -2915,16 +2915,16 @@
         <v>117</v>
       </c>
       <c r="B114">
-        <v>4.55976514025267</v>
+        <v>3.03124057404824</v>
       </c>
       <c r="C114">
-        <v>24.05993079739482</v>
+        <v>23.04766821817605</v>
       </c>
       <c r="D114">
-        <v>22.08857005415002</v>
+        <v>23.33187017783422</v>
       </c>
       <c r="E114">
-        <v>6.455606330314247</v>
+        <v>5.988147085957955</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -2932,16 +2932,16 @@
         <v>118</v>
       </c>
       <c r="B115">
-        <v>3.26915714860126</v>
+        <v>3.114405106702458</v>
       </c>
       <c r="C115">
-        <v>24.10476082287853</v>
+        <v>23.0665951200114</v>
       </c>
       <c r="D115">
-        <v>22.42256801931898</v>
+        <v>23.33584184982486</v>
       </c>
       <c r="E115">
-        <v>7.288560068189469</v>
+        <v>5.906798534244522</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -2949,16 +2949,16 @@
         <v>119</v>
       </c>
       <c r="B116">
-        <v>3.566048937004025</v>
+        <v>3.018633977531313</v>
       </c>
       <c r="C116">
-        <v>23.74218523507577</v>
+        <v>23.22928402097417</v>
       </c>
       <c r="D116">
-        <v>22.09653795111561</v>
+        <v>23.15653796604848</v>
       </c>
       <c r="E116">
-        <v>6.751810535623092</v>
+        <v>5.94656745167886</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -2966,16 +2966,16 @@
         <v>120</v>
       </c>
       <c r="B117">
-        <v>3.675399134295726</v>
+        <v>3.012098416420951</v>
       </c>
       <c r="C117">
-        <v>23.46361041582087</v>
+        <v>23.3253781928334</v>
       </c>
       <c r="D117">
-        <v>22.1540734857694</v>
+        <v>22.07456913026993</v>
       </c>
       <c r="E117">
-        <v>6.308818746259108</v>
+        <v>5.866846974644452</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -2983,16 +2983,16 @@
         <v>121</v>
       </c>
       <c r="B118">
-        <v>4.047493001101179</v>
+        <v>3.073778330574926</v>
       </c>
       <c r="C118">
-        <v>24.22469533097467</v>
+        <v>23.39979160211887</v>
       </c>
       <c r="D118">
-        <v>22.31833818449347</v>
+        <v>22.43873698586178</v>
       </c>
       <c r="E118">
-        <v>6.193223072214645</v>
+        <v>5.931638988692996</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -3000,16 +3000,16 @@
         <v>122</v>
       </c>
       <c r="B119">
-        <v>3.98306074837482</v>
+        <v>3.046071311388157</v>
       </c>
       <c r="C119">
-        <v>23.38495493078608</v>
+        <v>23.17855504489361</v>
       </c>
       <c r="D119">
-        <v>22.25459205372093</v>
+        <v>23.02480851416251</v>
       </c>
       <c r="E119">
-        <v>6.468061385305132</v>
+        <v>5.900820547504264</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -3017,16 +3017,16 @@
         <v>123</v>
       </c>
       <c r="B120">
-        <v>3.041269780861001</v>
+        <v>3.121161546098706</v>
       </c>
       <c r="C120">
-        <v>24.2210492700054</v>
+        <v>23.11834779455731</v>
       </c>
       <c r="D120">
-        <v>22.16572179771256</v>
+        <v>22.62507920409353</v>
       </c>
       <c r="E120">
-        <v>7.362780758533205</v>
+        <v>5.906852212121942</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -3034,16 +3034,16 @@
         <v>124</v>
       </c>
       <c r="B121">
-        <v>3.74744688078163</v>
+        <v>3.048461544147974</v>
       </c>
       <c r="C121">
-        <v>23.18188409608253</v>
+        <v>23.52854811630267</v>
       </c>
       <c r="D121">
-        <v>22.1232224727684</v>
+        <v>23.49081432663812</v>
       </c>
       <c r="E121">
-        <v>6.33339668652814</v>
+        <v>5.937743759884456</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -3051,16 +3051,16 @@
         <v>125</v>
       </c>
       <c r="B122">
-        <v>3.665622466669871</v>
+        <v>3.080837510672394</v>
       </c>
       <c r="C122">
-        <v>24.59130170602303</v>
+        <v>23.52571110632185</v>
       </c>
       <c r="D122">
-        <v>22.2928349624616</v>
+        <v>22.35807792457559</v>
       </c>
       <c r="E122">
-        <v>6.740942659347452</v>
+        <v>5.892485639541872</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -3068,16 +3068,16 @@
         <v>126</v>
       </c>
       <c r="B123">
-        <v>4.316529771324116</v>
+        <v>3.063782201754115</v>
       </c>
       <c r="C123">
-        <v>23.73308788995947</v>
+        <v>23.07597189133268</v>
       </c>
       <c r="D123">
-        <v>22.07468007944446</v>
+        <v>22.62910599541382</v>
       </c>
       <c r="E123">
-        <v>7.309759624630105</v>
+        <v>5.90624479793897</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -3085,16 +3085,16 @@
         <v>127</v>
       </c>
       <c r="B124">
-        <v>3.698873705955955</v>
+        <v>3.116635972022356</v>
       </c>
       <c r="C124">
-        <v>23.16880475315794</v>
+        <v>23.42769746200077</v>
       </c>
       <c r="D124">
-        <v>22.45113132092753</v>
+        <v>23.23471224359927</v>
       </c>
       <c r="E124">
-        <v>7.273136092215095</v>
+        <v>5.969822146135612</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -3102,16 +3102,16 @@
         <v>128</v>
       </c>
       <c r="B125">
-        <v>4.438302691596507</v>
+        <v>3.078881676183477</v>
       </c>
       <c r="C125">
-        <v>23.0548097072168</v>
+        <v>23.38286101845324</v>
       </c>
       <c r="D125">
-        <v>22.39753387289618</v>
+        <v>22.10506409627137</v>
       </c>
       <c r="E125">
-        <v>6.064476089204119</v>
+        <v>5.831354567761767</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -3119,16 +3119,16 @@
         <v>129</v>
       </c>
       <c r="B126">
-        <v>4.266338076940419</v>
+        <v>3.086373932156098</v>
       </c>
       <c r="C126">
-        <v>24.38842704312825</v>
+        <v>23.2909386981995</v>
       </c>
       <c r="D126">
-        <v>22.43300628170448</v>
+        <v>22.93227577737692</v>
       </c>
       <c r="E126">
-        <v>7.312856587765617</v>
+        <v>5.975388656994837</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -3136,16 +3136,16 @@
         <v>130</v>
       </c>
       <c r="B127">
-        <v>4.253524822472951</v>
+        <v>3.074175546645774</v>
       </c>
       <c r="C127">
-        <v>24.42534304172345</v>
+        <v>23.4487341985596</v>
       </c>
       <c r="D127">
-        <v>22.21715088312759</v>
+        <v>23.39314236184431</v>
       </c>
       <c r="E127">
-        <v>7.223248557558712</v>
+        <v>5.949023864437736</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -3153,16 +3153,16 @@
         <v>131</v>
       </c>
       <c r="B128">
-        <v>3.642780104056734</v>
+        <v>3.067990219457466</v>
       </c>
       <c r="C128">
-        <v>23.28698217694993</v>
+        <v>23.27128184740993</v>
       </c>
       <c r="D128">
-        <v>22.22114109502513</v>
+        <v>23.39930037701958</v>
       </c>
       <c r="E128">
-        <v>7.193614848685778</v>
+        <v>5.985541090137485</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -3170,16 +3170,16 @@
         <v>132</v>
       </c>
       <c r="B129">
-        <v>3.112344355786897</v>
+        <v>3.040166568095255</v>
       </c>
       <c r="C129">
-        <v>24.56613277838057</v>
+        <v>23.09193401928331</v>
       </c>
       <c r="D129">
-        <v>22.45509516643898</v>
+        <v>23.18629074162514</v>
       </c>
       <c r="E129">
-        <v>6.301375013489579</v>
+        <v>5.959491282813732</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -3187,16 +3187,16 @@
         <v>133</v>
       </c>
       <c r="B130">
-        <v>4.472316933246656</v>
+        <v>3.089970544763696</v>
       </c>
       <c r="C130">
-        <v>24.30458344475278</v>
+        <v>23.32163052500916</v>
       </c>
       <c r="D130">
-        <v>22.24760710330002</v>
+        <v>22.49606224101503</v>
       </c>
       <c r="E130">
-        <v>5.868598204451108</v>
+        <v>5.95704659444767</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -3204,16 +3204,16 @@
         <v>134</v>
       </c>
       <c r="B131">
-        <v>4.544347366403556</v>
+        <v>3.079810077803353</v>
       </c>
       <c r="C131">
-        <v>23.06516833172662</v>
+        <v>23.52711850076145</v>
       </c>
       <c r="D131">
-        <v>22.15876628297598</v>
+        <v>23.16895384130756</v>
       </c>
       <c r="E131">
-        <v>6.180835712855165</v>
+        <v>5.964314402525075</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -3221,16 +3221,16 @@
         <v>135</v>
       </c>
       <c r="B132">
-        <v>4.217455810487815</v>
+        <v>3.048081902407002</v>
       </c>
       <c r="C132">
-        <v>24.22577286171857</v>
+        <v>23.05326425338146</v>
       </c>
       <c r="D132">
-        <v>22.43877820651103</v>
+        <v>22.12994244257474</v>
       </c>
       <c r="E132">
-        <v>6.917500448565155</v>
+        <v>5.909424878108995</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -3238,16 +3238,16 @@
         <v>136</v>
       </c>
       <c r="B133">
-        <v>4.267715629346564</v>
+        <v>3.087015532130156</v>
       </c>
       <c r="C133">
-        <v>23.90303275365036</v>
+        <v>23.07986599368464</v>
       </c>
       <c r="D133">
-        <v>22.13436453480638</v>
+        <v>22.36837618578522</v>
       </c>
       <c r="E133">
-        <v>6.044192136507978</v>
+        <v>5.844594244522196</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -3255,16 +3255,16 @@
         <v>137</v>
       </c>
       <c r="B134">
-        <v>3.598490614962072</v>
+        <v>3.015004311529206</v>
       </c>
       <c r="C134">
-        <v>24.13579511775654</v>
+        <v>23.0243059662434</v>
       </c>
       <c r="D134">
-        <v>22.50135462911356</v>
+        <v>22.78335667007955</v>
       </c>
       <c r="E134">
-        <v>7.115771484669461</v>
+        <v>5.878635141326736</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -3272,16 +3272,16 @@
         <v>138</v>
       </c>
       <c r="B135">
-        <v>3.719032957369942</v>
+        <v>3.122383976015368</v>
       </c>
       <c r="C135">
-        <v>24.22628548756268</v>
+        <v>23.08429971091318</v>
       </c>
       <c r="D135">
-        <v>22.19818808812927</v>
+        <v>22.10156844529843</v>
       </c>
       <c r="E135">
-        <v>7.124599486526654</v>
+        <v>5.923296961953919</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -3289,16 +3289,16 @@
         <v>139</v>
       </c>
       <c r="B136">
-        <v>3.880029579173211</v>
+        <v>3.028991444282767</v>
       </c>
       <c r="C136">
-        <v>24.59172352420584</v>
+        <v>23.38350357334028</v>
       </c>
       <c r="D136">
-        <v>22.32522087160774</v>
+        <v>22.11438286817705</v>
       </c>
       <c r="E136">
-        <v>6.445670938680683</v>
+        <v>5.900965550792908</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -3306,16 +3306,16 @@
         <v>140</v>
       </c>
       <c r="B137">
-        <v>3.677153228364773</v>
+        <v>3.06914236115348</v>
       </c>
       <c r="C137">
-        <v>24.36908617937579</v>
+        <v>23.06514194980919</v>
       </c>
       <c r="D137">
-        <v>22.23435301292437</v>
+        <v>22.42527539272416</v>
       </c>
       <c r="E137">
-        <v>6.838220866498262</v>
+        <v>5.964071477851665</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -3323,16 +3323,16 @@
         <v>141</v>
       </c>
       <c r="B138">
-        <v>3.498811779222124</v>
+        <v>3.014137967245406</v>
       </c>
       <c r="C138">
-        <v>24.26048787157525</v>
+        <v>23.40712784591745</v>
       </c>
       <c r="D138">
-        <v>22.42162716734233</v>
+        <v>22.93448977384284</v>
       </c>
       <c r="E138">
-        <v>5.920807392738246</v>
+        <v>5.912043511979041</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -3340,16 +3340,16 @@
         <v>142</v>
       </c>
       <c r="B139">
-        <v>4.461795439847823</v>
+        <v>3.040852330961589</v>
       </c>
       <c r="C139">
-        <v>23.98544338119048</v>
+        <v>23.30268457847182</v>
       </c>
       <c r="D139">
-        <v>22.32380346728942</v>
+        <v>23.40131581482002</v>
       </c>
       <c r="E139">
-        <v>6.237564455429165</v>
+        <v>5.969618328189471</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -3357,16 +3357,16 @@
         <v>143</v>
       </c>
       <c r="B140">
-        <v>5.204641138352886</v>
+        <v>3.635377018999314</v>
       </c>
       <c r="C140">
-        <v>10.57850766670785</v>
+        <v>10.92973019680806</v>
       </c>
       <c r="D140">
-        <v>58.01330084143785</v>
+        <v>59.15191585519727</v>
       </c>
       <c r="E140">
-        <v>4.480058276590777</v>
+        <v>3.936476640283563</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -3374,16 +3374,16 @@
         <v>144</v>
       </c>
       <c r="B141">
-        <v>5.068543032234778</v>
+        <v>3.642467309602569</v>
       </c>
       <c r="C141">
-        <v>11.35778462188344</v>
+        <v>10.71177308861843</v>
       </c>
       <c r="D141">
-        <v>58.32974214349128</v>
+        <v>58.65062377068624</v>
       </c>
       <c r="E141">
-        <v>5.145167071698831</v>
+        <v>4.007122398312971</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -3391,16 +3391,16 @@
         <v>145</v>
       </c>
       <c r="B142">
-        <v>5.265328702773238</v>
+        <v>3.663855797857388</v>
       </c>
       <c r="C142">
-        <v>11.63757316639679</v>
+        <v>10.48933193929339</v>
       </c>
       <c r="D142">
-        <v>57.96336998771954</v>
+        <v>59.03305358490313</v>
       </c>
       <c r="E142">
-        <v>4.057165268454375</v>
+        <v>4.020872199127689</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -3408,16 +3408,16 @@
         <v>146</v>
       </c>
       <c r="B143">
-        <v>4.527677213747778</v>
+        <v>3.655111018049716</v>
       </c>
       <c r="C143">
-        <v>10.44002006412855</v>
+        <v>10.44146638041453</v>
       </c>
       <c r="D143">
-        <v>58.11813291612406</v>
+        <v>59.25377441707801</v>
       </c>
       <c r="E143">
-        <v>4.077552249687722</v>
+        <v>4.012538192524207</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -3425,16 +3425,16 @@
         <v>147</v>
       </c>
       <c r="B144">
-        <v>4.539840589609216</v>
+        <v>3.733987636770642</v>
       </c>
       <c r="C144">
-        <v>11.52762539129147</v>
+        <v>10.67472314679612</v>
       </c>
       <c r="D144">
-        <v>57.98437686971623</v>
+        <v>58.96562437569924</v>
       </c>
       <c r="E144">
-        <v>4.243564821055753</v>
+        <v>3.950492441208399</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -3442,16 +3442,16 @@
         <v>148</v>
       </c>
       <c r="B145">
-        <v>4.123335900789752</v>
+        <v>3.727043938799588</v>
       </c>
       <c r="C145">
-        <v>10.66138570123391</v>
+        <v>10.68919928400622</v>
       </c>
       <c r="D145">
-        <v>57.99134841443398</v>
+        <v>58.16160934011725</v>
       </c>
       <c r="E145">
-        <v>3.955678365709686</v>
+        <v>4.067144323469557</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -3459,16 +3459,16 @@
         <v>149</v>
       </c>
       <c r="B146">
-        <v>4.442684042952989</v>
+        <v>3.684234475371932</v>
       </c>
       <c r="C146">
-        <v>11.24117335244102</v>
+        <v>10.93808370215879</v>
       </c>
       <c r="D146">
-        <v>58.1286179915968</v>
+        <v>58.65000598564392</v>
       </c>
       <c r="E146">
-        <v>4.721669778217374</v>
+        <v>4.023315393052218</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -3476,16 +3476,16 @@
         <v>150</v>
       </c>
       <c r="B147">
-        <v>4.351630267091351</v>
+        <v>3.634458273081083</v>
       </c>
       <c r="C147">
-        <v>11.00645828216745</v>
+        <v>10.88759020923692</v>
       </c>
       <c r="D147">
-        <v>58.01969024457924</v>
+        <v>58.49709641860557</v>
       </c>
       <c r="E147">
-        <v>4.132661175391663</v>
+        <v>4.063642739677871</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -3493,16 +3493,16 @@
         <v>151</v>
       </c>
       <c r="B148">
-        <v>4.967917533235584</v>
+        <v>3.655613229613317</v>
       </c>
       <c r="C148">
-        <v>11.29674536365576</v>
+        <v>10.62309230386263</v>
       </c>
       <c r="D148">
-        <v>58.17980614394576</v>
+        <v>59.33791491424938</v>
       </c>
       <c r="E148">
-        <v>5.200202404459692</v>
+        <v>3.948890511869751</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -3510,16 +3510,16 @@
         <v>152</v>
       </c>
       <c r="B149">
-        <v>4.945492030869582</v>
+        <v>3.693179181389451</v>
       </c>
       <c r="C149">
-        <v>11.97449589569999</v>
+        <v>10.84229969892068</v>
       </c>
       <c r="D149">
-        <v>58.34616495561335</v>
+        <v>59.34784492404246</v>
       </c>
       <c r="E149">
-        <v>5.467352508016267</v>
+        <v>3.935597767485288</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -3527,16 +3527,16 @@
         <v>153</v>
       </c>
       <c r="B150">
-        <v>3.939731420295905</v>
+        <v>3.654444037565749</v>
       </c>
       <c r="C150">
-        <v>11.49920452006783</v>
+        <v>10.90626172417565</v>
       </c>
       <c r="D150">
-        <v>58.26230863886199</v>
+        <v>58.43682020611067</v>
       </c>
       <c r="E150">
-        <v>4.206370763847851</v>
+        <v>4.089660736363101</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -3544,16 +3544,16 @@
         <v>154</v>
       </c>
       <c r="B151">
-        <v>4.229804886171381</v>
+        <v>3.637366572613806</v>
       </c>
       <c r="C151">
-        <v>11.48333878864691</v>
+        <v>10.47135196445888</v>
       </c>
       <c r="D151">
-        <v>58.34078769880976</v>
+        <v>59.04625770751732</v>
       </c>
       <c r="E151">
-        <v>4.680283906774958</v>
+        <v>4.060447098766085</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -3561,16 +3561,16 @@
         <v>155</v>
       </c>
       <c r="B152">
-        <v>5.353253232939656</v>
+        <v>3.718364041012031</v>
       </c>
       <c r="C152">
-        <v>11.84456789403854</v>
+        <v>10.65635680659359</v>
       </c>
       <c r="D152">
-        <v>57.9908075107928</v>
+        <v>59.38935198592338</v>
       </c>
       <c r="E152">
-        <v>5.299838339649208</v>
+        <v>3.951952035796138</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -3578,16 +3578,16 @@
         <v>156</v>
       </c>
       <c r="B153">
-        <v>5.415486381314928</v>
+        <v>3.695686896398258</v>
       </c>
       <c r="C153">
-        <v>10.67566285686609</v>
+        <v>10.86661061444641</v>
       </c>
       <c r="D153">
-        <v>58.32936531702889</v>
+        <v>58.98321676632503</v>
       </c>
       <c r="E153">
-        <v>4.067249961158257</v>
+        <v>3.930439617699883</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -3595,16 +3595,16 @@
         <v>157</v>
       </c>
       <c r="B154">
-        <v>4.325353606657083</v>
+        <v>3.654968830357603</v>
       </c>
       <c r="C154">
-        <v>10.49941340262622</v>
+        <v>10.78373693406403</v>
       </c>
       <c r="D154">
-        <v>58.12815109213481</v>
+        <v>58.22142242923552</v>
       </c>
       <c r="E154">
-        <v>4.020231706226117</v>
+        <v>4.017506316464594</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -3612,16 +3612,16 @@
         <v>158</v>
       </c>
       <c r="B155">
-        <v>3.645044446612963</v>
+        <v>3.70190366378664</v>
       </c>
       <c r="C155">
-        <v>11.75818591498935</v>
+        <v>10.71363725307499</v>
       </c>
       <c r="D155">
-        <v>58.31436356539404</v>
+        <v>59.10938493962286</v>
       </c>
       <c r="E155">
-        <v>5.243924019354322</v>
+        <v>4.07968294678967</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -3629,16 +3629,16 @@
         <v>159</v>
       </c>
       <c r="B156">
-        <v>4.706082391147952</v>
+        <v>3.638153521032474</v>
       </c>
       <c r="C156">
-        <v>11.31322111942308</v>
+        <v>10.60362676517616</v>
       </c>
       <c r="D156">
-        <v>57.89138609607163</v>
+        <v>59.03415186775696</v>
       </c>
       <c r="E156">
-        <v>5.351103891705498</v>
+        <v>3.976878346826444</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -3646,16 +3646,16 @@
         <v>160</v>
       </c>
       <c r="B157">
-        <v>3.688494402874192</v>
+        <v>3.653555264529799</v>
       </c>
       <c r="C157">
-        <v>11.10050079223624</v>
+        <v>10.71450130841499</v>
       </c>
       <c r="D157">
-        <v>57.89736125521701</v>
+        <v>58.37944625684933</v>
       </c>
       <c r="E157">
-        <v>4.170914389070058</v>
+        <v>3.975352646634724</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -3663,16 +3663,16 @@
         <v>161</v>
       </c>
       <c r="B158">
-        <v>4.838077814861493</v>
+        <v>3.733875127557402</v>
       </c>
       <c r="C158">
-        <v>11.42543218438798</v>
+        <v>10.80667077469606</v>
       </c>
       <c r="D158">
-        <v>57.89406154326921</v>
+        <v>58.42918296885763</v>
       </c>
       <c r="E158">
-        <v>4.807783673335969</v>
+        <v>4.089207182990276</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -3680,16 +3680,16 @@
         <v>162</v>
       </c>
       <c r="B159">
-        <v>4.338865927930423</v>
+        <v>3.731988134641352</v>
       </c>
       <c r="C159">
-        <v>11.52582809396588</v>
+        <v>10.91553148450719</v>
       </c>
       <c r="D159">
-        <v>57.93471804761807</v>
+        <v>59.22325341469054</v>
       </c>
       <c r="E159">
-        <v>4.661354167667467</v>
+        <v>3.987653439803947</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -3697,16 +3697,16 @@
         <v>163</v>
       </c>
       <c r="B160">
-        <v>3.669304636590025</v>
+        <v>3.625532165861566</v>
       </c>
       <c r="C160">
-        <v>11.07653917868026</v>
+        <v>10.94769482290077</v>
       </c>
       <c r="D160">
-        <v>58.18632785740515</v>
+        <v>59.2788882117738</v>
       </c>
       <c r="E160">
-        <v>5.12158611038433</v>
+        <v>3.953557802394031</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -3714,16 +3714,16 @@
         <v>164</v>
       </c>
       <c r="B161">
-        <v>5.286789990182497</v>
+        <v>3.68673269681744</v>
       </c>
       <c r="C161">
-        <v>11.60876285526746</v>
+        <v>10.93046591007386</v>
       </c>
       <c r="D161">
-        <v>58.31443116980026</v>
+        <v>58.76674057350831</v>
       </c>
       <c r="E161">
-        <v>4.174605017814363</v>
+        <v>3.93940628758128</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -3731,16 +3731,16 @@
         <v>165</v>
       </c>
       <c r="B162">
-        <v>4.125646759104187</v>
+        <v>3.645430231613223</v>
       </c>
       <c r="C162">
-        <v>11.47242979505111</v>
+        <v>10.51049016868423</v>
       </c>
       <c r="D162">
-        <v>58.18080208920193</v>
+        <v>59.21134308828162</v>
       </c>
       <c r="E162">
-        <v>4.670484347575141</v>
+        <v>3.962440978997859</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -3748,16 +3748,16 @@
         <v>166</v>
       </c>
       <c r="B163">
-        <v>4.215605321317608</v>
+        <v>3.64282087462809</v>
       </c>
       <c r="C163">
-        <v>11.28975737530301</v>
+        <v>10.88177510076368</v>
       </c>
       <c r="D163">
-        <v>58.21683692288725</v>
+        <v>58.83657317168884</v>
       </c>
       <c r="E163">
-        <v>4.237026257194607</v>
+        <v>4.095173351261175</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -3765,16 +3765,16 @@
         <v>167</v>
       </c>
       <c r="B164">
-        <v>3.85180210077151</v>
+        <v>3.632836051994063</v>
       </c>
       <c r="C164">
-        <v>10.72631612919282</v>
+        <v>10.6746666627999</v>
       </c>
       <c r="D164">
-        <v>58.0066360193345</v>
+        <v>58.77430308184197</v>
       </c>
       <c r="E164">
-        <v>5.176659580858527</v>
+        <v>3.978165094514076</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -3782,16 +3782,16 @@
         <v>168</v>
       </c>
       <c r="B165">
-        <v>5.032829808061084</v>
+        <v>3.727643999313968</v>
       </c>
       <c r="C165">
-        <v>10.90316737530921</v>
+        <v>10.89458329440499</v>
       </c>
       <c r="D165">
-        <v>58.18738920925216</v>
+        <v>59.23712411741586</v>
       </c>
       <c r="E165">
-        <v>5.225299909909848</v>
+        <v>3.987675446836926</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -3799,16 +3799,16 @@
         <v>169</v>
       </c>
       <c r="B166">
-        <v>4.959410349152803</v>
+        <v>3.718599929800944</v>
       </c>
       <c r="C166">
-        <v>11.0481122863969</v>
+        <v>10.89370289003741</v>
       </c>
       <c r="D166">
-        <v>58.30488231711913</v>
+        <v>58.2260233956392</v>
       </c>
       <c r="E166">
-        <v>5.247857635584142</v>
+        <v>4.083881697008336</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -3816,16 +3816,16 @@
         <v>170</v>
       </c>
       <c r="B167">
-        <v>3.879883672548218</v>
+        <v>3.662591732795965</v>
       </c>
       <c r="C167">
-        <v>11.11832569683024</v>
+        <v>10.47881734385518</v>
       </c>
       <c r="D167">
-        <v>58.1368793551697</v>
+        <v>57.89365952653627</v>
       </c>
       <c r="E167">
-        <v>4.077092418273513</v>
+        <v>4.065271986511274</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -3833,16 +3833,16 @@
         <v>171</v>
       </c>
       <c r="B168">
-        <v>5.350559659169738</v>
+        <v>3.651884570978742</v>
       </c>
       <c r="C168">
-        <v>10.92052802791809</v>
+        <v>10.73724862928218</v>
       </c>
       <c r="D168">
-        <v>57.92894395279405</v>
+        <v>58.02539115770061</v>
       </c>
       <c r="E168">
-        <v>4.144827595944158</v>
+        <v>3.999646130378068</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -3850,16 +3850,16 @@
         <v>172</v>
       </c>
       <c r="B169">
-        <v>4.749685123257846</v>
+        <v>3.641434159648061</v>
       </c>
       <c r="C169">
-        <v>10.76811331372529</v>
+        <v>10.57397294056332</v>
       </c>
       <c r="D169">
-        <v>58.25875511518781</v>
+        <v>58.74691740168655</v>
       </c>
       <c r="E169">
-        <v>4.19162413327647</v>
+        <v>3.945623761366411</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -3867,16 +3867,16 @@
         <v>173</v>
       </c>
       <c r="B170">
-        <v>3.957148066938929</v>
+        <v>3.722127380530124</v>
       </c>
       <c r="C170">
-        <v>10.99223941406306</v>
+        <v>10.80788662095766</v>
       </c>
       <c r="D170">
-        <v>58.2627243944647</v>
+        <v>59.19366071964836</v>
       </c>
       <c r="E170">
-        <v>3.956602234435108</v>
+        <v>4.073451217466414</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -3884,16 +3884,16 @@
         <v>174</v>
       </c>
       <c r="B171">
-        <v>5.357937725617698</v>
+        <v>3.623428061078468</v>
       </c>
       <c r="C171">
-        <v>11.27764598524807</v>
+        <v>10.60644621286171</v>
       </c>
       <c r="D171">
-        <v>58.18181168868124</v>
+        <v>59.23393322742105</v>
       </c>
       <c r="E171">
-        <v>4.066885408817362</v>
+        <v>4.019888571391943</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -3901,16 +3901,16 @@
         <v>175</v>
       </c>
       <c r="B172">
-        <v>4.672013489359777</v>
+        <v>3.621728400516327</v>
       </c>
       <c r="C172">
-        <v>11.0697188262936</v>
+        <v>10.59543333143247</v>
       </c>
       <c r="D172">
-        <v>58.15042764458137</v>
+        <v>58.19794241063855</v>
       </c>
       <c r="E172">
-        <v>3.997654696371425</v>
+        <v>3.933511847352</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -3918,16 +3918,16 @@
         <v>176</v>
       </c>
       <c r="B173">
-        <v>4.858720705657497</v>
+        <v>3.652545674018757</v>
       </c>
       <c r="C173">
-        <v>10.78690975819723</v>
+        <v>10.51673825558342</v>
       </c>
       <c r="D173">
-        <v>58.21503769350691</v>
+        <v>59.10281749600848</v>
       </c>
       <c r="E173">
-        <v>4.340236734815991</v>
+        <v>3.932856536201266</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -3935,16 +3935,16 @@
         <v>177</v>
       </c>
       <c r="B174">
-        <v>3.879183599905391</v>
+        <v>3.692963596437642</v>
       </c>
       <c r="C174">
-        <v>11.9173743746187</v>
+        <v>10.79310258732828</v>
       </c>
       <c r="D174">
-        <v>58.27748989291505</v>
+        <v>58.31029336868774</v>
       </c>
       <c r="E174">
-        <v>4.222992769241918</v>
+        <v>4.049106475171521</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -3952,16 +3952,16 @@
         <v>178</v>
       </c>
       <c r="B175">
-        <v>4.058898218162275</v>
+        <v>3.693961499965559</v>
       </c>
       <c r="C175">
-        <v>10.93375665098471</v>
+        <v>10.89605051992357</v>
       </c>
       <c r="D175">
-        <v>58.19671023584569</v>
+        <v>58.27247474624771</v>
       </c>
       <c r="E175">
-        <v>4.123740947470274</v>
+        <v>4.025408614061781</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -3969,16 +3969,16 @@
         <v>179</v>
       </c>
       <c r="B176">
-        <v>4.448697568945459</v>
+        <v>3.678586571444891</v>
       </c>
       <c r="C176">
-        <v>10.6930980157424</v>
+        <v>10.45046615895993</v>
       </c>
       <c r="D176">
-        <v>58.33105787981487</v>
+        <v>59.07414277261021</v>
       </c>
       <c r="E176">
-        <v>4.116629562174077</v>
+        <v>3.978155715801425</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -3986,16 +3986,16 @@
         <v>180</v>
       </c>
       <c r="B177">
-        <v>4.90644304684327</v>
+        <v>3.7224465775988</v>
       </c>
       <c r="C177">
-        <v>11.88879248796705</v>
+        <v>10.82508918159298</v>
       </c>
       <c r="D177">
-        <v>58.22814592706827</v>
+        <v>59.17730863112593</v>
       </c>
       <c r="E177">
-        <v>5.268700593922278</v>
+        <v>4.077325638291385</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -4003,16 +4003,16 @@
         <v>181</v>
       </c>
       <c r="B178">
-        <v>4.80240733871577</v>
+        <v>3.66149787933051</v>
       </c>
       <c r="C178">
-        <v>11.96771688363322</v>
+        <v>10.44323545191808</v>
       </c>
       <c r="D178">
-        <v>58.07010577274842</v>
+        <v>59.369719536557</v>
       </c>
       <c r="E178">
-        <v>5.255842438939281</v>
+        <v>4.087821105614474</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -4020,16 +4020,16 @@
         <v>182</v>
       </c>
       <c r="B179">
-        <v>3.869358077881013</v>
+        <v>3.69924406640745</v>
       </c>
       <c r="C179">
-        <v>10.57530447226885</v>
+        <v>10.66350665779952</v>
       </c>
       <c r="D179">
-        <v>57.90253012157114</v>
+        <v>58.70153143100795</v>
       </c>
       <c r="E179">
-        <v>5.389524467368588</v>
+        <v>3.953580649115389</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -4037,16 +4037,16 @@
         <v>183</v>
       </c>
       <c r="B180">
-        <v>4.908883152807438</v>
+        <v>3.641959571697156</v>
       </c>
       <c r="C180">
-        <v>10.44720069870407</v>
+        <v>10.90311598367798</v>
       </c>
       <c r="D180">
-        <v>57.89009447410907</v>
+        <v>59.32945609168299</v>
       </c>
       <c r="E180">
-        <v>3.9592922416209</v>
+        <v>3.956929944808542</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -4054,16 +4054,16 @@
         <v>184</v>
       </c>
       <c r="B181">
-        <v>4.019469104268408</v>
+        <v>3.657177712259787</v>
       </c>
       <c r="C181">
-        <v>11.51756383360456</v>
+        <v>10.8798627637439</v>
       </c>
       <c r="D181">
-        <v>58.13740502042789</v>
+        <v>58.01869008061323</v>
       </c>
       <c r="E181">
-        <v>4.934529226971828</v>
+        <v>3.985914618025088</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -4071,16 +4071,16 @@
         <v>185</v>
       </c>
       <c r="B182">
-        <v>3.766015419290502</v>
+        <v>3.633548045342526</v>
       </c>
       <c r="C182">
-        <v>11.05838285941235</v>
+        <v>10.93653898493019</v>
       </c>
       <c r="D182">
-        <v>57.95172773164145</v>
+        <v>58.87319783170966</v>
       </c>
       <c r="E182">
-        <v>4.428289455586676</v>
+        <v>3.979362275282158</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -4088,16 +4088,16 @@
         <v>186</v>
       </c>
       <c r="B183">
-        <v>3.903955181366035</v>
+        <v>3.709784299444473</v>
       </c>
       <c r="C183">
-        <v>10.92273811430717</v>
+        <v>10.6407845535679</v>
       </c>
       <c r="D183">
-        <v>58.36425517031542</v>
+        <v>59.10516822586674</v>
       </c>
       <c r="E183">
-        <v>4.318460330661988</v>
+        <v>3.968451185195711</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -4105,16 +4105,16 @@
         <v>187</v>
       </c>
       <c r="B184">
-        <v>3.873459121793744</v>
+        <v>3.690189216100001</v>
       </c>
       <c r="C184">
-        <v>11.6789916929283</v>
+        <v>10.81553563669176</v>
       </c>
       <c r="D184">
-        <v>57.97685422225243</v>
+        <v>58.59665976617801</v>
       </c>
       <c r="E184">
-        <v>4.335428577525468</v>
+        <v>3.987105358809545</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -4122,16 +4122,16 @@
         <v>188</v>
       </c>
       <c r="B185">
-        <v>4.501484062975</v>
+        <v>3.670613178692935</v>
       </c>
       <c r="C185">
-        <v>10.97543476481377</v>
+        <v>10.56020878964528</v>
       </c>
       <c r="D185">
-        <v>58.30562637588079</v>
+        <v>58.63461326434547</v>
       </c>
       <c r="E185">
-        <v>5.511369959884268</v>
+        <v>4.039255741691442</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -4139,16 +4139,16 @@
         <v>189</v>
       </c>
       <c r="B186">
-        <v>5.345255511541469</v>
+        <v>3.629639507227687</v>
       </c>
       <c r="C186">
-        <v>11.01441144215786</v>
+        <v>10.64750729416874</v>
       </c>
       <c r="D186">
-        <v>57.88183688293714</v>
+        <v>57.98459533799543</v>
       </c>
       <c r="E186">
-        <v>5.124879386497911</v>
+        <v>4.030064322320277</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -4156,16 +4156,16 @@
         <v>190</v>
       </c>
       <c r="B187">
-        <v>3.746332526209104</v>
+        <v>3.662481197755814</v>
       </c>
       <c r="C187">
-        <v>11.97096600841115</v>
+        <v>10.79549827243194</v>
       </c>
       <c r="D187">
-        <v>58.0676164873187</v>
+        <v>58.60696589011063</v>
       </c>
       <c r="E187">
-        <v>5.094281263451973</v>
+        <v>3.949785547679617</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -4173,16 +4173,16 @@
         <v>191</v>
       </c>
       <c r="B188">
-        <v>4.86024879358022</v>
+        <v>3.646400133854939</v>
       </c>
       <c r="C188">
-        <v>10.80341845474052</v>
+        <v>10.81933727656777</v>
       </c>
       <c r="D188">
-        <v>58.05909857069993</v>
+        <v>58.30657423253079</v>
       </c>
       <c r="E188">
-        <v>5.270006811761887</v>
+        <v>3.954190235669413</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -4190,16 +4190,16 @@
         <v>192</v>
       </c>
       <c r="B189">
-        <v>4.900877178246582</v>
+        <v>3.620391133018538</v>
       </c>
       <c r="C189">
-        <v>11.04478035393212</v>
+        <v>10.58356955083592</v>
       </c>
       <c r="D189">
-        <v>58.27136478441376</v>
+        <v>58.84719024857535</v>
       </c>
       <c r="E189">
-        <v>5.467882818469581</v>
+        <v>4.011175539006592</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -4207,16 +4207,16 @@
         <v>193</v>
       </c>
       <c r="B190">
-        <v>4.681528236941909</v>
+        <v>3.713227771373933</v>
       </c>
       <c r="C190">
-        <v>11.70562000212696</v>
+        <v>10.53989662571035</v>
       </c>
       <c r="D190">
-        <v>57.93291224835079</v>
+        <v>59.27419166405505</v>
       </c>
       <c r="E190">
-        <v>4.964456179782742</v>
+        <v>3.986517858255227</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -4224,16 +4224,16 @@
         <v>194</v>
       </c>
       <c r="B191">
-        <v>3.62919621480207</v>
+        <v>3.673451146949523</v>
       </c>
       <c r="C191">
-        <v>10.51837365481483</v>
+        <v>10.79221169425571</v>
       </c>
       <c r="D191">
-        <v>58.00318622023838</v>
+        <v>58.9966329310385</v>
       </c>
       <c r="E191">
-        <v>4.963157480842147</v>
+        <v>4.074962376761224</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -4241,16 +4241,16 @@
         <v>195</v>
       </c>
       <c r="B192">
-        <v>3.799810384794264</v>
+        <v>3.700286927359266</v>
       </c>
       <c r="C192">
-        <v>11.32775652181935</v>
+        <v>10.62806908785474</v>
       </c>
       <c r="D192">
-        <v>58.16041661323246</v>
+        <v>58.64648643541897</v>
       </c>
       <c r="E192">
-        <v>5.022777130812081</v>
+        <v>3.954648769390094</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -4258,16 +4258,16 @@
         <v>196</v>
       </c>
       <c r="B193">
-        <v>4.708548663313516</v>
+        <v>3.712308329553708</v>
       </c>
       <c r="C193">
-        <v>11.48241816425793</v>
+        <v>10.89228422295725</v>
       </c>
       <c r="D193">
-        <v>57.91559835158014</v>
+        <v>59.07122346494453</v>
       </c>
       <c r="E193">
-        <v>5.24791396968012</v>
+        <v>3.970405108884154</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -4275,16 +4275,16 @@
         <v>197</v>
       </c>
       <c r="B194">
-        <v>4.047244769004164</v>
+        <v>3.655888638333155</v>
       </c>
       <c r="C194">
-        <v>11.9544957795033</v>
+        <v>10.58937220940422</v>
       </c>
       <c r="D194">
-        <v>58.02645297020218</v>
+        <v>58.13602853074271</v>
       </c>
       <c r="E194">
-        <v>4.373606284948889</v>
+        <v>4.055531796600202</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -4292,16 +4292,16 @@
         <v>198</v>
       </c>
       <c r="B195">
-        <v>3.695845272789291</v>
+        <v>3.649616037652327</v>
       </c>
       <c r="C195">
-        <v>11.43960939085195</v>
+        <v>10.60016127526931</v>
       </c>
       <c r="D195">
-        <v>57.94916489623225</v>
+        <v>58.32225159882334</v>
       </c>
       <c r="E195">
-        <v>5.284721265756035</v>
+        <v>4.089346792487585</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -4309,16 +4309,16 @@
         <v>199</v>
       </c>
       <c r="B196">
-        <v>5.042982132973973</v>
+        <v>3.726434424682771</v>
       </c>
       <c r="C196">
-        <v>11.8019535333152</v>
+        <v>10.7104279932715</v>
       </c>
       <c r="D196">
-        <v>58.36533666840418</v>
+        <v>58.59133787130263</v>
       </c>
       <c r="E196">
-        <v>4.819057262176062</v>
+        <v>4.084138060716207</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -4326,16 +4326,16 @@
         <v>200</v>
       </c>
       <c r="B197">
-        <v>5.155803226574747</v>
+        <v>3.649040570947035</v>
       </c>
       <c r="C197">
-        <v>11.85742850147574</v>
+        <v>10.84657356513412</v>
       </c>
       <c r="D197">
-        <v>58.1086318547852</v>
+        <v>58.5147642464906</v>
       </c>
       <c r="E197">
-        <v>3.985275943790552</v>
+        <v>3.980228951283475</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -4343,16 +4343,16 @@
         <v>201</v>
       </c>
       <c r="B198">
-        <v>4.68953064577143</v>
+        <v>3.728056527832105</v>
       </c>
       <c r="C198">
-        <v>11.62404362893826</v>
+        <v>10.61803225853648</v>
       </c>
       <c r="D198">
-        <v>57.96074001849445</v>
+        <v>58.06653611668114</v>
       </c>
       <c r="E198">
-        <v>5.4111022814162</v>
+        <v>3.958298424768473</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -4360,16 +4360,16 @@
         <v>202</v>
       </c>
       <c r="B199">
-        <v>3.809598418045775</v>
+        <v>3.661925669489244</v>
       </c>
       <c r="C199">
-        <v>11.03363320244439</v>
+        <v>10.56890523504541</v>
       </c>
       <c r="D199">
-        <v>58.26226219983565</v>
+        <v>59.288158492805</v>
       </c>
       <c r="E199">
-        <v>4.901741297165547</v>
+        <v>3.976245688560821</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -4377,16 +4377,16 @@
         <v>203</v>
       </c>
       <c r="B200">
-        <v>5.035035833554659</v>
+        <v>3.685939955456293</v>
       </c>
       <c r="C200">
-        <v>11.98904568114161</v>
+        <v>10.71930892677913</v>
       </c>
       <c r="D200">
-        <v>58.10253180284654</v>
+        <v>58.52907887517044</v>
       </c>
       <c r="E200">
-        <v>4.478764063882009</v>
+        <v>4.06685137320375</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -4394,16 +4394,16 @@
         <v>204</v>
       </c>
       <c r="B201">
-        <v>4.824862543304049</v>
+        <v>3.704340465224145</v>
       </c>
       <c r="C201">
-        <v>11.42618798247145</v>
+        <v>10.68135545691604</v>
       </c>
       <c r="D201">
-        <v>58.19928269888145</v>
+        <v>59.2559869305904</v>
       </c>
       <c r="E201">
-        <v>4.928022131252842</v>
+        <v>4.099571825064395</v>
       </c>
     </row>
   </sheetData>
